--- a/data/templates/NFC_Inventory_Import_Template.xlsx
+++ b/data/templates/NFC_Inventory_Import_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rcda8e815ebc64c56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R32d7c49b4bbc466d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="R03bec88663de4996"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="Rc505b70c00a549f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="Rb193db80559a469a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R7baea68a36c64486"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R1c012ad657294ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="R58c6d42c11ef4b52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="R9ab1bad1467641e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R96b6723f2dab4510"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -404,9 +404,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="BundleContentsTable" displayName="BundleContentsTable" ref="A1:H4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H4"/>
-  <x:tableColumns count="8">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="BundleContentsTable" displayName="BundleContentsTable" ref="A1:I4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I4"/>
+  <x:tableColumns count="9">
     <x:tableColumn id="1" name="asset_code"/>
     <x:tableColumn id="2" name="component_name"/>
     <x:tableColumn id="3" name="manufacturer"/>
@@ -415,6 +415,7 @@
     <x:tableColumn id="6" name="quantity"/>
     <x:tableColumn id="7" name="required_on_return"/>
     <x:tableColumn id="8" name="notes"/>
+    <x:tableColumn id="9" name="photo_reference"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -806,8 +807,12 @@
       <x:c r="H12" s="58"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="63"/>
-      <x:c r="B13" s="62"/>
+      <x:c r="A13" s="63" t="str">
+        <x:v>Photos</x:v>
+      </x:c>
+      <x:c r="B13" s="62" t="str">
+        <x:v>Use a stable HTTPS image URL for each equipment row and bundle component. Keep the placeholder until a suitable photo is available.</x:v>
+      </x:c>
       <x:c r="C13" s="58"/>
       <x:c r="D13" s="58"/>
       <x:c r="E13" s="58"/>
@@ -998,7 +1003,9 @@
       <x:c r="S2" s="78" t="str"/>
       <x:c r="T2" s="78" t="str"/>
       <x:c r="U2" s="78" t="str"/>
-      <x:c r="V2" s="78" t="str"/>
+      <x:c r="V2" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="76" t="str">
@@ -1034,7 +1041,9 @@
       <x:c r="S3" s="78" t="str"/>
       <x:c r="T3" s="78" t="str"/>
       <x:c r="U3" s="78" t="str"/>
-      <x:c r="V3" s="78" t="str"/>
+      <x:c r="V3" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="76" t="str">
@@ -1070,7 +1079,9 @@
       <x:c r="S4" s="78" t="str"/>
       <x:c r="T4" s="78" t="str"/>
       <x:c r="U4" s="78" t="str"/>
-      <x:c r="V4" s="78" t="str"/>
+      <x:c r="V4" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="76" t="str">
@@ -1106,7 +1117,9 @@
       <x:c r="S5" s="78" t="str"/>
       <x:c r="T5" s="78" t="str"/>
       <x:c r="U5" s="78" t="str"/>
-      <x:c r="V5" s="78" t="str"/>
+      <x:c r="V5" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="76" t="str">
@@ -1142,7 +1155,9 @@
       <x:c r="S6" s="78" t="str"/>
       <x:c r="T6" s="78" t="str"/>
       <x:c r="U6" s="78" t="str"/>
-      <x:c r="V6" s="78" t="str"/>
+      <x:c r="V6" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="76" t="str">
@@ -1178,7 +1193,9 @@
       <x:c r="S7" s="78" t="str"/>
       <x:c r="T7" s="78" t="str"/>
       <x:c r="U7" s="78" t="str"/>
-      <x:c r="V7" s="78" t="str"/>
+      <x:c r="V7" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="76" t="str">
@@ -1214,7 +1231,9 @@
       <x:c r="S8" s="78" t="str"/>
       <x:c r="T8" s="78" t="str"/>
       <x:c r="U8" s="78" t="str"/>
-      <x:c r="V8" s="78" t="str"/>
+      <x:c r="V8" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="76" t="str">
@@ -1250,7 +1269,9 @@
       <x:c r="S9" s="78" t="str"/>
       <x:c r="T9" s="78" t="str"/>
       <x:c r="U9" s="78" t="str"/>
-      <x:c r="V9" s="78" t="str"/>
+      <x:c r="V9" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="76" t="str">
@@ -1286,7 +1307,9 @@
       <x:c r="S10" s="78" t="str"/>
       <x:c r="T10" s="78" t="str"/>
       <x:c r="U10" s="78" t="str"/>
-      <x:c r="V10" s="78" t="str"/>
+      <x:c r="V10" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="76" t="str">
@@ -1322,7 +1345,9 @@
       <x:c r="S11" s="78" t="str"/>
       <x:c r="T11" s="78" t="str"/>
       <x:c r="U11" s="78" t="str"/>
-      <x:c r="V11" s="78" t="str"/>
+      <x:c r="V11" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="76" t="str">
@@ -1358,7 +1383,9 @@
       <x:c r="S12" s="78" t="str"/>
       <x:c r="T12" s="78" t="str"/>
       <x:c r="U12" s="78" t="str"/>
-      <x:c r="V12" s="78" t="str"/>
+      <x:c r="V12" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="76" t="str">
@@ -1394,7 +1421,9 @@
       <x:c r="S13" s="78" t="str"/>
       <x:c r="T13" s="78" t="str"/>
       <x:c r="U13" s="78" t="str"/>
-      <x:c r="V13" s="78" t="str"/>
+      <x:c r="V13" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="76" t="str">
@@ -1430,7 +1459,9 @@
       <x:c r="S14" s="78" t="str"/>
       <x:c r="T14" s="78" t="str"/>
       <x:c r="U14" s="78" t="str"/>
-      <x:c r="V14" s="78" t="str"/>
+      <x:c r="V14" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="76" t="str">
@@ -1466,7 +1497,9 @@
       <x:c r="S15" s="78" t="str"/>
       <x:c r="T15" s="78" t="str"/>
       <x:c r="U15" s="78" t="str"/>
-      <x:c r="V15" s="78" t="str"/>
+      <x:c r="V15" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="76" t="str">
@@ -1502,7 +1535,9 @@
       <x:c r="S16" s="78" t="str"/>
       <x:c r="T16" s="78" t="str"/>
       <x:c r="U16" s="78" t="str"/>
-      <x:c r="V16" s="78" t="str"/>
+      <x:c r="V16" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="76" t="str">
@@ -1538,7 +1573,9 @@
       <x:c r="S17" s="78" t="str"/>
       <x:c r="T17" s="78" t="str"/>
       <x:c r="U17" s="78" t="str"/>
-      <x:c r="V17" s="78" t="str"/>
+      <x:c r="V17" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="76" t="str">
@@ -1574,7 +1611,9 @@
       <x:c r="S18" s="78" t="str"/>
       <x:c r="T18" s="78" t="str"/>
       <x:c r="U18" s="78" t="str"/>
-      <x:c r="V18" s="78" t="str"/>
+      <x:c r="V18" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="76" t="str">
@@ -1610,7 +1649,9 @@
       <x:c r="S19" s="78" t="str"/>
       <x:c r="T19" s="78" t="str"/>
       <x:c r="U19" s="78" t="str"/>
-      <x:c r="V19" s="78" t="str"/>
+      <x:c r="V19" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="76" t="str">
@@ -1646,7 +1687,9 @@
       <x:c r="S20" s="78" t="str"/>
       <x:c r="T20" s="78" t="str"/>
       <x:c r="U20" s="78" t="str"/>
-      <x:c r="V20" s="78" t="str"/>
+      <x:c r="V20" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="76" t="str">
@@ -1682,7 +1725,9 @@
       <x:c r="S21" s="78" t="str"/>
       <x:c r="T21" s="78" t="str"/>
       <x:c r="U21" s="78" t="str"/>
-      <x:c r="V21" s="78" t="str"/>
+      <x:c r="V21" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="76" t="str">
@@ -1718,7 +1763,9 @@
       <x:c r="S22" s="78" t="str"/>
       <x:c r="T22" s="78" t="str"/>
       <x:c r="U22" s="78" t="str"/>
-      <x:c r="V22" s="78" t="str"/>
+      <x:c r="V22" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="76" t="str">
@@ -1754,7 +1801,9 @@
       <x:c r="S23" s="78" t="str"/>
       <x:c r="T23" s="78" t="str"/>
       <x:c r="U23" s="78" t="str"/>
-      <x:c r="V23" s="78" t="str"/>
+      <x:c r="V23" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="76" t="str">
@@ -1790,7 +1839,9 @@
       <x:c r="S24" s="78" t="str"/>
       <x:c r="T24" s="78" t="str"/>
       <x:c r="U24" s="78" t="str"/>
-      <x:c r="V24" s="78" t="str"/>
+      <x:c r="V24" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="76" t="str">
@@ -1826,7 +1877,9 @@
       <x:c r="S25" s="78" t="str"/>
       <x:c r="T25" s="78" t="str"/>
       <x:c r="U25" s="78" t="str"/>
-      <x:c r="V25" s="78" t="str"/>
+      <x:c r="V25" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="76" t="str">
@@ -1862,7 +1915,9 @@
       <x:c r="S26" s="78" t="str"/>
       <x:c r="T26" s="78" t="str"/>
       <x:c r="U26" s="78" t="str"/>
-      <x:c r="V26" s="78" t="str"/>
+      <x:c r="V26" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="76" t="str">
@@ -1898,7 +1953,9 @@
       <x:c r="S27" s="78" t="str"/>
       <x:c r="T27" s="78" t="str"/>
       <x:c r="U27" s="78" t="str"/>
-      <x:c r="V27" s="78" t="str"/>
+      <x:c r="V27" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="76" t="str">
@@ -1934,7 +1991,9 @@
       <x:c r="S28" s="78" t="str"/>
       <x:c r="T28" s="78" t="str"/>
       <x:c r="U28" s="78" t="str"/>
-      <x:c r="V28" s="78" t="str"/>
+      <x:c r="V28" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="76" t="str">
@@ -1970,7 +2029,9 @@
       <x:c r="S29" s="78" t="str"/>
       <x:c r="T29" s="78" t="str"/>
       <x:c r="U29" s="78" t="str"/>
-      <x:c r="V29" s="78" t="str"/>
+      <x:c r="V29" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="76" t="str">
@@ -2006,7 +2067,9 @@
       <x:c r="S30" s="78" t="str"/>
       <x:c r="T30" s="78" t="str"/>
       <x:c r="U30" s="78" t="str"/>
-      <x:c r="V30" s="78" t="str"/>
+      <x:c r="V30" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="76" t="str">
@@ -2042,7 +2105,9 @@
       <x:c r="S31" s="78" t="str"/>
       <x:c r="T31" s="78" t="str"/>
       <x:c r="U31" s="78" t="str"/>
-      <x:c r="V31" s="78" t="str"/>
+      <x:c r="V31" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="76" t="str">
@@ -2078,7 +2143,9 @@
       <x:c r="S32" s="78" t="str"/>
       <x:c r="T32" s="78" t="str"/>
       <x:c r="U32" s="78" t="str"/>
-      <x:c r="V32" s="78" t="str"/>
+      <x:c r="V32" s="78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="5">
@@ -2100,7 +2167,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4ba3e61930f4410"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R383badd084114f43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2120,6 +2187,7 @@
     <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="42" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -2147,6 +2215,9 @@
       <x:c r="H1" s="38" t="str">
         <x:v>notes</x:v>
       </x:c>
+      <x:c r="I1" t="str">
+        <x:v>photo_reference</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="77" t="str">
@@ -2165,6 +2236,9 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H2" s="78" t="str"/>
+      <x:c r="I2" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="77" t="str">
@@ -2183,6 +2257,9 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H3" s="78" t="str"/>
+      <x:c r="I3" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="77" t="str">
@@ -2201,6 +2278,9 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H4" s="78" t="str"/>
+      <x:c r="I4" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
@@ -2216,7 +2296,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd29ceefbe4cb473e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdec5bddf0d4e455a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2328,7 +2408,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52629735925644c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4793a36a75324730"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2458,7 +2538,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42f40225afcb4aae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd23e6904df6e47d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/templates/NFC_Inventory_Import_Template.xlsx
+++ b/data/templates/NFC_Inventory_Import_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R7baea68a36c64486"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R1c012ad657294ffc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="R58c6d42c11ef4b52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="R9ab1bad1467641e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R96b6723f2dab4510"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R27ae6c101c524cea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rd70638f0cb154ec8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="R6db5d35c805a4367"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="R309d68c952674a0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R8918985fc9914dad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -811,7 +811,7 @@
         <x:v>Photos</x:v>
       </x:c>
       <x:c r="B13" s="62" t="str">
-        <x:v>Use a stable HTTPS image URL for each equipment row and bundle component. Keep the placeholder until a suitable photo is available.</x:v>
+        <x:v>Use a stable HTTPS image URL for each equipment row and bundle component. Product reference images are listed in docs/image-sources.md; replace them with lab-owned photos when available. Keep the placeholder when the exact model is unknown.</x:v>
       </x:c>
       <x:c r="C13" s="58"/>
       <x:c r="D13" s="58"/>
@@ -1004,7 +1004,7 @@
       <x:c r="T2" s="78" t="str"/>
       <x:c r="U2" s="78" t="str"/>
       <x:c r="V2" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/misty-ii.png</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1042,7 +1042,7 @@
       <x:c r="T3" s="78" t="str"/>
       <x:c r="U3" s="78" t="str"/>
       <x:c r="V3" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/misty-ii.png</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1080,7 +1080,7 @@
       <x:c r="T4" s="78" t="str"/>
       <x:c r="U4" s="78" t="str"/>
       <x:c r="V4" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1118,7 +1118,7 @@
       <x:c r="T5" s="78" t="str"/>
       <x:c r="U5" s="78" t="str"/>
       <x:c r="V5" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-lite.png</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1308,7 +1308,7 @@
       <x:c r="T10" s="78" t="str"/>
       <x:c r="U10" s="78" t="str"/>
       <x:c r="V10" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/azure-kinect-dk.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1346,7 +1346,7 @@
       <x:c r="T11" s="78" t="str"/>
       <x:c r="U11" s="78" t="str"/>
       <x:c r="V11" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/azure-kinect-dk.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1384,7 +1384,7 @@
       <x:c r="T12" s="78" t="str"/>
       <x:c r="U12" s="78" t="str"/>
       <x:c r="V12" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/anker-powerconf-c200.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1422,7 +1422,7 @@
       <x:c r="T13" s="78" t="str"/>
       <x:c r="U13" s="78" t="str"/>
       <x:c r="V13" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/anker-powerconf-c200.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1460,7 +1460,7 @@
       <x:c r="T14" s="78" t="str"/>
       <x:c r="U14" s="78" t="str"/>
       <x:c r="V14" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/victiv-tripod.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1498,7 +1498,7 @@
       <x:c r="T15" s="78" t="str"/>
       <x:c r="U15" s="78" t="str"/>
       <x:c r="V15" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/victiv-tripod.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1536,7 +1536,7 @@
       <x:c r="T16" s="78" t="str"/>
       <x:c r="U16" s="78" t="str"/>
       <x:c r="V16" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/victiv-tripod.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1650,7 +1650,7 @@
       <x:c r="T19" s="78" t="str"/>
       <x:c r="U19" s="78" t="str"/>
       <x:c r="V19" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/lammcou-small-tripod.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1688,7 +1688,7 @@
       <x:c r="T20" s="78" t="str"/>
       <x:c r="U20" s="78" t="str"/>
       <x:c r="V20" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/lammcou-small-tripod.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1878,7 +1878,7 @@
       <x:c r="T25" s="78" t="str"/>
       <x:c r="U25" s="78" t="str"/>
       <x:c r="V25" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/boya-v30.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1916,7 +1916,7 @@
       <x:c r="T26" s="78" t="str"/>
       <x:c r="U26" s="78" t="str"/>
       <x:c r="V26" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/dji-mic-mini.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2030,7 +2030,7 @@
       <x:c r="T29" s="78" t="str"/>
       <x:c r="U29" s="78" t="str"/>
       <x:c r="V29" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/belkin-bsv804.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2068,7 +2068,7 @@
       <x:c r="T30" s="78" t="str"/>
       <x:c r="U30" s="78" t="str"/>
       <x:c r="V30" s="78" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/tapo-p110.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -2167,7 +2167,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R383badd084114f43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1e1e7b7b4224b5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2237,7 +2237,7 @@
       </x:c>
       <x:c r="H2" s="78" t="str"/>
       <x:c r="I2" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2296,7 +2296,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdec5bddf0d4e455a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf447d4fd9bc14bbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2408,7 +2408,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4793a36a75324730"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17535bd80f314851"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2538,7 +2538,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd23e6904df6e47d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f3a24519bad4cdf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/templates/NFC_Inventory_Import_Template.xlsx
+++ b/data/templates/NFC_Inventory_Import_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R6a93ed6a73084ced"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R02bb2c5185b44264"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="R07f74c1e96a24817"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="R47d29cfc2359400a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="Rc9732e0284f84455"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R07fea3f966bf445e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R4035cf9c9ed2443b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="R36221e72967543d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="R1f1ec372e0984d85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R50412a6762a143ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -219,9 +219,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">TAB-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Lenovo Tab M10</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Tablets</x:t>
@@ -1797,19 +1794,25 @@
       <x:c r="A8" s="9" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B8" s="10" t="s">
+      <x:c r="B8" s="10" t="str">
+        <x:v>Lenovo Tab M10 (3rd Gen)</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C8" s="10" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="D8" s="10" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="E8" s="4"/>
-      <x:c r="F8" s="4"/>
+      <x:c r="E8" s="4" t="str">
+        <x:v>Lenovo</x:v>
+      </x:c>
+      <x:c r="F8" s="4" t="str">
+        <x:v>TB328FU</x:v>
+      </x:c>
       <x:c r="G8" s="4"/>
-      <x:c r="H8" s="11"/>
+      <x:c r="H8" s="11" t="str">
+        <x:v>3rd Gen</x:v>
+      </x:c>
       <x:c r="I8" s="11"/>
       <x:c r="J8" s="11"/>
       <x:c r="K8" s="12" t="s">
@@ -1828,26 +1831,32 @@
       <x:c r="T8" s="11"/>
       <x:c r="U8" s="11"/>
       <x:c r="V8" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="37.5">
       <x:c r="A9" s="9" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>Lenovo Tab M10 (3rd Gen)</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C9" s="10" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="D9" s="10" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="E9" s="4"/>
-      <x:c r="F9" s="4"/>
+      <x:c r="E9" s="4" t="str">
+        <x:v>Lenovo</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="str">
+        <x:v>TB328FU</x:v>
+      </x:c>
       <x:c r="G9" s="4"/>
-      <x:c r="H9" s="11"/>
+      <x:c r="H9" s="11" t="str">
+        <x:v>3rd Gen</x:v>
+      </x:c>
       <x:c r="I9" s="11"/>
       <x:c r="J9" s="11"/>
       <x:c r="K9" s="12" t="s">
@@ -1866,18 +1875,18 @@
       <x:c r="T9" s="11"/>
       <x:c r="U9" s="11"/>
       <x:c r="V9" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="37.5">
       <x:c r="A10" s="9" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B10" s="10" t="s">
+      <x:c r="C10" s="10" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="C10" s="10" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="D10" s="10" t="s">
         <x:v>51</x:v>
@@ -1904,18 +1913,18 @@
       <x:c r="T10" s="11"/>
       <x:c r="U10" s="11"/>
       <x:c r="V10" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="37.5">
       <x:c r="A11" s="9" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B11" s="10" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="C11" s="10" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="D11" s="10" t="s">
         <x:v>51</x:v>
@@ -1942,15 +1951,15 @@
       <x:c r="T11" s="11"/>
       <x:c r="U11" s="11"/>
       <x:c r="V11" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="37.5">
       <x:c r="A12" s="9" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="B12" s="10" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
         <x:v>Cameras</x:v>
@@ -1980,15 +1989,15 @@
       <x:c r="T12" s="11"/>
       <x:c r="U12" s="11"/>
       <x:c r="V12" s="11" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="37.5">
       <x:c r="A13" s="9" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B13" s="10" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
         <x:v>Cameras</x:v>
@@ -2018,15 +2027,15 @@
       <x:c r="T13" s="11"/>
       <x:c r="U13" s="11"/>
       <x:c r="V13" s="11" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="37.5">
       <x:c r="A14" s="9" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="B14" s="10" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
         <x:v>Cameras</x:v>
@@ -2035,14 +2044,14 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E14" s="4" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="F14" s="4" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="G14" s="4"/>
       <x:c r="H14" s="11" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="I14" s="11"/>
       <x:c r="J14" s="11"/>
@@ -2063,18 +2072,18 @@
       <x:c r="S14" s="11"/>
       <x:c r="T14" s="11"/>
       <x:c r="U14" s="11" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="V14" s="11" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="V14" s="11" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="37.5">
       <x:c r="A15" s="9" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B15" s="10" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
         <x:v>Cameras</x:v>
@@ -2083,14 +2092,14 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F15" s="4" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="F15" s="4" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="G15" s="4"/>
       <x:c r="H15" s="11" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="I15" s="11"/>
       <x:c r="J15" s="11"/>
@@ -2111,21 +2120,21 @@
       <x:c r="S15" s="11"/>
       <x:c r="T15" s="11"/>
       <x:c r="U15" s="11" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="V15" s="11" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="V15" s="11" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="37.5">
       <x:c r="A16" s="9" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B16" s="10" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="C16" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D16" s="10" t="s">
         <x:v>51</x:v>
@@ -2152,18 +2161,18 @@
       <x:c r="T16" s="11"/>
       <x:c r="U16" s="11"/>
       <x:c r="V16" s="11" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="37.5">
       <x:c r="A17" s="9" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B17" s="10" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C17" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D17" s="10" t="s">
         <x:v>51</x:v>
@@ -2190,18 +2199,18 @@
       <x:c r="T17" s="11"/>
       <x:c r="U17" s="11"/>
       <x:c r="V17" s="11" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="37.5">
       <x:c r="A18" s="9" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B18" s="10" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C18" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D18" s="10" t="s">
         <x:v>51</x:v>
@@ -2228,18 +2237,18 @@
       <x:c r="T18" s="11"/>
       <x:c r="U18" s="11"/>
       <x:c r="V18" s="11" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="37.5">
       <x:c r="A19" s="9" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B19" s="10" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="C19" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D19" s="10" t="s">
         <x:v>51</x:v>
@@ -2266,18 +2275,18 @@
       <x:c r="T19" s="11"/>
       <x:c r="U19" s="11"/>
       <x:c r="V19" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="37.5">
       <x:c r="A20" s="9" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B20" s="10" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C20" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D20" s="10" t="s">
         <x:v>51</x:v>
@@ -2304,18 +2313,18 @@
       <x:c r="T20" s="11"/>
       <x:c r="U20" s="11"/>
       <x:c r="V20" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="37.5">
       <x:c r="A21" s="9" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B21" s="10" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B21" s="10" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="C21" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D21" s="10" t="s">
         <x:v>51</x:v>
@@ -2342,18 +2351,18 @@
       <x:c r="T21" s="11"/>
       <x:c r="U21" s="11"/>
       <x:c r="V21" s="11" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="37.5">
       <x:c r="A22" s="9" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B22" s="10" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C22" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D22" s="10" t="s">
         <x:v>51</x:v>
@@ -2380,18 +2389,18 @@
       <x:c r="T22" s="11"/>
       <x:c r="U22" s="11"/>
       <x:c r="V22" s="11" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="37.5">
       <x:c r="A23" s="9" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B23" s="10" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="B23" s="10" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="C23" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D23" s="10" t="s">
         <x:v>51</x:v>
@@ -2418,18 +2427,18 @@
       <x:c r="T23" s="11"/>
       <x:c r="U23" s="11"/>
       <x:c r="V23" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="37.5">
       <x:c r="A24" s="9" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B24" s="10" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C24" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D24" s="10" t="s">
         <x:v>51</x:v>
@@ -2456,31 +2465,31 @@
       <x:c r="T24" s="11"/>
       <x:c r="U24" s="11"/>
       <x:c r="V24" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="37.5">
       <x:c r="A25" s="9" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B25" s="10" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="B25" s="10" t="s">
+      <x:c r="C25" s="10" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C25" s="10" t="s">
+      <x:c r="D25" s="10" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E25" s="4" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="D25" s="10" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E25" s="4" t="s">
+      <x:c r="F25" s="4" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="F25" s="4" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="G25" s="4"/>
       <x:c r="H25" s="11" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I25" s="11"/>
       <x:c r="J25" s="11"/>
@@ -2500,31 +2509,31 @@
       <x:c r="T25" s="11"/>
       <x:c r="U25" s="11"/>
       <x:c r="V25" s="11" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="37.5">
       <x:c r="A26" s="9" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B26" s="10" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C26" s="10" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C26" s="10" t="s">
+      <x:c r="D26" s="10" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E26" s="4" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="D26" s="10" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E26" s="4" t="s">
+      <x:c r="F26" s="4" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="F26" s="4" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="G26" s="4"/>
       <x:c r="H26" s="11" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I26" s="11"/>
       <x:c r="J26" s="11"/>
@@ -2544,31 +2553,31 @@
       <x:c r="T26" s="11"/>
       <x:c r="U26" s="11"/>
       <x:c r="V26" s="11" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="37.5">
       <x:c r="A27" s="9" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B27" s="10" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B27" s="10" t="s">
+      <x:c r="C27" s="10" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="C27" s="10" t="s">
+      <x:c r="D27" s="10" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E27" s="4" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="D27" s="10" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E27" s="4" t="s">
+      <x:c r="F27" s="4" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="F27" s="4" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="G27" s="4"/>
       <x:c r="H27" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="I27" s="11"/>
       <x:c r="J27" s="11"/>
@@ -2588,18 +2597,18 @@
       <x:c r="T27" s="11"/>
       <x:c r="U27" s="11"/>
       <x:c r="V27" s="11" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="37.5">
       <x:c r="A28" s="9" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B28" s="10" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="B28" s="10" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="C28" s="10" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D28" s="10" t="s">
         <x:v>51</x:v>
@@ -2626,18 +2635,18 @@
       <x:c r="T28" s="11"/>
       <x:c r="U28" s="11"/>
       <x:c r="V28" s="11" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="37.5">
       <x:c r="A29" s="9" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B29" s="10" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="B29" s="10" t="s">
+      <x:c r="C29" s="10" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="C29" s="10" t="s">
-        <x:v>124</x:v>
       </x:c>
       <x:c r="D29" s="10" t="s">
         <x:v>51</x:v>
@@ -2664,18 +2673,18 @@
       <x:c r="T29" s="11"/>
       <x:c r="U29" s="11"/>
       <x:c r="V29" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="37.5">
       <x:c r="A30" s="9" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B30" s="10" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="C30" s="10" t="s">
-        <x:v>124</x:v>
       </x:c>
       <x:c r="D30" s="10" t="s">
         <x:v>51</x:v>
@@ -2702,18 +2711,18 @@
       <x:c r="T30" s="11"/>
       <x:c r="U30" s="11"/>
       <x:c r="V30" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="37.5">
       <x:c r="A31" s="9" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B31" s="10" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B31" s="10" t="s">
-        <x:v>127</x:v>
-      </x:c>
       <x:c r="C31" s="10" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D31" s="10" t="s">
         <x:v>51</x:v>
@@ -2740,18 +2749,18 @@
       <x:c r="T31" s="11"/>
       <x:c r="U31" s="11"/>
       <x:c r="V31" s="11" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="37.5">
       <x:c r="A32" s="9" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B32" s="10" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B32" s="10" t="s">
-        <x:v>130</x:v>
-      </x:c>
       <x:c r="C32" s="10" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D32" s="10" t="s">
         <x:v>51</x:v>
@@ -2778,31 +2787,31 @@
       <x:c r="T32" s="11"/>
       <x:c r="U32" s="11"/>
       <x:c r="V32" s="11" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="87.5">
       <x:c r="A33" s="9" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B33" s="10" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="B33" s="10" t="s">
+      <x:c r="C33" s="10" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="C33" s="10" t="s">
+      <x:c r="D33" s="10" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D33" s="10" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E33" s="4" t="s">
+      <x:c r="F33" s="4" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="F33" s="4" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="G33" s="4"/>
       <x:c r="H33" s="11" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="I33" s="11"/>
       <x:c r="J33" s="11"/>
@@ -2823,34 +2832,34 @@
       <x:c r="S33" s="11"/>
       <x:c r="T33" s="11"/>
       <x:c r="U33" s="11" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="V33" s="11" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="V33" s="11" t="s">
-        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="87.5">
       <x:c r="A34" s="9" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B34" s="10" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C34" s="10" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="C34" s="10" t="s">
+      <x:c r="D34" s="10" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D34" s="10" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E34" s="4" t="s">
+      <x:c r="F34" s="4" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="F34" s="4" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="G34" s="4"/>
       <x:c r="H34" s="11" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="I34" s="11"/>
       <x:c r="J34" s="11"/>
@@ -2871,18 +2880,18 @@
       <x:c r="S34" s="11"/>
       <x:c r="T34" s="11"/>
       <x:c r="U34" s="11" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="V34" s="11" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="V34" s="11" t="s">
-        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B35" t="s">
         <x:v>141</x:v>
-      </x:c>
-      <x:c r="B35" t="s">
-        <x:v>142</x:v>
       </x:c>
       <x:c r="C35" t="str">
         <x:v>Cameras</x:v>
@@ -2891,13 +2900,13 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E35" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="F35" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="F35" t="s">
+      <x:c r="H35" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="H35" t="s">
-        <x:v>145</x:v>
       </x:c>
       <x:c r="K35" t="s">
         <x:v>52</x:v>
@@ -2909,18 +2918,18 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U35" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="V35" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="V35" t="s">
-        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B36" t="s">
         <x:v>148</x:v>
-      </x:c>
-      <x:c r="B36" t="s">
-        <x:v>149</x:v>
       </x:c>
       <x:c r="C36" t="str">
         <x:v>Cameras</x:v>
@@ -2929,13 +2938,13 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E36" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F36" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="F36" t="s">
+      <x:c r="H36" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="H36" t="s">
-        <x:v>152</x:v>
       </x:c>
       <x:c r="K36" t="s">
         <x:v>52</x:v>
@@ -2947,33 +2956,33 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U36" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="V36" t="s">
         <x:v>153</x:v>
-      </x:c>
-      <x:c r="V36" t="s">
-        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B37" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="B37" t="s">
+      <x:c r="C37" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D37" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E37" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="C37" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D37" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E37" t="s">
+      <x:c r="F37" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="F37" t="s">
+      <x:c r="H37" t="s">
         <x:v>158</x:v>
-      </x:c>
-      <x:c r="H37" t="s">
-        <x:v>159</x:v>
       </x:c>
       <x:c r="K37" t="s">
         <x:v>52</x:v>
@@ -2985,33 +2994,33 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U37" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="V37" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="V37" t="s">
-        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B38" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C38" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D38" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E38" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="C38" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D38" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E38" t="s">
+      <x:c r="F38" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="F38" t="s">
+      <x:c r="H38" t="s">
         <x:v>158</x:v>
-      </x:c>
-      <x:c r="H38" t="s">
-        <x:v>159</x:v>
       </x:c>
       <x:c r="K38" t="s">
         <x:v>52</x:v>
@@ -3023,33 +3032,33 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U38" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="V38" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="V38" t="s">
-        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B39" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="B39" t="s">
+      <x:c r="C39" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D39" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E39" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F39" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="C39" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D39" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E39" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="F39" t="s">
+      <x:c r="H39" t="s">
         <x:v>165</x:v>
-      </x:c>
-      <x:c r="H39" t="s">
-        <x:v>166</x:v>
       </x:c>
       <x:c r="K39" t="s">
         <x:v>52</x:v>
@@ -3061,30 +3070,30 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U39" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="V39" t="s">
         <x:v>167</x:v>
-      </x:c>
-      <x:c r="V39" t="s">
-        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="B40" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="B40" t="s">
+      <x:c r="C40" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D40" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F40" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="C40" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D40" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F40" t="s">
+      <x:c r="H40" t="s">
         <x:v>171</x:v>
-      </x:c>
-      <x:c r="H40" t="s">
-        <x:v>172</x:v>
       </x:c>
       <x:c r="K40" t="s">
         <x:v>52</x:v>
@@ -3096,33 +3105,33 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U40" t="s">
-        <x:v>173</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="V40" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="s">
-        <x:v>174</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B41" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C41" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="C41" t="s">
+      <x:c r="D41" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E41" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D41" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E41" t="s">
+      <x:c r="F41" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="F41" t="s">
+      <x:c r="H41" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="H41" t="s">
-        <x:v>137</x:v>
       </x:c>
       <x:c r="K41" t="s">
         <x:v>52</x:v>
@@ -3134,33 +3143,33 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U41" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="V41" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="V41" t="s">
-        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B42" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="B42" t="s">
+      <x:c r="C42" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D42" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E42" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="C42" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D42" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E42" t="s">
+      <x:c r="F42" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="F42" t="s">
+      <x:c r="H42" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="H42" t="s">
-        <x:v>179</x:v>
       </x:c>
       <x:c r="K42" t="s">
         <x:v>52</x:v>
@@ -3172,33 +3181,33 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U42" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="V42" t="s">
         <x:v>180</x:v>
-      </x:c>
-      <x:c r="V42" t="s">
-        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B43" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C43" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D43" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E43" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="C43" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D43" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E43" t="s">
+      <x:c r="F43" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="F43" t="s">
+      <x:c r="H43" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="H43" t="s">
-        <x:v>179</x:v>
       </x:c>
       <x:c r="K43" t="s">
         <x:v>52</x:v>
@@ -3210,33 +3219,33 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U43" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="V43" t="s">
         <x:v>180</x:v>
-      </x:c>
-      <x:c r="V43" t="s">
-        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="s">
-        <x:v>183</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B44" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C44" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D44" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E44" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="C44" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D44" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E44" t="s">
+      <x:c r="F44" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="F44" t="s">
+      <x:c r="H44" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="H44" t="s">
-        <x:v>179</x:v>
       </x:c>
       <x:c r="K44" t="s">
         <x:v>52</x:v>
@@ -3248,33 +3257,33 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U44" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="V44" t="s">
         <x:v>180</x:v>
-      </x:c>
-      <x:c r="V44" t="s">
-        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B45" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="B45" t="s">
+      <x:c r="C45" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D45" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E45" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="C45" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D45" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E45" t="s">
+      <x:c r="F45" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="F45" t="s">
+      <x:c r="H45" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="H45" t="s">
-        <x:v>188</x:v>
       </x:c>
       <x:c r="K45" t="s">
         <x:v>52</x:v>
@@ -3286,33 +3295,33 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U45" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="V45" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="V45" t="s">
-        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B46" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="C46" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D46" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E46" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="C46" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D46" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E46" t="s">
+      <x:c r="F46" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="F46" t="s">
+      <x:c r="H46" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="H46" t="s">
-        <x:v>188</x:v>
       </x:c>
       <x:c r="K46" t="s">
         <x:v>52</x:v>
@@ -3324,33 +3333,33 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U46" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="V46" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="V46" t="s">
-        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B47" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="C47" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D47" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E47" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="C47" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D47" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E47" t="s">
+      <x:c r="F47" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="F47" t="s">
+      <x:c r="H47" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="H47" t="s">
-        <x:v>188</x:v>
       </x:c>
       <x:c r="K47" t="s">
         <x:v>52</x:v>
@@ -3362,33 +3371,33 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U47" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="V47" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="V47" t="s">
-        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B48" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="B48" t="s">
+      <x:c r="C48" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="C48" t="s">
+      <x:c r="D48" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E48" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="D48" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E48" t="s">
+      <x:c r="F48" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="F48" t="s">
+      <x:c r="H48" t="s">
         <x:v>197</x:v>
-      </x:c>
-      <x:c r="H48" t="s">
-        <x:v>198</x:v>
       </x:c>
       <x:c r="K48" t="s">
         <x:v>52</x:v>
@@ -3400,33 +3409,33 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U48" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="V48" t="s">
         <x:v>199</x:v>
-      </x:c>
-      <x:c r="V48" t="s">
-        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="s">
-        <x:v>201</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B49" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="C49" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="C49" t="s">
+      <x:c r="D49" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E49" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="D49" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E49" t="s">
+      <x:c r="F49" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="F49" t="s">
+      <x:c r="H49" t="s">
         <x:v>197</x:v>
-      </x:c>
-      <x:c r="H49" t="s">
-        <x:v>198</x:v>
       </x:c>
       <x:c r="K49" t="s">
         <x:v>52</x:v>
@@ -3438,10 +3447,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U49" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="V49" t="s">
         <x:v>199</x:v>
-      </x:c>
-      <x:c r="V49" t="s">
-        <x:v>200</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3461,7 +3470,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcae7c15e36b4618"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf96762f4b04493e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3485,7 +3494,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
         <x:v>30</x:v>
@@ -3497,13 +3506,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="s">
+      <x:c r="H1" s="3" t="s">
         <x:v>204</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="s">
-        <x:v>205</x:v>
       </x:c>
       <x:c r="I1" t="s">
         <x:v>47</x:v>
@@ -3514,7 +3523,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B2" s="10" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C2" s="4"/>
       <x:c r="D2" s="4"/>
@@ -3523,7 +3532,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G2" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H2" s="11"/>
       <x:c r="I2" t="s">
@@ -3535,7 +3544,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>208</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C3" s="4"/>
       <x:c r="D3" s="4"/>
@@ -3544,11 +3553,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H3" s="11"/>
       <x:c r="I3" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3556,7 +3565,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B4" s="10" t="s">
-        <x:v>209</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="D4" s="4"/>
@@ -3565,11 +3574,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G4" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H4" s="11"/>
       <x:c r="I4" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3577,7 +3586,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B5" s="10" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C5" s="4"/>
       <x:c r="D5" s="4"/>
@@ -3586,7 +3595,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H5" s="11"/>
       <x:c r="I5" t="str">
@@ -3598,7 +3607,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B6" s="10" t="s">
-        <x:v>208</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C6" s="4"/>
       <x:c r="D6" s="4"/>
@@ -3607,11 +3616,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H6" s="11"/>
       <x:c r="I6" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3619,7 +3628,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B7" s="10" t="s">
-        <x:v>209</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C7" s="4"/>
       <x:c r="D7" s="4"/>
@@ -3628,11 +3637,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H7" s="11"/>
       <x:c r="I7" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3640,7 +3649,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B8" s="10" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C8" s="4"/>
       <x:c r="D8" s="4"/>
@@ -3649,7 +3658,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H8" s="11"/>
       <x:c r="I8" t="str">
@@ -3661,7 +3670,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B9" s="10" t="s">
-        <x:v>208</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C9" s="4"/>
       <x:c r="D9" s="4"/>
@@ -3670,11 +3679,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H9" s="11"/>
       <x:c r="I9" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3682,7 +3691,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B10" s="10" t="s">
-        <x:v>209</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C10" s="4"/>
       <x:c r="D10" s="4"/>
@@ -3691,11 +3700,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H10" s="11"/>
       <x:c r="I10" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3703,7 +3712,7 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B11" s="10" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C11" s="4"/>
       <x:c r="D11" s="4"/>
@@ -3712,7 +3721,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H11" s="11"/>
       <x:c r="I11" t="str">
@@ -3724,7 +3733,7 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B12" s="10" t="s">
-        <x:v>208</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C12" s="4"/>
       <x:c r="D12" s="4"/>
@@ -3733,11 +3742,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H12" s="11"/>
       <x:c r="I12" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3745,7 +3754,7 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B13" s="10" t="s">
-        <x:v>209</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C13" s="4"/>
       <x:c r="D13" s="4"/>
@@ -3754,11 +3763,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H13" s="11"/>
       <x:c r="I13" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3772,7 +3781,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re91057a58dc84cc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93f03117bd6e4c78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3791,87 +3800,87 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="1" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="s">
+      <x:c r="C1" s="2" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>212</x:v>
-      </x:c>
       <x:c r="D1" s="3" t="s">
-        <x:v>205</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="10" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="B2" s="10" t="s">
-        <x:v>214</x:v>
-      </x:c>
       <x:c r="C2" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D2" s="4"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="B3" s="10" t="s">
-        <x:v>216</x:v>
-      </x:c>
       <x:c r="C3" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D3" s="4"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="B4" s="10" t="s">
-        <x:v>218</x:v>
-      </x:c>
       <x:c r="C4" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D4" s="4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="B5" s="10" t="s">
-        <x:v>220</x:v>
-      </x:c>
       <x:c r="C5" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D5" s="4"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B6" s="10" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="B6" s="10" t="s">
-        <x:v>222</x:v>
-      </x:c>
       <x:c r="C6" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D6" s="4"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="B7" s="10" t="s">
-        <x:v>224</x:v>
-      </x:c>
       <x:c r="C7" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D7" s="4"/>
     </x:row>
@@ -3883,7 +3892,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b5128ebdcfa4327"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R982107907aec4690"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3905,10 +3914,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="s">
         <x:v>225</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="s">
-        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -3916,115 +3925,115 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B2" s="10" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s">
         <x:v>227</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s">
-        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="B4" s="10" t="s">
+      <x:c r="C4" s="11" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="C4" s="11" t="s">
-        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B5" s="10" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="s">
         <x:v>234</x:v>
-      </x:c>
-      <x:c r="C5" s="11" t="s">
-        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B6" s="10" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B7" s="10" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="s">
         <x:v>238</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B8" s="10" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
         <x:v>240</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10" t="s">
-        <x:v>134</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B9" s="10" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="B10" s="10" t="s">
+      <x:c r="C10" s="11" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="s">
-        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="s">
-        <x:v>195</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B11" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="C11" t="s">
         <x:v>247</x:v>
-      </x:c>
-      <x:c r="C11" t="s">
-        <x:v>248</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7508f1a403a4e43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72bd6fef27e9462c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/templates/NFC_Inventory_Import_Template.xlsx
+++ b/data/templates/NFC_Inventory_Import_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R07fea3f966bf445e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R4035cf9c9ed2443b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="R36221e72967543d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="R1f1ec372e0984d85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R50412a6762a143ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rd1c2b1c46df4453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Ra7d675b8b89a4211"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="R0d76ad2cdbd541e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="Rf79136a8e59846f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R559ce88da8e348a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -29,9 +29,6 @@
     <x:t xml:space="preserve">Source</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Equipment and member details were derived from the lab-supplied inventory and purchase-list workbooks.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Required Equipment fields</x:t>
   </x:si>
   <x:si>
@@ -629,31 +626,22 @@
     <x:t xml:space="preserve">notes</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Robot</x:t>
+    <x:t xml:space="preserve">username</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">display_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">active</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">n.salomons</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nicole</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Yes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Charger</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">USB Cable</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">username</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">display_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">active</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">n.salomons</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Nicole</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">e.akinrintoyo23</x:t>
@@ -955,8 +943,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentTable" displayName="EquipmentTable" ref="A1:V49" totalsRowShown="0">
-  <x:autoFilter ref="A1:V49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentTable" displayName="EquipmentTable" ref="A1:V79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:V79"/>
   <x:tableColumns count="22">
     <x:tableColumn id="1" name="asset_code"/>
     <x:tableColumn id="2" name="equipment_name"/>
@@ -986,8 +974,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="BundleContentsTable" displayName="BundleContentsTable" ref="A1:I4" totalsRowShown="0">
-  <x:autoFilter ref="A1:I4"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="BundleContentsTable" displayName="BundleContentsTable" ref="A1:I22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:I22"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="asset_code"/>
     <x:tableColumn id="2" name="component_name"/>
@@ -1017,8 +1005,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="CategoriesTable" displayName="CategoriesTable" ref="A1:C11" totalsRowShown="0">
-  <x:autoFilter ref="A1:C11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="CategoriesTable" displayName="CategoriesTable" ref="A1:C14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:C14"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="category"/>
     <x:tableColumn id="2" name="asset_code_prefix"/>
@@ -1271,7 +1259,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="6" t="str">
-        <x:v>48 unique equipment units are included. Duplicate source rows were consolidated and one asset code is used for each physical unit or complete bundle.</x:v>
+        <x:v>78 unique equipment units are included. One asset code is used for each physical unit or complete bundle.</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="D4" s="4"/>
@@ -1284,8 +1272,8 @@
       <x:c r="A5" s="16" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>5</x:v>
+      <x:c r="B5" s="6" t="str">
+        <x:v>Equipment and member details were derived from the lab-supplied inventory, purchase-list workbooks and subsequent physical-count updates.</x:v>
       </x:c>
       <x:c r="C5" s="4"/>
       <x:c r="D5" s="4"/>
@@ -1306,10 +1294,10 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="16" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="s">
         <x:v>6</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="s">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="C7" s="4"/>
       <x:c r="D7" s="4"/>
@@ -1320,10 +1308,10 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="B8" s="6" t="s">
-        <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="4"/>
       <x:c r="D8" s="4"/>
@@ -1334,10 +1322,10 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="16" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="s">
-        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="4"/>
       <x:c r="D9" s="4"/>
@@ -1348,10 +1336,10 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="16" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="B10" s="6" t="s">
-        <x:v>13</x:v>
       </x:c>
       <x:c r="C10" s="4"/>
       <x:c r="D10" s="4"/>
@@ -1362,10 +1350,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="16" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="B11" s="6" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="4"/>
       <x:c r="D11" s="4"/>
@@ -1376,10 +1364,10 @@
     </x:row>
     <x:row r="12" ht="25">
       <x:c r="A12" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="B12" s="6" t="s">
-        <x:v>17</x:v>
       </x:c>
       <x:c r="C12" s="4"/>
       <x:c r="D12" s="4"/>
@@ -1390,10 +1378,10 @@
     </x:row>
     <x:row r="13" ht="37.5">
       <x:c r="A13" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="B13" s="6" t="s">
-        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="4"/>
       <x:c r="D13" s="4"/>
@@ -1404,10 +1392,10 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="B14" s="6" t="s">
-        <x:v>21</x:v>
       </x:c>
       <x:c r="C14" s="4"/>
       <x:c r="D14" s="4"/>
@@ -1418,10 +1406,10 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="B15" s="6" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="C15" s="4"/>
       <x:c r="D15" s="4"/>
@@ -1432,10 +1420,10 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="18" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B16" s="8" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="B16" s="8" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="C16" s="4"/>
       <x:c r="D16" s="4"/>
@@ -1472,84 +1460,84 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="s">
+      <x:c r="C1" s="2" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="s">
+      <x:c r="D1" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
+      <x:c r="E1" s="2" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="s">
+      <x:c r="F1" s="2" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="s">
+      <x:c r="G1" s="2" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="s">
+      <x:c r="H1" s="2" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
+      <x:c r="I1" s="2" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="s">
+      <x:c r="J1" s="2" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="s">
+      <x:c r="K1" s="2" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="s">
+      <x:c r="L1" s="2" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="L1" s="2" t="s">
+      <x:c r="M1" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="M1" s="2" t="s">
+      <x:c r="N1" s="2" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="N1" s="2" t="s">
+      <x:c r="O1" s="2" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="O1" s="2" t="s">
+      <x:c r="P1" s="2" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="P1" s="2" t="s">
+      <x:c r="Q1" s="2" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="Q1" s="2" t="s">
+      <x:c r="R1" s="2" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="R1" s="2" t="s">
+      <x:c r="S1" s="2" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="S1" s="2" t="s">
+      <x:c r="T1" s="2" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="T1" s="2" t="s">
+      <x:c r="U1" s="2" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="U1" s="2" t="s">
+      <x:c r="V1" s="3" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="V1" s="3" t="s">
-        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="25">
       <x:c r="A2" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B2" s="10" t="s">
+      <x:c r="C2" s="10" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C2" s="10" t="s">
+      <x:c r="D2" s="10" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="D2" s="10" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="E2" s="4"/>
       <x:c r="F2" s="4"/>
@@ -1558,12 +1546,12 @@
       <x:c r="I2" s="11"/>
       <x:c r="J2" s="11"/>
       <x:c r="K2" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L2" s="13"/>
       <x:c r="M2" s="14"/>
       <x:c r="N2" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O2" s="11"/>
       <x:c r="P2" s="11"/>
@@ -1573,21 +1561,21 @@
       <x:c r="T2" s="11"/>
       <x:c r="U2" s="11"/>
       <x:c r="V2" s="11" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="25">
       <x:c r="A3" s="9" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C3" s="10" t="s">
+      <x:c r="D3" s="10" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="D3" s="10" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="E3" s="4"/>
       <x:c r="F3" s="4"/>
@@ -1596,12 +1584,12 @@
       <x:c r="I3" s="11"/>
       <x:c r="J3" s="11"/>
       <x:c r="K3" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L3" s="13"/>
       <x:c r="M3" s="14"/>
       <x:c r="N3" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O3" s="11"/>
       <x:c r="P3" s="11"/>
@@ -1611,41 +1599,41 @@
       <x:c r="T3" s="11"/>
       <x:c r="U3" s="11"/>
       <x:c r="V3" s="11" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="37.5">
       <x:c r="A4" s="9" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B4" s="10" t="s">
+      <x:c r="C4" s="10" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C4" s="10" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D4" s="10" t="s">
+      <x:c r="E4" s="4" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E4" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="F4" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="4"/>
       <x:c r="H4" s="11"/>
       <x:c r="I4" s="11"/>
       <x:c r="J4" s="11"/>
       <x:c r="K4" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L4" s="13"/>
       <x:c r="M4" s="14">
         <x:v>439.93</x:v>
       </x:c>
       <x:c r="N4" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O4" s="11"/>
       <x:c r="P4" s="11"/>
@@ -1654,44 +1642,44 @@
       <x:c r="S4" s="11"/>
       <x:c r="T4" s="11"/>
       <x:c r="U4" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="V4" s="11" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="V4" s="11" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="37.5">
       <x:c r="A5" s="9" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B5" s="10" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="C5" s="10" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D5" s="10" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E5" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="F5" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G5" s="4"/>
       <x:c r="H5" s="11"/>
       <x:c r="I5" s="11"/>
       <x:c r="J5" s="11"/>
       <x:c r="K5" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L5" s="13"/>
       <x:c r="M5" s="14">
         <x:v>302.16000000000003</x:v>
       </x:c>
       <x:c r="N5" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O5" s="11"/>
       <x:c r="P5" s="11"/>
@@ -1700,42 +1688,44 @@
       <x:c r="S5" s="11"/>
       <x:c r="T5" s="11"/>
       <x:c r="U5" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="V5" s="11" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="V5" s="11" t="s">
-        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="37.5">
       <x:c r="A6" s="9" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B6" s="10" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B6" s="10" t="str">
+        <x:v>Reachy Mini Wireless</x:v>
       </x:c>
       <x:c r="C6" s="10" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D6" s="10" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E6" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F6" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E6" s="4" t="str">
+        <x:v>Pollen Robotics</x:v>
+      </x:c>
+      <x:c r="F6" s="4" t="str">
+        <x:v>Reachy Mini Wireless</x:v>
       </x:c>
       <x:c r="G6" s="4"/>
-      <x:c r="H6" s="11"/>
+      <x:c r="H6" s="11" t="str">
+        <x:v>Wireless Reachy Mini robot bundle</x:v>
+      </x:c>
       <x:c r="I6" s="11"/>
       <x:c r="J6" s="11"/>
       <x:c r="K6" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L6" s="13"/>
       <x:c r="M6" s="14"/>
       <x:c r="N6" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O6" s="11"/>
       <x:c r="P6" s="11"/>
@@ -1745,39 +1735,39 @@
       <x:c r="T6" s="11"/>
       <x:c r="U6" s="11"/>
       <x:c r="V6" s="11" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-lite.png</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="37.5">
       <x:c r="A7" s="9" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B7" s="10" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C7" s="10" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D7" s="10" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E7" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="F7" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G7" s="4"/>
       <x:c r="H7" s="11"/>
       <x:c r="I7" s="11"/>
       <x:c r="J7" s="11"/>
       <x:c r="K7" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L7" s="13"/>
       <x:c r="M7" s="14"/>
       <x:c r="N7" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O7" s="11"/>
       <x:c r="P7" s="11"/>
@@ -1787,21 +1777,21 @@
       <x:c r="T7" s="11"/>
       <x:c r="U7" s="11"/>
       <x:c r="V7" s="11" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="37.5">
       <x:c r="A8" s="9" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
         <x:v>Lenovo Tab M10 (3rd Gen)</x:v>
       </x:c>
       <x:c r="C8" s="10" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D8" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
         <x:v>Lenovo</x:v>
@@ -1816,12 +1806,12 @@
       <x:c r="I8" s="11"/>
       <x:c r="J8" s="11"/>
       <x:c r="K8" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L8" s="13"/>
       <x:c r="M8" s="14"/>
       <x:c r="N8" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O8" s="11"/>
       <x:c r="P8" s="11"/>
@@ -1831,21 +1821,21 @@
       <x:c r="T8" s="11"/>
       <x:c r="U8" s="11"/>
       <x:c r="V8" s="11" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="37.5">
       <x:c r="A9" s="9" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
         <x:v>Lenovo Tab M10 (3rd Gen)</x:v>
       </x:c>
       <x:c r="C9" s="10" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D9" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
         <x:v>Lenovo</x:v>
@@ -1860,12 +1850,12 @@
       <x:c r="I9" s="11"/>
       <x:c r="J9" s="11"/>
       <x:c r="K9" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L9" s="13"/>
       <x:c r="M9" s="14"/>
       <x:c r="N9" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O9" s="11"/>
       <x:c r="P9" s="11"/>
@@ -1875,21 +1865,21 @@
       <x:c r="T9" s="11"/>
       <x:c r="U9" s="11"/>
       <x:c r="V9" s="11" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="37.5">
       <x:c r="A10" s="9" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B10" s="10" t="s">
+      <x:c r="C10" s="10" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C10" s="10" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="D10" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E10" s="4"/>
       <x:c r="F10" s="4"/>
@@ -1898,12 +1888,12 @@
       <x:c r="I10" s="11"/>
       <x:c r="J10" s="11"/>
       <x:c r="K10" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L10" s="13"/>
       <x:c r="M10" s="14"/>
       <x:c r="N10" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O10" s="11"/>
       <x:c r="P10" s="11"/>
@@ -1913,21 +1903,21 @@
       <x:c r="T10" s="11"/>
       <x:c r="U10" s="11"/>
       <x:c r="V10" s="11" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="37.5">
       <x:c r="A11" s="9" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B11" s="10" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C11" s="10" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="D11" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E11" s="4"/>
       <x:c r="F11" s="4"/>
@@ -1936,12 +1926,12 @@
       <x:c r="I11" s="11"/>
       <x:c r="J11" s="11"/>
       <x:c r="K11" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L11" s="13"/>
       <x:c r="M11" s="14"/>
       <x:c r="N11" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O11" s="11"/>
       <x:c r="P11" s="11"/>
@@ -1951,21 +1941,21 @@
       <x:c r="T11" s="11"/>
       <x:c r="U11" s="11"/>
       <x:c r="V11" s="11" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="37.5">
       <x:c r="A12" s="9" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="B12" s="10" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
         <x:v>Cameras</x:v>
       </x:c>
       <x:c r="D12" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E12" s="4"/>
       <x:c r="F12" s="4"/>
@@ -1974,12 +1964,12 @@
       <x:c r="I12" s="11"/>
       <x:c r="J12" s="11"/>
       <x:c r="K12" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L12" s="13"/>
       <x:c r="M12" s="14"/>
       <x:c r="N12" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O12" s="11"/>
       <x:c r="P12" s="11"/>
@@ -1989,21 +1979,21 @@
       <x:c r="T12" s="11"/>
       <x:c r="U12" s="11"/>
       <x:c r="V12" s="11" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="37.5">
       <x:c r="A13" s="9" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B13" s="10" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
         <x:v>Cameras</x:v>
       </x:c>
       <x:c r="D13" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
@@ -2012,12 +2002,12 @@
       <x:c r="I13" s="11"/>
       <x:c r="J13" s="11"/>
       <x:c r="K13" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L13" s="13"/>
       <x:c r="M13" s="14"/>
       <x:c r="N13" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O13" s="11"/>
       <x:c r="P13" s="11"/>
@@ -2027,43 +2017,43 @@
       <x:c r="T13" s="11"/>
       <x:c r="U13" s="11"/>
       <x:c r="V13" s="11" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="37.5">
       <x:c r="A14" s="9" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="B14" s="10" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
         <x:v>Cameras</x:v>
       </x:c>
       <x:c r="D14" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E14" s="4" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="F14" s="4" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="G14" s="4"/>
       <x:c r="H14" s="11" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="I14" s="11"/>
       <x:c r="J14" s="11"/>
       <x:c r="K14" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L14" s="13"/>
       <x:c r="M14" s="14">
         <x:v>43.81</x:v>
       </x:c>
       <x:c r="N14" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O14" s="11"/>
       <x:c r="P14" s="11"/>
@@ -2072,46 +2062,46 @@
       <x:c r="S14" s="11"/>
       <x:c r="T14" s="11"/>
       <x:c r="U14" s="11" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="V14" s="11" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="V14" s="11" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="37.5">
       <x:c r="A15" s="9" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B15" s="10" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
         <x:v>Cameras</x:v>
       </x:c>
       <x:c r="D15" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F15" s="4" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="F15" s="4" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="G15" s="4"/>
       <x:c r="H15" s="11" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="I15" s="11"/>
       <x:c r="J15" s="11"/>
       <x:c r="K15" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L15" s="13"/>
       <x:c r="M15" s="14">
         <x:v>43.81</x:v>
       </x:c>
       <x:c r="N15" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O15" s="11"/>
       <x:c r="P15" s="11"/>
@@ -2120,24 +2110,24 @@
       <x:c r="S15" s="11"/>
       <x:c r="T15" s="11"/>
       <x:c r="U15" s="11" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="V15" s="11" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="V15" s="11" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="37.5">
       <x:c r="A16" s="9" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B16" s="10" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="C16" s="10" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D16" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E16" s="4"/>
       <x:c r="F16" s="4"/>
@@ -2146,12 +2136,12 @@
       <x:c r="I16" s="11"/>
       <x:c r="J16" s="11"/>
       <x:c r="K16" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L16" s="13"/>
       <x:c r="M16" s="14"/>
       <x:c r="N16" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O16" s="11"/>
       <x:c r="P16" s="11"/>
@@ -2161,21 +2151,21 @@
       <x:c r="T16" s="11"/>
       <x:c r="U16" s="11"/>
       <x:c r="V16" s="11" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="37.5">
       <x:c r="A17" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B17" s="10" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C17" s="10" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D17" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E17" s="4"/>
       <x:c r="F17" s="4"/>
@@ -2184,12 +2174,12 @@
       <x:c r="I17" s="11"/>
       <x:c r="J17" s="11"/>
       <x:c r="K17" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L17" s="13"/>
       <x:c r="M17" s="14"/>
       <x:c r="N17" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O17" s="11"/>
       <x:c r="P17" s="11"/>
@@ -2199,21 +2189,21 @@
       <x:c r="T17" s="11"/>
       <x:c r="U17" s="11"/>
       <x:c r="V17" s="11" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="37.5">
       <x:c r="A18" s="9" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B18" s="10" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C18" s="10" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D18" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E18" s="4"/>
       <x:c r="F18" s="4"/>
@@ -2222,12 +2212,12 @@
       <x:c r="I18" s="11"/>
       <x:c r="J18" s="11"/>
       <x:c r="K18" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L18" s="13"/>
       <x:c r="M18" s="14"/>
       <x:c r="N18" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O18" s="11"/>
       <x:c r="P18" s="11"/>
@@ -2237,21 +2227,21 @@
       <x:c r="T18" s="11"/>
       <x:c r="U18" s="11"/>
       <x:c r="V18" s="11" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="37.5">
       <x:c r="A19" s="9" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B19" s="10" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="C19" s="10" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D19" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E19" s="4"/>
       <x:c r="F19" s="4"/>
@@ -2260,12 +2250,12 @@
       <x:c r="I19" s="11"/>
       <x:c r="J19" s="11"/>
       <x:c r="K19" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L19" s="13"/>
       <x:c r="M19" s="14"/>
       <x:c r="N19" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O19" s="11"/>
       <x:c r="P19" s="11"/>
@@ -2275,21 +2265,21 @@
       <x:c r="T19" s="11"/>
       <x:c r="U19" s="11"/>
       <x:c r="V19" s="11" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="37.5">
       <x:c r="A20" s="9" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B20" s="10" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C20" s="10" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D20" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E20" s="4"/>
       <x:c r="F20" s="4"/>
@@ -2298,12 +2288,12 @@
       <x:c r="I20" s="11"/>
       <x:c r="J20" s="11"/>
       <x:c r="K20" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L20" s="13"/>
       <x:c r="M20" s="14"/>
       <x:c r="N20" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O20" s="11"/>
       <x:c r="P20" s="11"/>
@@ -2313,21 +2303,21 @@
       <x:c r="T20" s="11"/>
       <x:c r="U20" s="11"/>
       <x:c r="V20" s="11" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="37.5">
       <x:c r="A21" s="9" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B21" s="10" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B21" s="10" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="C21" s="10" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D21" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E21" s="4"/>
       <x:c r="F21" s="4"/>
@@ -2336,12 +2326,12 @@
       <x:c r="I21" s="11"/>
       <x:c r="J21" s="11"/>
       <x:c r="K21" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L21" s="13"/>
       <x:c r="M21" s="14"/>
       <x:c r="N21" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O21" s="11"/>
       <x:c r="P21" s="11"/>
@@ -2351,21 +2341,21 @@
       <x:c r="T21" s="11"/>
       <x:c r="U21" s="11"/>
       <x:c r="V21" s="11" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="37.5">
       <x:c r="A22" s="9" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B22" s="10" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C22" s="10" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D22" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E22" s="4"/>
       <x:c r="F22" s="4"/>
@@ -2374,12 +2364,12 @@
       <x:c r="I22" s="11"/>
       <x:c r="J22" s="11"/>
       <x:c r="K22" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L22" s="13"/>
       <x:c r="M22" s="14"/>
       <x:c r="N22" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O22" s="11"/>
       <x:c r="P22" s="11"/>
@@ -2389,21 +2379,21 @@
       <x:c r="T22" s="11"/>
       <x:c r="U22" s="11"/>
       <x:c r="V22" s="11" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="37.5">
       <x:c r="A23" s="9" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B23" s="10" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B23" s="10" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="C23" s="10" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D23" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E23" s="4"/>
       <x:c r="F23" s="4"/>
@@ -2412,12 +2402,12 @@
       <x:c r="I23" s="11"/>
       <x:c r="J23" s="11"/>
       <x:c r="K23" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L23" s="13"/>
       <x:c r="M23" s="14"/>
       <x:c r="N23" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O23" s="11"/>
       <x:c r="P23" s="11"/>
@@ -2427,21 +2417,21 @@
       <x:c r="T23" s="11"/>
       <x:c r="U23" s="11"/>
       <x:c r="V23" s="11" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="37.5">
       <x:c r="A24" s="9" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B24" s="10" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C24" s="10" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D24" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E24" s="4"/>
       <x:c r="F24" s="4"/>
@@ -2450,12 +2440,12 @@
       <x:c r="I24" s="11"/>
       <x:c r="J24" s="11"/>
       <x:c r="K24" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L24" s="13"/>
       <x:c r="M24" s="14"/>
       <x:c r="N24" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O24" s="11"/>
       <x:c r="P24" s="11"/>
@@ -2465,41 +2455,41 @@
       <x:c r="T24" s="11"/>
       <x:c r="U24" s="11"/>
       <x:c r="V24" s="11" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="37.5">
       <x:c r="A25" s="9" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B25" s="10" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B25" s="10" t="s">
+      <x:c r="C25" s="10" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C25" s="10" t="s">
+      <x:c r="D25" s="10" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E25" s="4" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D25" s="10" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E25" s="4" t="s">
+      <x:c r="F25" s="4" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="F25" s="4" t="s">
-        <x:v>107</x:v>
       </x:c>
       <x:c r="G25" s="4"/>
       <x:c r="H25" s="11" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I25" s="11"/>
       <x:c r="J25" s="11"/>
       <x:c r="K25" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L25" s="13"/>
       <x:c r="M25" s="14"/>
       <x:c r="N25" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O25" s="11"/>
       <x:c r="P25" s="11"/>
@@ -2509,41 +2499,41 @@
       <x:c r="T25" s="11"/>
       <x:c r="U25" s="11"/>
       <x:c r="V25" s="11" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="37.5">
       <x:c r="A26" s="9" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B26" s="10" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C26" s="10" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C26" s="10" t="s">
+      <x:c r="D26" s="10" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E26" s="4" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D26" s="10" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E26" s="4" t="s">
+      <x:c r="F26" s="4" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="F26" s="4" t="s">
-        <x:v>107</x:v>
       </x:c>
       <x:c r="G26" s="4"/>
       <x:c r="H26" s="11" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I26" s="11"/>
       <x:c r="J26" s="11"/>
       <x:c r="K26" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L26" s="13"/>
       <x:c r="M26" s="14"/>
       <x:c r="N26" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O26" s="11"/>
       <x:c r="P26" s="11"/>
@@ -2553,41 +2543,41 @@
       <x:c r="T26" s="11"/>
       <x:c r="U26" s="11"/>
       <x:c r="V26" s="11" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="37.5">
       <x:c r="A27" s="9" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B27" s="10" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B27" s="10" t="s">
+      <x:c r="C27" s="10" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="C27" s="10" t="s">
+      <x:c r="D27" s="10" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E27" s="4" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="D27" s="10" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E27" s="4" t="s">
+      <x:c r="F27" s="4" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="F27" s="4" t="s">
-        <x:v>115</x:v>
       </x:c>
       <x:c r="G27" s="4"/>
       <x:c r="H27" s="11" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I27" s="11"/>
       <x:c r="J27" s="11"/>
       <x:c r="K27" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L27" s="13"/>
       <x:c r="M27" s="14"/>
       <x:c r="N27" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O27" s="11"/>
       <x:c r="P27" s="11"/>
@@ -2597,21 +2587,21 @@
       <x:c r="T27" s="11"/>
       <x:c r="U27" s="11"/>
       <x:c r="V27" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="37.5">
       <x:c r="A28" s="9" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B28" s="10" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="B28" s="10" t="s">
-        <x:v>119</x:v>
-      </x:c>
       <x:c r="C28" s="10" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D28" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E28" s="4"/>
       <x:c r="F28" s="4"/>
@@ -2620,12 +2610,12 @@
       <x:c r="I28" s="11"/>
       <x:c r="J28" s="11"/>
       <x:c r="K28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L28" s="13"/>
       <x:c r="M28" s="14"/>
       <x:c r="N28" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O28" s="11"/>
       <x:c r="P28" s="11"/>
@@ -2635,21 +2625,21 @@
       <x:c r="T28" s="11"/>
       <x:c r="U28" s="11"/>
       <x:c r="V28" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="37.5">
       <x:c r="A29" s="9" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B29" s="10" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B29" s="10" t="s">
+      <x:c r="C29" s="10" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="C29" s="10" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="D29" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E29" s="4"/>
       <x:c r="F29" s="4"/>
@@ -2658,12 +2648,12 @@
       <x:c r="I29" s="11"/>
       <x:c r="J29" s="11"/>
       <x:c r="K29" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L29" s="13"/>
       <x:c r="M29" s="14"/>
       <x:c r="N29" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O29" s="11"/>
       <x:c r="P29" s="11"/>
@@ -2673,21 +2663,21 @@
       <x:c r="T29" s="11"/>
       <x:c r="U29" s="11"/>
       <x:c r="V29" s="11" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="37.5">
       <x:c r="A30" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B30" s="10" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="C30" s="10" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="D30" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E30" s="4"/>
       <x:c r="F30" s="4"/>
@@ -2696,12 +2686,12 @@
       <x:c r="I30" s="11"/>
       <x:c r="J30" s="11"/>
       <x:c r="K30" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L30" s="13"/>
       <x:c r="M30" s="14"/>
       <x:c r="N30" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O30" s="11"/>
       <x:c r="P30" s="11"/>
@@ -2711,21 +2701,21 @@
       <x:c r="T30" s="11"/>
       <x:c r="U30" s="11"/>
       <x:c r="V30" s="11" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="37.5">
       <x:c r="A31" s="9" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B31" s="10" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="B31" s="10" t="s">
-        <x:v>126</x:v>
-      </x:c>
       <x:c r="C31" s="10" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D31" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E31" s="4"/>
       <x:c r="F31" s="4"/>
@@ -2734,12 +2724,12 @@
       <x:c r="I31" s="11"/>
       <x:c r="J31" s="11"/>
       <x:c r="K31" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L31" s="13"/>
       <x:c r="M31" s="14"/>
       <x:c r="N31" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O31" s="11"/>
       <x:c r="P31" s="11"/>
@@ -2749,21 +2739,21 @@
       <x:c r="T31" s="11"/>
       <x:c r="U31" s="11"/>
       <x:c r="V31" s="11" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="37.5">
       <x:c r="A32" s="9" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B32" s="10" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B32" s="10" t="s">
-        <x:v>129</x:v>
-      </x:c>
       <x:c r="C32" s="10" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D32" s="10" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E32" s="4"/>
       <x:c r="F32" s="4"/>
@@ -2772,12 +2762,12 @@
       <x:c r="I32" s="11"/>
       <x:c r="J32" s="11"/>
       <x:c r="K32" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L32" s="13"/>
       <x:c r="M32" s="14"/>
       <x:c r="N32" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O32" s="11"/>
       <x:c r="P32" s="11"/>
@@ -2787,43 +2777,43 @@
       <x:c r="T32" s="11"/>
       <x:c r="U32" s="11"/>
       <x:c r="V32" s="11" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="87.5">
       <x:c r="A33" s="9" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B33" s="10" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="B33" s="10" t="s">
+      <x:c r="C33" s="10" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="C33" s="10" t="s">
+      <x:c r="D33" s="10" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="D33" s="10" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E33" s="4" t="s">
+      <x:c r="F33" s="4" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="F33" s="4" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="G33" s="4"/>
       <x:c r="H33" s="11" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="I33" s="11"/>
       <x:c r="J33" s="11"/>
       <x:c r="K33" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L33" s="13"/>
       <x:c r="M33" s="14">
         <x:v>12.84</x:v>
       </x:c>
       <x:c r="N33" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O33" s="11"/>
       <x:c r="P33" s="11"/>
@@ -2832,46 +2822,46 @@
       <x:c r="S33" s="11"/>
       <x:c r="T33" s="11"/>
       <x:c r="U33" s="11" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="V33" s="11" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="V33" s="11" t="s">
-        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="87.5">
       <x:c r="A34" s="9" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B34" s="10" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C34" s="10" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="C34" s="10" t="s">
+      <x:c r="D34" s="10" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="D34" s="10" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E34" s="4" t="s">
+      <x:c r="F34" s="4" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="F34" s="4" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="G34" s="4"/>
       <x:c r="H34" s="11" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="I34" s="11"/>
       <x:c r="J34" s="11"/>
       <x:c r="K34" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L34" s="13"/>
       <x:c r="M34" s="14">
         <x:v>12.84</x:v>
       </x:c>
       <x:c r="N34" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O34" s="11"/>
       <x:c r="P34" s="11"/>
@@ -2880,581 +2870,1887 @@
       <x:c r="S34" s="11"/>
       <x:c r="T34" s="11"/>
       <x:c r="U34" s="11" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="V34" s="11" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="V34" s="11" t="s">
-        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B35" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="B35" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="C35" t="str">
         <x:v>Cameras</x:v>
       </x:c>
       <x:c r="D35" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E35" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F35" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H35" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="K35" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E35" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="F35" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="H35" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="K35" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M35">
         <x:v>49.77</x:v>
       </x:c>
       <x:c r="N35" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U35" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="V35" t="s">
         <x:v>145</x:v>
-      </x:c>
-      <x:c r="V35" t="s">
-        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B36" t="s">
         <x:v>147</x:v>
-      </x:c>
-      <x:c r="B36" t="s">
-        <x:v>148</x:v>
       </x:c>
       <x:c r="C36" t="str">
         <x:v>Cameras</x:v>
       </x:c>
       <x:c r="D36" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E36" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F36" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H36" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K36" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E36" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F36" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H36" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="K36" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M36">
         <x:v>39.81</x:v>
       </x:c>
       <x:c r="N36" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U36" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="V36" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="V36" t="s">
-        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B37" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="B37" t="s">
+      <x:c r="C37" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D37" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E37" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="C37" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D37" t="s">
+      <x:c r="F37" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H37" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="K37" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E37" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F37" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="H37" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="K37" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M37">
         <x:v>297.7</x:v>
       </x:c>
       <x:c r="N37" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U37" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="V37" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="V37" t="s">
-        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B38" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C38" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D38" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E38" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="C38" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D38" t="s">
+      <x:c r="F38" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H38" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="K38" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E38" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F38" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="H38" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="K38" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M38">
         <x:v>297.7</x:v>
       </x:c>
       <x:c r="N38" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U38" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="V38" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="V38" t="s">
-        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B39" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="B39" t="s">
+      <x:c r="C39" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D39" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E39" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="F39" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C39" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D39" t="s">
+      <x:c r="H39" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="K39" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E39" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F39" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="H39" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="K39" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M39">
         <x:v>146.35</x:v>
       </x:c>
       <x:c r="N39" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U39" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="V39" t="s">
         <x:v>166</x:v>
-      </x:c>
-      <x:c r="V39" t="s">
-        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B40" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="B40" t="s">
+      <x:c r="C40" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D40" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F40" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="C40" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D40" t="s">
+      <x:c r="H40" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="K40" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="F40" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H40" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="K40" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M40">
         <x:v>7.95</x:v>
       </x:c>
       <x:c r="N40" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U40" t="s">
-        <x:v>172</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="V40" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="s">
-        <x:v>173</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B41" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C41" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="C41" t="s">
+      <x:c r="D41" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E41" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="D41" t="s">
+      <x:c r="F41" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H41" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="K41" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E41" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="F41" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H41" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="K41" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M41">
         <x:v>12.84</x:v>
       </x:c>
       <x:c r="N41" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U41" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="V41" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="V41" t="s">
-        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B42" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="B42" t="s">
+      <x:c r="C42" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D42" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E42" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="C42" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D42" t="s">
+      <x:c r="F42" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="H42" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="K42" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E42" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F42" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="H42" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="K42" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M42">
         <x:v>75.650000000000006</x:v>
       </x:c>
       <x:c r="N42" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U42" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="V42" t="s">
         <x:v>179</x:v>
-      </x:c>
-      <x:c r="V42" t="s">
-        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B43" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="C43" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D43" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E43" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="C43" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D43" t="s">
+      <x:c r="F43" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="H43" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="K43" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E43" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F43" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="H43" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="K43" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M43">
         <x:v>75.650000000000006</x:v>
       </x:c>
       <x:c r="N43" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U43" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="V43" t="s">
         <x:v>179</x:v>
-      </x:c>
-      <x:c r="V43" t="s">
-        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B44" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="C44" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D44" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E44" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="C44" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D44" t="s">
+      <x:c r="F44" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="H44" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="K44" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E44" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F44" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="H44" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="K44" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M44">
         <x:v>75.650000000000006</x:v>
       </x:c>
       <x:c r="N44" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U44" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="V44" t="s">
         <x:v>179</x:v>
-      </x:c>
-      <x:c r="V44" t="s">
-        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="B45" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="B45" t="s">
+      <x:c r="C45" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D45" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E45" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C45" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D45" t="s">
+      <x:c r="F45" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H45" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="K45" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E45" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="F45" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="H45" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="K45" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M45">
         <x:v>21.88</x:v>
       </x:c>
       <x:c r="N45" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U45" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="V45" t="s">
         <x:v>188</x:v>
-      </x:c>
-      <x:c r="V45" t="s">
-        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B46" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="C46" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D46" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E46" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C46" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D46" t="s">
+      <x:c r="F46" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H46" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="K46" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E46" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="F46" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="H46" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="K46" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M46">
         <x:v>21.88</x:v>
       </x:c>
       <x:c r="N46" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U46" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="V46" t="s">
         <x:v>188</x:v>
-      </x:c>
-      <x:c r="V46" t="s">
-        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B47" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="C47" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D47" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E47" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C47" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D47" t="s">
+      <x:c r="F47" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H47" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="K47" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E47" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="F47" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="H47" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="K47" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M47">
         <x:v>21.88</x:v>
       </x:c>
       <x:c r="N47" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U47" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="V47" t="s">
         <x:v>188</x:v>
-      </x:c>
-      <x:c r="V47" t="s">
-        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B48" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="B48" t="s">
+      <x:c r="C48" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="C48" t="s">
+      <x:c r="D48" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E48" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="D48" t="s">
+      <x:c r="F48" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H48" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="K48" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E48" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F48" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H48" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="K48" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M48">
         <x:v>606.92999999999995</x:v>
       </x:c>
       <x:c r="N48" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U48" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="V48" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="V48" t="s">
-        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B49" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C49" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="C49" t="s">
+      <x:c r="D49" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E49" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="D49" t="s">
+      <x:c r="F49" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H49" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="K49" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E49" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F49" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H49" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="K49" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="M49">
         <x:v>606.92999999999995</x:v>
       </x:c>
       <x:c r="N49" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U49" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="V49" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="V49" t="s">
-        <x:v>199</x:v>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>ROB-007</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>Reachy Mini Wireless</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>Robots</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
+        <x:v>Bundle</x:v>
+      </x:c>
+      <x:c r="E50" t="str">
+        <x:v>Pollen Robotics</x:v>
+      </x:c>
+      <x:c r="F50" t="str">
+        <x:v>Reachy Mini Wireless</x:v>
+      </x:c>
+      <x:c r="G50"/>
+      <x:c r="H50" t="str">
+        <x:v>Wireless Reachy Mini robot bundle</x:v>
+      </x:c>
+      <x:c r="I50"/>
+      <x:c r="J50"/>
+      <x:c r="K50" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L50"/>
+      <x:c r="M50"/>
+      <x:c r="N50" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O50"/>
+      <x:c r="P50"/>
+      <x:c r="Q50"/>
+      <x:c r="R50"/>
+      <x:c r="S50"/>
+      <x:c r="T50"/>
+      <x:c r="U50"/>
+      <x:c r="V50" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>MON-001</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>LG 27-inch Monitor</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>Monitors</x:v>
+      </x:c>
+      <x:c r="D51" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E51" t="str">
+        <x:v>LG</x:v>
+      </x:c>
+      <x:c r="F51" t="str">
+        <x:v>27MR400-B</x:v>
+      </x:c>
+      <x:c r="G51"/>
+      <x:c r="H51" t="str">
+        <x:v>27-inch IPS Full HD display, 100 Hz refresh rate and AMD FreeSync</x:v>
+      </x:c>
+      <x:c r="I51"/>
+      <x:c r="J51"/>
+      <x:c r="K51" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L51"/>
+      <x:c r="M51"/>
+      <x:c r="N51" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O51"/>
+      <x:c r="P51"/>
+      <x:c r="Q51"/>
+      <x:c r="R51" t="str">
+        <x:v>https://www.lg.com/uk/monitors/fhd-qhd/27mr400-b/</x:v>
+      </x:c>
+      <x:c r="S51"/>
+      <x:c r="T51"/>
+      <x:c r="U51"/>
+      <x:c r="V51" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>MON-002</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>LG 27-inch Monitor</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>Monitors</x:v>
+      </x:c>
+      <x:c r="D52" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E52" t="str">
+        <x:v>LG</x:v>
+      </x:c>
+      <x:c r="F52" t="str">
+        <x:v>27MR400-B</x:v>
+      </x:c>
+      <x:c r="G52"/>
+      <x:c r="H52" t="str">
+        <x:v>27-inch IPS Full HD display, 100 Hz refresh rate and AMD FreeSync</x:v>
+      </x:c>
+      <x:c r="I52"/>
+      <x:c r="J52"/>
+      <x:c r="K52" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L52"/>
+      <x:c r="M52"/>
+      <x:c r="N52" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O52"/>
+      <x:c r="P52"/>
+      <x:c r="Q52"/>
+      <x:c r="R52" t="str">
+        <x:v>https://www.lg.com/uk/monitors/fhd-qhd/27mr400-b/</x:v>
+      </x:c>
+      <x:c r="S52"/>
+      <x:c r="T52"/>
+      <x:c r="U52"/>
+      <x:c r="V52" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="str">
+        <x:v>MON-003</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>LG 27-inch Monitor</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>Monitors</x:v>
+      </x:c>
+      <x:c r="D53" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E53" t="str">
+        <x:v>LG</x:v>
+      </x:c>
+      <x:c r="F53" t="str">
+        <x:v>27MR400-B</x:v>
+      </x:c>
+      <x:c r="G53"/>
+      <x:c r="H53" t="str">
+        <x:v>27-inch IPS Full HD display, 100 Hz refresh rate and AMD FreeSync</x:v>
+      </x:c>
+      <x:c r="I53"/>
+      <x:c r="J53"/>
+      <x:c r="K53" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L53"/>
+      <x:c r="M53"/>
+      <x:c r="N53" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O53"/>
+      <x:c r="P53"/>
+      <x:c r="Q53"/>
+      <x:c r="R53" t="str">
+        <x:v>https://www.lg.com/uk/monitors/fhd-qhd/27mr400-b/</x:v>
+      </x:c>
+      <x:c r="S53"/>
+      <x:c r="T53"/>
+      <x:c r="U53"/>
+      <x:c r="V53" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str">
+        <x:v>MON-004</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>Amazon Basics Monitor</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>Monitors</x:v>
+      </x:c>
+      <x:c r="D54" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E54" t="str">
+        <x:v>Amazon Basics</x:v>
+      </x:c>
+      <x:c r="F54" t="str">
+        <x:v>C26M2020UK</x:v>
+      </x:c>
+      <x:c r="G54"/>
+      <x:c r="H54"/>
+      <x:c r="I54"/>
+      <x:c r="J54"/>
+      <x:c r="K54" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L54"/>
+      <x:c r="M54"/>
+      <x:c r="N54" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O54"/>
+      <x:c r="P54"/>
+      <x:c r="Q54"/>
+      <x:c r="R54"/>
+      <x:c r="S54"/>
+      <x:c r="T54"/>
+      <x:c r="U54"/>
+      <x:c r="V54" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str">
+        <x:v>MON-005</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>Amazon Basics Monitor</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>Monitors</x:v>
+      </x:c>
+      <x:c r="D55" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E55" t="str">
+        <x:v>Amazon Basics</x:v>
+      </x:c>
+      <x:c r="F55" t="str">
+        <x:v>C26M2020UK</x:v>
+      </x:c>
+      <x:c r="G55"/>
+      <x:c r="H55"/>
+      <x:c r="I55"/>
+      <x:c r="J55"/>
+      <x:c r="K55" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L55"/>
+      <x:c r="M55"/>
+      <x:c r="N55" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O55"/>
+      <x:c r="P55"/>
+      <x:c r="Q55"/>
+      <x:c r="R55"/>
+      <x:c r="S55"/>
+      <x:c r="T55"/>
+      <x:c r="U55"/>
+      <x:c r="V55" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str">
+        <x:v>MON-006</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>Amazon Basics Monitor</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>Monitors</x:v>
+      </x:c>
+      <x:c r="D56" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E56" t="str">
+        <x:v>Amazon Basics</x:v>
+      </x:c>
+      <x:c r="F56" t="str">
+        <x:v>C26M2020UK</x:v>
+      </x:c>
+      <x:c r="G56"/>
+      <x:c r="H56"/>
+      <x:c r="I56"/>
+      <x:c r="J56"/>
+      <x:c r="K56" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L56"/>
+      <x:c r="M56"/>
+      <x:c r="N56" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O56"/>
+      <x:c r="P56"/>
+      <x:c r="Q56"/>
+      <x:c r="R56"/>
+      <x:c r="S56"/>
+      <x:c r="T56"/>
+      <x:c r="U56"/>
+      <x:c r="V56" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="str">
+        <x:v>MON-007</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>Amazon Basics Monitor</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>Monitors</x:v>
+      </x:c>
+      <x:c r="D57" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E57" t="str">
+        <x:v>Amazon Basics</x:v>
+      </x:c>
+      <x:c r="F57" t="str">
+        <x:v>C26M2020UK</x:v>
+      </x:c>
+      <x:c r="G57"/>
+      <x:c r="H57"/>
+      <x:c r="I57"/>
+      <x:c r="J57"/>
+      <x:c r="K57" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L57"/>
+      <x:c r="M57"/>
+      <x:c r="N57" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O57"/>
+      <x:c r="P57"/>
+      <x:c r="Q57"/>
+      <x:c r="R57"/>
+      <x:c r="S57"/>
+      <x:c r="T57"/>
+      <x:c r="U57"/>
+      <x:c r="V57" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str">
+        <x:v>NET-001</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>TP-Link AX1500 Wi-Fi 6 Router</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>Networking</x:v>
+      </x:c>
+      <x:c r="D58" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E58" t="str">
+        <x:v>TP-Link</x:v>
+      </x:c>
+      <x:c r="F58" t="str">
+        <x:v>Archer AX1500</x:v>
+      </x:c>
+      <x:c r="G58"/>
+      <x:c r="H58" t="str">
+        <x:v>Dual-band Wi-Fi 6 router with speeds up to 1.5 Gbps</x:v>
+      </x:c>
+      <x:c r="I58"/>
+      <x:c r="J58"/>
+      <x:c r="K58" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L58"/>
+      <x:c r="M58"/>
+      <x:c r="N58" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O58"/>
+      <x:c r="P58"/>
+      <x:c r="Q58"/>
+      <x:c r="R58" t="str">
+        <x:v>https://www.tp-link.com/uk/home-networking/wifi-router/archer-ax1500/v1/</x:v>
+      </x:c>
+      <x:c r="S58"/>
+      <x:c r="T58"/>
+      <x:c r="U58"/>
+      <x:c r="V58" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str">
+        <x:v>NET-002</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>TP-Link AX1500 Wi-Fi 6 Router</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>Networking</x:v>
+      </x:c>
+      <x:c r="D59" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E59" t="str">
+        <x:v>TP-Link</x:v>
+      </x:c>
+      <x:c r="F59" t="str">
+        <x:v>Archer AX1500</x:v>
+      </x:c>
+      <x:c r="G59"/>
+      <x:c r="H59" t="str">
+        <x:v>Dual-band Wi-Fi 6 router with speeds up to 1.5 Gbps</x:v>
+      </x:c>
+      <x:c r="I59"/>
+      <x:c r="J59"/>
+      <x:c r="K59" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L59"/>
+      <x:c r="M59"/>
+      <x:c r="N59" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O59"/>
+      <x:c r="P59"/>
+      <x:c r="Q59"/>
+      <x:c r="R59" t="str">
+        <x:v>https://www.tp-link.com/uk/home-networking/wifi-router/archer-ax1500/v1/</x:v>
+      </x:c>
+      <x:c r="S59"/>
+      <x:c r="T59"/>
+      <x:c r="U59"/>
+      <x:c r="V59" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="str">
+        <x:v>NET-003</x:v>
+      </x:c>
+      <x:c r="B60" t="str">
+        <x:v>TP-Link AX1500 Wi-Fi 6 Router</x:v>
+      </x:c>
+      <x:c r="C60" t="str">
+        <x:v>Networking</x:v>
+      </x:c>
+      <x:c r="D60" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E60" t="str">
+        <x:v>TP-Link</x:v>
+      </x:c>
+      <x:c r="F60" t="str">
+        <x:v>Archer AX1500</x:v>
+      </x:c>
+      <x:c r="G60"/>
+      <x:c r="H60" t="str">
+        <x:v>Dual-band Wi-Fi 6 router with speeds up to 1.5 Gbps</x:v>
+      </x:c>
+      <x:c r="I60"/>
+      <x:c r="J60"/>
+      <x:c r="K60" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L60"/>
+      <x:c r="M60"/>
+      <x:c r="N60" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O60"/>
+      <x:c r="P60"/>
+      <x:c r="Q60"/>
+      <x:c r="R60" t="str">
+        <x:v>https://www.tp-link.com/uk/home-networking/wifi-router/archer-ax1500/v1/</x:v>
+      </x:c>
+      <x:c r="S60"/>
+      <x:c r="T60"/>
+      <x:c r="U60"/>
+      <x:c r="V60" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str">
+        <x:v>NET-004</x:v>
+      </x:c>
+      <x:c r="B61" t="str">
+        <x:v>TP-Link Wireless N Router</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>Networking</x:v>
+      </x:c>
+      <x:c r="D61" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E61" t="str">
+        <x:v>TP-Link</x:v>
+      </x:c>
+      <x:c r="F61" t="str">
+        <x:v>TL-WR841N</x:v>
+      </x:c>
+      <x:c r="G61"/>
+      <x:c r="H61" t="str">
+        <x:v>300 Mbps 2.4 GHz Wireless N router</x:v>
+      </x:c>
+      <x:c r="I61"/>
+      <x:c r="J61"/>
+      <x:c r="K61" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L61"/>
+      <x:c r="M61"/>
+      <x:c r="N61" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O61"/>
+      <x:c r="P61"/>
+      <x:c r="Q61"/>
+      <x:c r="R61" t="str">
+        <x:v>https://www.tp-link.com/uk/home-networking/wifi-router/tl-wr841n/</x:v>
+      </x:c>
+      <x:c r="S61"/>
+      <x:c r="T61"/>
+      <x:c r="U61"/>
+      <x:c r="V61" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="str">
+        <x:v>NET-005</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>TP-Link Wireless N Router</x:v>
+      </x:c>
+      <x:c r="C62" t="str">
+        <x:v>Networking</x:v>
+      </x:c>
+      <x:c r="D62" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E62" t="str">
+        <x:v>TP-Link</x:v>
+      </x:c>
+      <x:c r="F62" t="str">
+        <x:v>TL-WR841N</x:v>
+      </x:c>
+      <x:c r="G62"/>
+      <x:c r="H62" t="str">
+        <x:v>300 Mbps 2.4 GHz Wireless N router</x:v>
+      </x:c>
+      <x:c r="I62"/>
+      <x:c r="J62"/>
+      <x:c r="K62" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L62"/>
+      <x:c r="M62"/>
+      <x:c r="N62" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O62"/>
+      <x:c r="P62"/>
+      <x:c r="Q62"/>
+      <x:c r="R62" t="str">
+        <x:v>https://www.tp-link.com/uk/home-networking/wifi-router/tl-wr841n/</x:v>
+      </x:c>
+      <x:c r="S62"/>
+      <x:c r="T62"/>
+      <x:c r="U62"/>
+      <x:c r="V62" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="str">
+        <x:v>LGT-003</x:v>
+      </x:c>
+      <x:c r="B63" t="str">
+        <x:v>Overhead Light</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>Lighting</x:v>
+      </x:c>
+      <x:c r="D63" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E63" t="str">
+        <x:v>NEEWER</x:v>
+      </x:c>
+      <x:c r="F63" t="str">
+        <x:v>BASICS BP66</x:v>
+      </x:c>
+      <x:c r="G63"/>
+      <x:c r="H63" t="str">
+        <x:v>Overhead light supplied as part of a two-pack</x:v>
+      </x:c>
+      <x:c r="I63"/>
+      <x:c r="J63"/>
+      <x:c r="K63" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L63"/>
+      <x:c r="M63"/>
+      <x:c r="N63" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O63"/>
+      <x:c r="P63"/>
+      <x:c r="Q63"/>
+      <x:c r="R63"/>
+      <x:c r="S63"/>
+      <x:c r="T63"/>
+      <x:c r="U63"/>
+      <x:c r="V63" t="str">
+        <x:v>https://m.media-amazon.com/images/I/61Gj-qwZzvL._AC_SL1500_.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str">
+        <x:v>LGT-004</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>Overhead Light</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>Lighting</x:v>
+      </x:c>
+      <x:c r="D64" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E64" t="str">
+        <x:v>NEEWER</x:v>
+      </x:c>
+      <x:c r="F64" t="str">
+        <x:v>BASICS BP66</x:v>
+      </x:c>
+      <x:c r="G64"/>
+      <x:c r="H64" t="str">
+        <x:v>Overhead light supplied as part of a two-pack</x:v>
+      </x:c>
+      <x:c r="I64"/>
+      <x:c r="J64"/>
+      <x:c r="K64" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L64"/>
+      <x:c r="M64"/>
+      <x:c r="N64" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O64"/>
+      <x:c r="P64"/>
+      <x:c r="Q64"/>
+      <x:c r="R64"/>
+      <x:c r="S64"/>
+      <x:c r="T64"/>
+      <x:c r="U64"/>
+      <x:c r="V64" t="str">
+        <x:v>https://m.media-amazon.com/images/I/61Gj-qwZzvL._AC_SL1500_.jpg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str">
+        <x:v>PER-001</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>Logitech MK270 Wireless Keyboard and Mouse</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>Computer peripherals</x:v>
+      </x:c>
+      <x:c r="D65" t="str">
+        <x:v>Bundle</x:v>
+      </x:c>
+      <x:c r="E65" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="F65" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="G65"/>
+      <x:c r="H65" t="str">
+        <x:v>Wireless full-size keyboard and mouse combo</x:v>
+      </x:c>
+      <x:c r="I65"/>
+      <x:c r="J65"/>
+      <x:c r="K65" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L65"/>
+      <x:c r="M65"/>
+      <x:c r="N65" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O65"/>
+      <x:c r="P65" t="str">
+        <x:v>Return the keyboard, mouse and USB receiver together.</x:v>
+      </x:c>
+      <x:c r="Q65"/>
+      <x:c r="R65" t="str">
+        <x:v>https://www.logitech.com/en-gb/shop/p/mk270-wireless-keyboard-mouse</x:v>
+      </x:c>
+      <x:c r="S65"/>
+      <x:c r="T65"/>
+      <x:c r="U65"/>
+      <x:c r="V65" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>PER-002</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>Logitech MK270 Wireless Keyboard and Mouse</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>Computer peripherals</x:v>
+      </x:c>
+      <x:c r="D66" t="str">
+        <x:v>Bundle</x:v>
+      </x:c>
+      <x:c r="E66" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="F66" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="G66"/>
+      <x:c r="H66" t="str">
+        <x:v>Wireless full-size keyboard and mouse combo</x:v>
+      </x:c>
+      <x:c r="I66"/>
+      <x:c r="J66"/>
+      <x:c r="K66" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L66"/>
+      <x:c r="M66"/>
+      <x:c r="N66" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O66"/>
+      <x:c r="P66" t="str">
+        <x:v>Return the keyboard, mouse and USB receiver together.</x:v>
+      </x:c>
+      <x:c r="Q66"/>
+      <x:c r="R66" t="str">
+        <x:v>https://www.logitech.com/en-gb/shop/p/mk270-wireless-keyboard-mouse</x:v>
+      </x:c>
+      <x:c r="S66"/>
+      <x:c r="T66"/>
+      <x:c r="U66"/>
+      <x:c r="V66" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>PER-003</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>Logitech MK270 Wireless Keyboard and Mouse</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>Computer peripherals</x:v>
+      </x:c>
+      <x:c r="D67" t="str">
+        <x:v>Bundle</x:v>
+      </x:c>
+      <x:c r="E67" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="F67" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="G67"/>
+      <x:c r="H67" t="str">
+        <x:v>Wireless full-size keyboard and mouse combo</x:v>
+      </x:c>
+      <x:c r="I67"/>
+      <x:c r="J67"/>
+      <x:c r="K67" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L67"/>
+      <x:c r="M67"/>
+      <x:c r="N67" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O67"/>
+      <x:c r="P67" t="str">
+        <x:v>Return the keyboard, mouse and USB receiver together.</x:v>
+      </x:c>
+      <x:c r="Q67"/>
+      <x:c r="R67" t="str">
+        <x:v>https://www.logitech.com/en-gb/shop/p/mk270-wireless-keyboard-mouse</x:v>
+      </x:c>
+      <x:c r="S67"/>
+      <x:c r="T67"/>
+      <x:c r="U67"/>
+      <x:c r="V67" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str">
+        <x:v>PER-004</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>Logitech MK270 Wireless Keyboard and Mouse</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>Computer peripherals</x:v>
+      </x:c>
+      <x:c r="D68" t="str">
+        <x:v>Bundle</x:v>
+      </x:c>
+      <x:c r="E68" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="F68" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="G68"/>
+      <x:c r="H68" t="str">
+        <x:v>Wireless full-size keyboard and mouse combo</x:v>
+      </x:c>
+      <x:c r="I68"/>
+      <x:c r="J68"/>
+      <x:c r="K68" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L68"/>
+      <x:c r="M68"/>
+      <x:c r="N68" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O68"/>
+      <x:c r="P68" t="str">
+        <x:v>Return the keyboard, mouse and USB receiver together.</x:v>
+      </x:c>
+      <x:c r="Q68"/>
+      <x:c r="R68" t="str">
+        <x:v>https://www.logitech.com/en-gb/shop/p/mk270-wireless-keyboard-mouse</x:v>
+      </x:c>
+      <x:c r="S68"/>
+      <x:c r="T68"/>
+      <x:c r="U68"/>
+      <x:c r="V68" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str">
+        <x:v>PER-005</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>Logitech MK270 Wireless Keyboard and Mouse</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>Computer peripherals</x:v>
+      </x:c>
+      <x:c r="D69" t="str">
+        <x:v>Bundle</x:v>
+      </x:c>
+      <x:c r="E69" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="F69" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="G69"/>
+      <x:c r="H69" t="str">
+        <x:v>Wireless full-size keyboard and mouse combo</x:v>
+      </x:c>
+      <x:c r="I69"/>
+      <x:c r="J69"/>
+      <x:c r="K69" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L69"/>
+      <x:c r="M69"/>
+      <x:c r="N69" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O69"/>
+      <x:c r="P69" t="str">
+        <x:v>Return the keyboard, mouse and USB receiver together.</x:v>
+      </x:c>
+      <x:c r="Q69"/>
+      <x:c r="R69" t="str">
+        <x:v>https://www.logitech.com/en-gb/shop/p/mk270-wireless-keyboard-mouse</x:v>
+      </x:c>
+      <x:c r="S69"/>
+      <x:c r="T69"/>
+      <x:c r="U69"/>
+      <x:c r="V69" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str">
+        <x:v>LGT-005</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>IKEA TOKABO Ambient Lamp</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>Lighting</x:v>
+      </x:c>
+      <x:c r="D70" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E70" t="str">
+        <x:v>IKEA</x:v>
+      </x:c>
+      <x:c r="F70" t="str">
+        <x:v>B1903 TOKABO</x:v>
+      </x:c>
+      <x:c r="G70"/>
+      <x:c r="H70"/>
+      <x:c r="I70"/>
+      <x:c r="J70"/>
+      <x:c r="K70" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L70"/>
+      <x:c r="M70"/>
+      <x:c r="N70" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O70"/>
+      <x:c r="P70"/>
+      <x:c r="Q70"/>
+      <x:c r="R70"/>
+      <x:c r="S70"/>
+      <x:c r="T70"/>
+      <x:c r="U70"/>
+      <x:c r="V70" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str">
+        <x:v>MNT-013</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>Phone Stand</x:v>
+      </x:c>
+      <x:c r="C71" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D71" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E71"/>
+      <x:c r="F71"/>
+      <x:c r="G71"/>
+      <x:c r="H71"/>
+      <x:c r="I71"/>
+      <x:c r="J71"/>
+      <x:c r="K71" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L71"/>
+      <x:c r="M71"/>
+      <x:c r="N71" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O71"/>
+      <x:c r="P71"/>
+      <x:c r="Q71"/>
+      <x:c r="R71"/>
+      <x:c r="S71"/>
+      <x:c r="T71"/>
+      <x:c r="U71"/>
+      <x:c r="V71" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str">
+        <x:v>PWR-005</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>MSCIEN Power Strip</x:v>
+      </x:c>
+      <x:c r="C72" t="str">
+        <x:v>Power and connectivity</x:v>
+      </x:c>
+      <x:c r="D72" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E72" t="str">
+        <x:v>MSCIEN</x:v>
+      </x:c>
+      <x:c r="F72" t="str">
+        <x:v>YP11Y2Y203U</x:v>
+      </x:c>
+      <x:c r="G72"/>
+      <x:c r="H72"/>
+      <x:c r="I72"/>
+      <x:c r="J72"/>
+      <x:c r="K72" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L72"/>
+      <x:c r="M72"/>
+      <x:c r="N72" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O72"/>
+      <x:c r="P72"/>
+      <x:c r="Q72"/>
+      <x:c r="R72"/>
+      <x:c r="S72"/>
+      <x:c r="T72"/>
+      <x:c r="U72"/>
+      <x:c r="V72" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str">
+        <x:v>PWR-006</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>UGREEN 6-in-1 USB Hub</x:v>
+      </x:c>
+      <x:c r="C73" t="str">
+        <x:v>Power and connectivity</x:v>
+      </x:c>
+      <x:c r="D73" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E73" t="str">
+        <x:v>UGREEN</x:v>
+      </x:c>
+      <x:c r="F73" t="str">
+        <x:v>6-in-1 USB Hub</x:v>
+      </x:c>
+      <x:c r="G73"/>
+      <x:c r="H73"/>
+      <x:c r="I73"/>
+      <x:c r="J73"/>
+      <x:c r="K73" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L73"/>
+      <x:c r="M73"/>
+      <x:c r="N73" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O73"/>
+      <x:c r="P73"/>
+      <x:c r="Q73"/>
+      <x:c r="R73"/>
+      <x:c r="S73"/>
+      <x:c r="T73"/>
+      <x:c r="U73"/>
+      <x:c r="V73" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str">
+        <x:v>MNT-014</x:v>
+      </x:c>
+      <x:c r="B74" t="str">
+        <x:v>Phone Mount</x:v>
+      </x:c>
+      <x:c r="C74" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D74" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E74"/>
+      <x:c r="F74"/>
+      <x:c r="G74"/>
+      <x:c r="H74"/>
+      <x:c r="I74"/>
+      <x:c r="J74"/>
+      <x:c r="K74" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L74"/>
+      <x:c r="M74"/>
+      <x:c r="N74" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O74"/>
+      <x:c r="P74"/>
+      <x:c r="Q74"/>
+      <x:c r="R74"/>
+      <x:c r="S74"/>
+      <x:c r="T74"/>
+      <x:c r="U74"/>
+      <x:c r="V74" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="str">
+        <x:v>MNT-015</x:v>
+      </x:c>
+      <x:c r="B75" t="str">
+        <x:v>Phone Mount</x:v>
+      </x:c>
+      <x:c r="C75" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D75" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E75"/>
+      <x:c r="F75"/>
+      <x:c r="G75"/>
+      <x:c r="H75"/>
+      <x:c r="I75"/>
+      <x:c r="J75"/>
+      <x:c r="K75" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L75"/>
+      <x:c r="M75"/>
+      <x:c r="N75" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O75"/>
+      <x:c r="P75"/>
+      <x:c r="Q75"/>
+      <x:c r="R75"/>
+      <x:c r="S75"/>
+      <x:c r="T75"/>
+      <x:c r="U75"/>
+      <x:c r="V75" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str">
+        <x:v>MNT-016</x:v>
+      </x:c>
+      <x:c r="B76" t="str">
+        <x:v>Phone Mount</x:v>
+      </x:c>
+      <x:c r="C76" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D76" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E76"/>
+      <x:c r="F76"/>
+      <x:c r="G76"/>
+      <x:c r="H76"/>
+      <x:c r="I76"/>
+      <x:c r="J76"/>
+      <x:c r="K76" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L76"/>
+      <x:c r="M76"/>
+      <x:c r="N76" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O76"/>
+      <x:c r="P76"/>
+      <x:c r="Q76"/>
+      <x:c r="R76"/>
+      <x:c r="S76"/>
+      <x:c r="T76"/>
+      <x:c r="U76"/>
+      <x:c r="V76" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str">
+        <x:v>PWR-007</x:v>
+      </x:c>
+      <x:c r="B77" t="str">
+        <x:v>RSHTECH USB Hub</x:v>
+      </x:c>
+      <x:c r="C77" t="str">
+        <x:v>Power and connectivity</x:v>
+      </x:c>
+      <x:c r="D77" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E77" t="str">
+        <x:v>RSHTECH</x:v>
+      </x:c>
+      <x:c r="F77"/>
+      <x:c r="G77"/>
+      <x:c r="H77"/>
+      <x:c r="I77"/>
+      <x:c r="J77"/>
+      <x:c r="K77" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L77"/>
+      <x:c r="M77"/>
+      <x:c r="N77" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O77"/>
+      <x:c r="P77"/>
+      <x:c r="Q77"/>
+      <x:c r="R77"/>
+      <x:c r="S77"/>
+      <x:c r="T77"/>
+      <x:c r="U77"/>
+      <x:c r="V77" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str">
+        <x:v>PWR-008</x:v>
+      </x:c>
+      <x:c r="B78" t="str">
+        <x:v>RSHTECH USB Hub</x:v>
+      </x:c>
+      <x:c r="C78" t="str">
+        <x:v>Power and connectivity</x:v>
+      </x:c>
+      <x:c r="D78" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E78" t="str">
+        <x:v>RSHTECH</x:v>
+      </x:c>
+      <x:c r="F78"/>
+      <x:c r="G78"/>
+      <x:c r="H78"/>
+      <x:c r="I78"/>
+      <x:c r="J78"/>
+      <x:c r="K78" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L78"/>
+      <x:c r="M78"/>
+      <x:c r="N78" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O78"/>
+      <x:c r="P78"/>
+      <x:c r="Q78"/>
+      <x:c r="R78"/>
+      <x:c r="S78"/>
+      <x:c r="T78"/>
+      <x:c r="U78"/>
+      <x:c r="V78" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str">
+        <x:v>PWR-009</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>RSHTECH USB Hub</x:v>
+      </x:c>
+      <x:c r="C79" t="str">
+        <x:v>Power and connectivity</x:v>
+      </x:c>
+      <x:c r="D79" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E79" t="str">
+        <x:v>RSHTECH</x:v>
+      </x:c>
+      <x:c r="F79"/>
+      <x:c r="G79"/>
+      <x:c r="H79"/>
+      <x:c r="I79"/>
+      <x:c r="J79"/>
+      <x:c r="K79" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L79"/>
+      <x:c r="M79"/>
+      <x:c r="N79" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O79"/>
+      <x:c r="P79"/>
+      <x:c r="Q79"/>
+      <x:c r="R79"/>
+      <x:c r="S79"/>
+      <x:c r="T79"/>
+      <x:c r="U79"/>
+      <x:c r="V79" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="4">
+  <x:dataValidations count="5">
     <x:dataValidation type="list" sqref="D2:D34">
       <x:formula1>"Individual,Bundle"</x:formula1>
     </x:dataValidation>
@@ -3467,10 +4763,13 @@
     <x:dataValidation type="list" sqref="N2:N34">
       <x:formula1>"GBP,EUR,USD"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="C2:C250">
+      <x:formula1>Categories!$A$2:$A$14</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf96762f4b04493e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dfef7f8f8154cc6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3491,111 +4790,119 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
+      <x:c r="G1" s="2" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="s">
+      <x:c r="H1" s="3" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="s">
-        <x:v>204</x:v>
-      </x:c>
       <x:c r="I1" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="10" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B2" s="10" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="C2" s="4"/>
-      <x:c r="D2" s="4"/>
+      <x:c r="A2" s="10" t="str">
+        <x:v>ROB-003</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="str">
+        <x:v>Robot</x:v>
+      </x:c>
+      <x:c r="C2" s="4" t="str">
+        <x:v>Pollen Robotics</x:v>
+      </x:c>
+      <x:c r="D2" s="4" t="str">
+        <x:v>Reachy Mini Wireless</x:v>
+      </x:c>
       <x:c r="E2" s="4"/>
-      <x:c r="F2" s="10">
+      <x:c r="F2" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G2" s="10" t="s">
-        <x:v>206</x:v>
+      <x:c r="G2" s="10" t="str">
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H2" s="11"/>
-      <x:c r="I2" t="s">
-        <x:v>61</x:v>
+      <x:c r="I2" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="10" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="s">
-        <x:v>207</x:v>
+      <x:c r="A3" s="10" t="str">
+        <x:v>ROB-003</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="str">
+        <x:v>Charger</x:v>
       </x:c>
       <x:c r="C3" s="4"/>
       <x:c r="D3" s="4"/>
       <x:c r="E3" s="4"/>
-      <x:c r="F3" s="10">
+      <x:c r="F3" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G3" s="10" t="s">
-        <x:v>206</x:v>
+      <x:c r="G3" s="10" t="str">
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H3" s="11"/>
-      <x:c r="I3" t="s">
-        <x:v>70</x:v>
+      <x:c r="I3" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="10" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B4" s="10" t="s">
-        <x:v>208</x:v>
+      <x:c r="A4" s="10" t="str">
+        <x:v>ROB-003</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>USB Cable</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="D4" s="4"/>
       <x:c r="E4" s="4"/>
-      <x:c r="F4" s="10">
+      <x:c r="F4" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G4" s="10" t="s">
-        <x:v>206</x:v>
+      <x:c r="G4" s="10" t="str">
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H4" s="11"/>
-      <x:c r="I4" t="s">
-        <x:v>70</x:v>
+      <x:c r="I4" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="10" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B5" s="10" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="C5" s="4"/>
-      <x:c r="D5" s="4"/>
+      <x:c r="A5" s="10" t="str">
+        <x:v>ROB-004</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>Robot</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="str">
+        <x:v>Pollen Robotics</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="str">
+        <x:v>Reachy Mini Lite</x:v>
+      </x:c>
       <x:c r="E5" s="4"/>
-      <x:c r="F5" s="10">
+      <x:c r="F5" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>206</x:v>
+      <x:c r="G5" s="10" t="str">
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H5" s="11"/>
       <x:c r="I5" t="str">
@@ -3603,125 +4910,133 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="10" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B6" s="10" t="s">
-        <x:v>207</x:v>
+      <x:c r="A6" s="10" t="str">
+        <x:v>ROB-004</x:v>
+      </x:c>
+      <x:c r="B6" s="10" t="str">
+        <x:v>Charger</x:v>
       </x:c>
       <x:c r="C6" s="4"/>
       <x:c r="D6" s="4"/>
       <x:c r="E6" s="4"/>
-      <x:c r="F6" s="10">
+      <x:c r="F6" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G6" s="10" t="s">
-        <x:v>206</x:v>
+      <x:c r="G6" s="10" t="str">
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H6" s="11"/>
-      <x:c r="I6" t="s">
-        <x:v>70</x:v>
+      <x:c r="I6" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="10" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B7" s="10" t="s">
-        <x:v>208</x:v>
+      <x:c r="A7" s="10" t="str">
+        <x:v>ROB-004</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>USB Cable</x:v>
       </x:c>
       <x:c r="C7" s="4"/>
       <x:c r="D7" s="4"/>
       <x:c r="E7" s="4"/>
-      <x:c r="F7" s="10">
+      <x:c r="F7" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
-        <x:v>206</x:v>
+      <x:c r="G7" s="10" t="str">
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H7" s="11"/>
-      <x:c r="I7" t="s">
-        <x:v>70</x:v>
+      <x:c r="I7" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="10" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B8" s="10" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="C8" s="4"/>
-      <x:c r="D8" s="4"/>
+      <x:c r="A8" s="10" t="str">
+        <x:v>ROB-005</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>Robot</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="str">
+        <x:v>Pollen Robotics</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="str">
+        <x:v>Reachy Mini Wireless</x:v>
+      </x:c>
       <x:c r="E8" s="4"/>
-      <x:c r="F8" s="10">
+      <x:c r="F8" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G8" s="10" t="s">
-        <x:v>206</x:v>
+      <x:c r="G8" s="10" t="str">
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H8" s="11"/>
       <x:c r="I8" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-lite.png</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="10" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="s">
-        <x:v>207</x:v>
+      <x:c r="A9" s="10" t="str">
+        <x:v>ROB-005</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>Charger</x:v>
       </x:c>
       <x:c r="C9" s="4"/>
       <x:c r="D9" s="4"/>
       <x:c r="E9" s="4"/>
-      <x:c r="F9" s="10">
+      <x:c r="F9" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G9" s="10" t="s">
-        <x:v>206</x:v>
+      <x:c r="G9" s="10" t="str">
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H9" s="11"/>
-      <x:c r="I9" t="s">
-        <x:v>70</x:v>
+      <x:c r="I9" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="10" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B10" s="10" t="s">
-        <x:v>208</x:v>
+      <x:c r="A10" s="10" t="str">
+        <x:v>ROB-005</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>USB Cable</x:v>
       </x:c>
       <x:c r="C10" s="4"/>
       <x:c r="D10" s="4"/>
       <x:c r="E10" s="4"/>
-      <x:c r="F10" s="10">
+      <x:c r="F10" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G10" s="10" t="s">
-        <x:v>206</x:v>
+      <x:c r="G10" s="10" t="str">
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H10" s="11"/>
-      <x:c r="I10" t="s">
-        <x:v>70</x:v>
+      <x:c r="I10" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="10" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B11" s="10" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="C11" s="4"/>
-      <x:c r="D11" s="4"/>
+      <x:c r="A11" s="10" t="str">
+        <x:v>ROB-006</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>Robot</x:v>
+      </x:c>
+      <x:c r="C11" s="4" t="str">
+        <x:v>Pollen Robotics</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="str">
+        <x:v>Reachy Mini Lite</x:v>
+      </x:c>
       <x:c r="E11" s="4"/>
-      <x:c r="F11" s="10">
+      <x:c r="F11" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G11" s="10" t="s">
-        <x:v>206</x:v>
+      <x:c r="G11" s="10" t="str">
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H11" s="11"/>
       <x:c r="I11" t="str">
@@ -3729,45 +5044,497 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="10" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B12" s="10" t="s">
-        <x:v>207</x:v>
+      <x:c r="A12" s="10" t="str">
+        <x:v>ROB-006</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>Charger</x:v>
       </x:c>
       <x:c r="C12" s="4"/>
       <x:c r="D12" s="4"/>
       <x:c r="E12" s="4"/>
-      <x:c r="F12" s="10">
+      <x:c r="F12" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G12" s="10" t="s">
-        <x:v>206</x:v>
+      <x:c r="G12" s="10" t="str">
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H12" s="11"/>
-      <x:c r="I12" t="s">
-        <x:v>70</x:v>
+      <x:c r="I12" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="10" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B13" s="10" t="s">
-        <x:v>208</x:v>
+      <x:c r="A13" s="10" t="str">
+        <x:v>ROB-006</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>USB Cable</x:v>
       </x:c>
       <x:c r="C13" s="4"/>
       <x:c r="D13" s="4"/>
       <x:c r="E13" s="4"/>
-      <x:c r="F13" s="10">
+      <x:c r="F13" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G13" s="10" t="s">
-        <x:v>206</x:v>
+      <x:c r="G13" s="10" t="str">
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H13" s="11"/>
-      <x:c r="I13" t="s">
-        <x:v>70</x:v>
+      <x:c r="I13" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>ROB-007</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Robot</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>Pollen Robotics</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Reachy Mini Wireless</x:v>
+      </x:c>
+      <x:c r="E14"/>
+      <x:c r="F14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H14"/>
+      <x:c r="I14" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>ROB-007</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Charger</x:v>
+      </x:c>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H15"/>
+      <x:c r="I15" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>ROB-007</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>USB Cable</x:v>
+      </x:c>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H16"/>
+      <x:c r="I16" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PER-001</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Keyboard</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E17"/>
+      <x:c r="F17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H17"/>
+      <x:c r="I17" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>PER-001</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Mouse</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E18"/>
+      <x:c r="F18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H18"/>
+      <x:c r="I18" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>PER-001</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>USB receiver</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E19"/>
+      <x:c r="F19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>Nano receiver for this keyboard and mouse set</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>PER-002</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Keyboard</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E20"/>
+      <x:c r="F20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H20"/>
+      <x:c r="I20" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>PER-002</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Mouse</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E21"/>
+      <x:c r="F21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H21"/>
+      <x:c r="I21" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>PER-002</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>USB receiver</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E22"/>
+      <x:c r="F22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>Nano receiver for this keyboard and mouse set</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>PER-003</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Keyboard</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E23"/>
+      <x:c r="F23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H23"/>
+      <x:c r="I23" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>PER-003</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>Mouse</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E24"/>
+      <x:c r="F24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H24"/>
+      <x:c r="I24" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>PER-003</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>USB receiver</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E25"/>
+      <x:c r="F25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>Nano receiver for this keyboard and mouse set</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>PER-004</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>Keyboard</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E26"/>
+      <x:c r="F26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H26"/>
+      <x:c r="I26" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>PER-004</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>Mouse</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E27"/>
+      <x:c r="F27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H27"/>
+      <x:c r="I27" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>PER-004</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>USB receiver</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E28"/>
+      <x:c r="F28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>Nano receiver for this keyboard and mouse set</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>PER-005</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>Keyboard</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E29"/>
+      <x:c r="F29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H29"/>
+      <x:c r="I29" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>PER-005</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Mouse</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E30"/>
+      <x:c r="F30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H30"/>
+      <x:c r="I30" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>PER-005</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>USB receiver</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
+      <x:c r="E31"/>
+      <x:c r="F31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>Nano receiver for this keyboard and mouse set</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3781,7 +5548,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93f03117bd6e4c78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb82a3c10c7f4486e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3800,87 +5567,87 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>210</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>211</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D1" s="3" t="s">
-        <x:v>204</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="10" t="s">
-        <x:v>212</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B2" s="10" t="s">
-        <x:v>213</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C2" s="10" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D2" s="4"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="s">
-        <x:v>214</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>215</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C3" s="10" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D3" s="4"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="s">
-        <x:v>216</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B4" s="10" t="s">
-        <x:v>217</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C4" s="10" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D4" s="4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="s">
-        <x:v>218</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B5" s="10" t="s">
-        <x:v>219</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C5" s="10" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D5" s="4"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="s">
-        <x:v>220</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B6" s="10" t="s">
-        <x:v>221</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C6" s="10" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D6" s="4"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="s">
-        <x:v>222</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B7" s="10" t="s">
-        <x:v>223</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C7" s="10" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D7" s="4"/>
     </x:row>
@@ -3892,7 +5659,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R982107907aec4690"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a5445168ddc404b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3911,129 +5678,162 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>224</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C1" s="3" t="s">
-        <x:v>225</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="10" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B2" s="10" t="s">
-        <x:v>226</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C2" s="11" t="s">
-        <x:v>227</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>228</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>229</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="s">
-        <x:v>230</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B4" s="10" t="s">
-        <x:v>231</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C4" s="11" t="s">
-        <x:v>232</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B5" s="10" t="s">
-        <x:v>233</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C5" s="11" t="s">
-        <x:v>234</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B6" s="10" t="s">
-        <x:v>235</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>236</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B7" s="10" t="s">
-        <x:v>237</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
-        <x:v>238</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B8" s="10" t="s">
-        <x:v>239</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C8" s="11" t="s">
-        <x:v>240</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B9" s="10" t="s">
-        <x:v>241</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C9" s="11" t="s">
-        <x:v>242</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="s">
-        <x:v>243</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B10" s="10" t="s">
-        <x:v>244</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C10" s="11" t="s">
-        <x:v>245</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>246</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>247</x:v>
+        <x:v>243</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Monitors</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>MON</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>Computer monitors and displays</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Networking</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>NET</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Routers and network equipment</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Computer peripherals</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>Keyboards, mice and peripheral bundles</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72bd6fef27e9462c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1965319964e7468b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/templates/NFC_Inventory_Import_Template.xlsx
+++ b/data/templates/NFC_Inventory_Import_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rd1c2b1c46df4453b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Ra7d675b8b89a4211"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="R0d76ad2cdbd541e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="Rf79136a8e59846f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R559ce88da8e348a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R78708799343443e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R1ec2f7575a92469a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="R61e768b9a3754cd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="Rb22e291e17f5474d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R63d8785d76c74084"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -278,9 +278,6 @@
     <x:t xml:space="preserve">MNT-003</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Big Tripod</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/victiv-tripod.jpg</x:t>
   </x:si>
   <x:si>
@@ -300,9 +297,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">MNT-008</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Small Tripod</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/lammcou-small-tripod.jpg</x:t>
@@ -2120,8 +2114,8 @@
       <x:c r="A16" s="9" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B16" s="10" t="s">
-        <x:v>88</x:v>
+      <x:c r="B16" s="10" t="str">
+        <x:v>PEMOTech Tripod</x:v>
       </x:c>
       <x:c r="C16" s="10" t="s">
         <x:v>73</x:v>
@@ -2129,7 +2123,9 @@
       <x:c r="D16" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E16" s="4"/>
+      <x:c r="E16" s="4" t="str">
+        <x:v>PEMOTech</x:v>
+      </x:c>
       <x:c r="F16" s="4"/>
       <x:c r="G16" s="4"/>
       <x:c r="H16" s="11"/>
@@ -2151,15 +2147,15 @@
       <x:c r="T16" s="11"/>
       <x:c r="U16" s="11"/>
       <x:c r="V16" s="11" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="37.5">
       <x:c r="A17" s="9" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B17" s="10" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>Victiv Tripod</x:v>
       </x:c>
       <x:c r="C17" s="10" t="s">
         <x:v>73</x:v>
@@ -2167,8 +2163,12 @@
       <x:c r="D17" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E17" s="4"/>
-      <x:c r="F17" s="4"/>
+      <x:c r="E17" s="4" t="str">
+        <x:v>Victiv</x:v>
+      </x:c>
+      <x:c r="F17" s="4" t="str">
+        <x:v>NT70</x:v>
+      </x:c>
       <x:c r="G17" s="4"/>
       <x:c r="H17" s="11"/>
       <x:c r="I17" s="11"/>
@@ -2189,15 +2189,15 @@
       <x:c r="T17" s="11"/>
       <x:c r="U17" s="11"/>
       <x:c r="V17" s="11" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="37.5">
       <x:c r="A18" s="9" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B18" s="10" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str">
+        <x:v>K&amp;F Tripod</x:v>
       </x:c>
       <x:c r="C18" s="10" t="s">
         <x:v>73</x:v>
@@ -2205,8 +2205,12 @@
       <x:c r="D18" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E18" s="4"/>
-      <x:c r="F18" s="4"/>
+      <x:c r="E18" s="4" t="str">
+        <x:v>K&amp;F Concept</x:v>
+      </x:c>
+      <x:c r="F18" s="4" t="str">
+        <x:v>K234A0</x:v>
+      </x:c>
       <x:c r="G18" s="4"/>
       <x:c r="H18" s="11"/>
       <x:c r="I18" s="11"/>
@@ -2227,15 +2231,15 @@
       <x:c r="T18" s="11"/>
       <x:c r="U18" s="11"/>
       <x:c r="V18" s="11" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="37.5">
       <x:c r="A19" s="9" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="B19" s="10" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="C19" s="10" t="s">
         <x:v>73</x:v>
@@ -2270,10 +2274,10 @@
     </x:row>
     <x:row r="20" ht="37.5">
       <x:c r="A20" s="9" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B20" s="10" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C20" s="10" t="s">
         <x:v>73</x:v>
@@ -2308,10 +2312,10 @@
     </x:row>
     <x:row r="21" ht="37.5">
       <x:c r="A21" s="9" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B21" s="10" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B21" s="10" t="str">
+        <x:v>Unbranded Three-Stage Tripod</x:v>
       </x:c>
       <x:c r="C21" s="10" t="s">
         <x:v>73</x:v>
@@ -2319,7 +2323,9 @@
       <x:c r="D21" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E21" s="4"/>
+      <x:c r="E21" s="4" t="str">
+        <x:v>Unbranded</x:v>
+      </x:c>
       <x:c r="F21" s="4"/>
       <x:c r="G21" s="4"/>
       <x:c r="H21" s="11"/>
@@ -2341,15 +2347,15 @@
       <x:c r="T21" s="11"/>
       <x:c r="U21" s="11"/>
       <x:c r="V21" s="11" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="37.5">
       <x:c r="A22" s="9" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="B22" s="10" t="s">
         <x:v>96</x:v>
+      </x:c>
+      <x:c r="B22" s="10" t="str">
+        <x:v>Unbranded Three-Stage Tripod</x:v>
       </x:c>
       <x:c r="C22" s="10" t="s">
         <x:v>73</x:v>
@@ -2357,7 +2363,9 @@
       <x:c r="D22" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E22" s="4"/>
+      <x:c r="E22" s="4" t="str">
+        <x:v>Unbranded</x:v>
+      </x:c>
       <x:c r="F22" s="4"/>
       <x:c r="G22" s="4"/>
       <x:c r="H22" s="11"/>
@@ -2379,15 +2387,15 @@
       <x:c r="T22" s="11"/>
       <x:c r="U22" s="11"/>
       <x:c r="V22" s="11" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="37.5">
       <x:c r="A23" s="9" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B23" s="10" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C23" s="10" t="s">
         <x:v>73</x:v>
@@ -2422,10 +2430,10 @@
     </x:row>
     <x:row r="24" ht="37.5">
       <x:c r="A24" s="9" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B24" s="10" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C24" s="10" t="s">
         <x:v>73</x:v>
@@ -2460,26 +2468,26 @@
     </x:row>
     <x:row r="25" ht="37.5">
       <x:c r="A25" s="9" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B25" s="10" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C25" s="10" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="B25" s="10" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C25" s="10" t="s">
-        <x:v>104</x:v>
       </x:c>
       <x:c r="D25" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E25" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F25" s="4" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G25" s="4"/>
       <x:c r="H25" s="11" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="I25" s="11"/>
       <x:c r="J25" s="11"/>
@@ -2499,31 +2507,31 @@
       <x:c r="T25" s="11"/>
       <x:c r="U25" s="11"/>
       <x:c r="V25" s="11" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="37.5">
       <x:c r="A26" s="9" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B26" s="10" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C26" s="10" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D26" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E26" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F26" s="4" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G26" s="4"/>
       <x:c r="H26" s="11" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="I26" s="11"/>
       <x:c r="J26" s="11"/>
@@ -2543,31 +2551,31 @@
       <x:c r="T26" s="11"/>
       <x:c r="U26" s="11"/>
       <x:c r="V26" s="11" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="37.5">
       <x:c r="A27" s="9" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B27" s="10" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C27" s="10" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="B27" s="10" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C27" s="10" t="s">
-        <x:v>112</x:v>
       </x:c>
       <x:c r="D27" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E27" s="4" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F27" s="4" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G27" s="4"/>
       <x:c r="H27" s="11" t="s">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I27" s="11"/>
       <x:c r="J27" s="11"/>
@@ -2587,18 +2595,18 @@
       <x:c r="T27" s="11"/>
       <x:c r="U27" s="11"/>
       <x:c r="V27" s="11" t="s">
-        <x:v>116</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="37.5">
       <x:c r="A28" s="9" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B28" s="10" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C28" s="10" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D28" s="10" t="s">
         <x:v>50</x:v>
@@ -2625,18 +2633,18 @@
       <x:c r="T28" s="11"/>
       <x:c r="U28" s="11"/>
       <x:c r="V28" s="11" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="37.5">
       <x:c r="A29" s="9" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B29" s="10" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C29" s="10" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="B29" s="10" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C29" s="10" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="D29" s="10" t="s">
         <x:v>50</x:v>
@@ -2668,13 +2676,13 @@
     </x:row>
     <x:row r="30" ht="37.5">
       <x:c r="A30" s="9" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B30" s="10" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C30" s="10" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D30" s="10" t="s">
         <x:v>50</x:v>
@@ -2706,13 +2714,13 @@
     </x:row>
     <x:row r="31" ht="37.5">
       <x:c r="A31" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B31" s="10" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C31" s="10" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D31" s="10" t="s">
         <x:v>50</x:v>
@@ -2739,18 +2747,18 @@
       <x:c r="T31" s="11"/>
       <x:c r="U31" s="11"/>
       <x:c r="V31" s="11" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="37.5">
       <x:c r="A32" s="9" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B32" s="10" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C32" s="10" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D32" s="10" t="s">
         <x:v>50</x:v>
@@ -2777,31 +2785,31 @@
       <x:c r="T32" s="11"/>
       <x:c r="U32" s="11"/>
       <x:c r="V32" s="11" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="87.5">
       <x:c r="A33" s="9" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B33" s="10" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C33" s="10" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="B33" s="10" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C33" s="10" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="D33" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E33" s="4" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F33" s="4" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G33" s="4"/>
       <x:c r="H33" s="11" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="I33" s="11"/>
       <x:c r="J33" s="11"/>
@@ -2822,34 +2830,34 @@
       <x:c r="S33" s="11"/>
       <x:c r="T33" s="11"/>
       <x:c r="U33" s="11" t="s">
-        <x:v>136</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="V33" s="11" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="87.5">
       <x:c r="A34" s="9" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B34" s="10" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C34" s="10" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D34" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E34" s="4" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F34" s="4" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G34" s="4"/>
       <x:c r="H34" s="11" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="I34" s="11"/>
       <x:c r="J34" s="11"/>
@@ -2870,18 +2878,18 @@
       <x:c r="S34" s="11"/>
       <x:c r="T34" s="11"/>
       <x:c r="U34" s="11" t="s">
-        <x:v>136</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="V34" s="11" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="s">
-        <x:v>139</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>140</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C35" t="str">
         <x:v>Cameras</x:v>
@@ -2890,13 +2898,13 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E35" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="F35" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H35" t="s">
         <x:v>141</x:v>
-      </x:c>
-      <x:c r="F35" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="H35" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="K35" t="s">
         <x:v>51</x:v>
@@ -2908,18 +2916,18 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U35" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="V35" t="s">
-        <x:v>145</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="s">
-        <x:v>146</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>147</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C36" t="str">
         <x:v>Cameras</x:v>
@@ -2928,13 +2936,13 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E36" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="F36" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H36" t="s">
         <x:v>148</x:v>
-      </x:c>
-      <x:c r="F36" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="H36" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="K36" t="s">
         <x:v>51</x:v>
@@ -2946,18 +2954,18 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U36" t="s">
-        <x:v>151</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="V36" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>154</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C37" t="s">
         <x:v>68</x:v>
@@ -2966,13 +2974,13 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E37" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F37" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H37" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="F37" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H37" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="K37" t="s">
         <x:v>51</x:v>
@@ -2984,18 +2992,18 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U37" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="V37" t="s">
-        <x:v>159</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="s">
-        <x:v>160</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>154</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C38" t="s">
         <x:v>68</x:v>
@@ -3004,13 +3012,13 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E38" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F38" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H38" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="F38" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H38" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="K38" t="s">
         <x:v>51</x:v>
@@ -3022,18 +3030,18 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U38" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="V38" t="s">
-        <x:v>159</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="s">
-        <x:v>161</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>162</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C39" t="s">
         <x:v>68</x:v>
@@ -3042,13 +3050,13 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E39" t="s">
-        <x:v>155</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F39" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H39" t="s">
-        <x:v>164</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="K39" t="s">
         <x:v>51</x:v>
@@ -3060,18 +3068,18 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U39" t="s">
-        <x:v>165</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="V39" t="s">
-        <x:v>166</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="s">
-        <x:v>167</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>168</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C40" t="s">
         <x:v>73</x:v>
@@ -3080,10 +3088,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="F40" t="s">
-        <x:v>169</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H40" t="s">
-        <x:v>170</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="K40" t="s">
         <x:v>51</x:v>
@@ -3095,7 +3103,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U40" t="s">
-        <x:v>171</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="V40" t="s">
         <x:v>69</x:v>
@@ -3103,25 +3111,25 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="s">
-        <x:v>172</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D41" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E41" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F41" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H41" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="F41" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="H41" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="K41" t="s">
         <x:v>51</x:v>
@@ -3133,33 +3141,33 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U41" t="s">
-        <x:v>136</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="V41" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="s">
-        <x:v>173</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>174</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D42" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E42" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F42" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H42" t="s">
         <x:v>175</x:v>
-      </x:c>
-      <x:c r="F42" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="H42" t="s">
-        <x:v>177</x:v>
       </x:c>
       <x:c r="K42" t="s">
         <x:v>51</x:v>
@@ -3171,33 +3179,33 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U42" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="V42" t="s">
-        <x:v>179</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>174</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D43" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E43" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F43" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H43" t="s">
         <x:v>175</x:v>
-      </x:c>
-      <x:c r="F43" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="H43" t="s">
-        <x:v>177</x:v>
       </x:c>
       <x:c r="K43" t="s">
         <x:v>51</x:v>
@@ -3209,33 +3217,33 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U43" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="V43" t="s">
-        <x:v>179</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="s">
-        <x:v>181</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>174</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D44" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E44" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F44" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H44" t="s">
         <x:v>175</x:v>
-      </x:c>
-      <x:c r="F44" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="H44" t="s">
-        <x:v>177</x:v>
       </x:c>
       <x:c r="K44" t="s">
         <x:v>51</x:v>
@@ -3247,33 +3255,33 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U44" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="V44" t="s">
-        <x:v>179</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="s">
-        <x:v>182</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>183</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D45" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E45" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F45" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H45" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="F45" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="H45" t="s">
-        <x:v>186</x:v>
       </x:c>
       <x:c r="K45" t="s">
         <x:v>51</x:v>
@@ -3285,33 +3293,33 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U45" t="s">
-        <x:v>187</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="V45" t="s">
-        <x:v>188</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="s">
-        <x:v>189</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>183</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D46" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E46" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F46" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H46" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="F46" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="H46" t="s">
-        <x:v>186</x:v>
       </x:c>
       <x:c r="K46" t="s">
         <x:v>51</x:v>
@@ -3323,33 +3331,33 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U46" t="s">
-        <x:v>187</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="V46" t="s">
-        <x:v>188</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="s">
-        <x:v>190</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>183</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D47" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E47" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F47" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H47" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="F47" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="H47" t="s">
-        <x:v>186</x:v>
       </x:c>
       <x:c r="K47" t="s">
         <x:v>51</x:v>
@@ -3361,33 +3369,33 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U47" t="s">
-        <x:v>187</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="V47" t="s">
-        <x:v>188</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B48" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="C48" t="s">
         <x:v>191</x:v>
-      </x:c>
-      <x:c r="B48" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="C48" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="D48" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E48" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F48" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H48" t="s">
         <x:v>194</x:v>
-      </x:c>
-      <x:c r="F48" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="H48" t="s">
-        <x:v>196</x:v>
       </x:c>
       <x:c r="K48" t="s">
         <x:v>51</x:v>
@@ -3399,33 +3407,33 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U48" t="s">
-        <x:v>197</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="V48" t="s">
-        <x:v>198</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="s">
-        <x:v>199</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>192</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>193</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D49" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E49" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F49" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H49" t="s">
         <x:v>194</x:v>
-      </x:c>
-      <x:c r="F49" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="H49" t="s">
-        <x:v>196</x:v>
       </x:c>
       <x:c r="K49" t="s">
         <x:v>51</x:v>
@@ -3437,10 +3445,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U49" t="s">
-        <x:v>197</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="V49" t="s">
-        <x:v>198</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -4769,7 +4777,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dfef7f8f8154cc6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recc76ca8e5ee4aed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4793,7 +4801,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>200</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
         <x:v>29</x:v>
@@ -4805,13 +4813,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H1" s="3" t="s">
         <x:v>201</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="s">
-        <x:v>203</x:v>
       </x:c>
       <x:c r="I1" t="s">
         <x:v>46</x:v>
@@ -5548,7 +5556,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb82a3c10c7f4486e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35e8a9f14c884c46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5567,87 +5575,87 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="1" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>206</x:v>
-      </x:c>
       <x:c r="D1" s="3" t="s">
-        <x:v>203</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="10" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="C2" s="10" t="s">
         <x:v>207</x:v>
-      </x:c>
-      <x:c r="B2" s="10" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="C2" s="10" t="s">
-        <x:v>209</x:v>
       </x:c>
       <x:c r="D2" s="4"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="s">
-        <x:v>210</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>211</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C3" s="10" t="s">
-        <x:v>209</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D3" s="4"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="s">
-        <x:v>212</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B4" s="10" t="s">
-        <x:v>213</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C4" s="10" t="s">
-        <x:v>209</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D4" s="4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="s">
-        <x:v>214</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B5" s="10" t="s">
-        <x:v>215</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C5" s="10" t="s">
-        <x:v>209</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D5" s="4"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="s">
-        <x:v>216</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B6" s="10" t="s">
-        <x:v>217</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C6" s="10" t="s">
-        <x:v>209</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D6" s="4"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="s">
-        <x:v>218</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B7" s="10" t="s">
-        <x:v>219</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C7" s="10" t="s">
-        <x:v>209</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D7" s="4"/>
     </x:row>
@@ -5659,7 +5667,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a5445168ddc404b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf529312bef6140b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5681,10 +5689,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>220</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C1" s="3" t="s">
-        <x:v>221</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -5692,10 +5700,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B2" s="10" t="s">
-        <x:v>222</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C2" s="11" t="s">
-        <x:v>223</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -5703,21 +5711,21 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>224</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>225</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="B4" s="10" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="C4" s="11" t="s">
-        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -5725,76 +5733,76 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B5" s="10" t="s">
-        <x:v>229</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C5" s="11" t="s">
-        <x:v>230</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B6" s="10" t="s">
-        <x:v>231</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>232</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B7" s="10" t="s">
-        <x:v>233</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
-        <x:v>234</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B8" s="10" t="s">
-        <x:v>235</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C8" s="11" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B9" s="10" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C9" s="11" t="s">
-        <x:v>238</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
         <x:v>239</x:v>
-      </x:c>
-      <x:c r="B10" s="10" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="s">
-        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="s">
-        <x:v>193</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>243</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -5833,7 +5841,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1965319964e7468b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde40156dd5e1433b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/templates/NFC_Inventory_Import_Template.xlsx
+++ b/data/templates/NFC_Inventory_Import_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R78708799343443e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R1ec2f7575a92469a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="R61e768b9a3754cd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="Rb22e291e17f5474d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R63d8785d76c74084"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R2ab823917c754294"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R2f811497a6d14128"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="Re52e61fe6f244595"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="R861d94f5bf4b42b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="Rbdfb56e206fd40cf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1736,8 +1736,8 @@
       <x:c r="A7" s="9" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B7" s="10" t="s">
-        <x:v>62</x:v>
+      <x:c r="B7" s="10" t="str">
+        <x:v>Reachy Mini Wireless</x:v>
       </x:c>
       <x:c r="C7" s="10" t="s">
         <x:v>49</x:v>
@@ -1748,11 +1748,13 @@
       <x:c r="E7" s="4" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="F7" s="4" t="s">
-        <x:v>62</x:v>
+      <x:c r="F7" s="4" t="str">
+        <x:v>Reachy Mini Wireless</x:v>
       </x:c>
       <x:c r="G7" s="4"/>
-      <x:c r="H7" s="11"/>
+      <x:c r="H7" s="11" t="str">
+        <x:v>Wireless Reachy Mini robot bundle</x:v>
+      </x:c>
       <x:c r="I7" s="11"/>
       <x:c r="J7" s="11"/>
       <x:c r="K7" s="12" t="s">
@@ -1770,8 +1772,8 @@
       <x:c r="S7" s="11"/>
       <x:c r="T7" s="11"/>
       <x:c r="U7" s="11"/>
-      <x:c r="V7" s="11" t="s">
-        <x:v>64</x:v>
+      <x:c r="V7" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="37.5">
@@ -4777,7 +4779,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recc76ca8e5ee4aed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3b45ed2e1424ab3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5037,7 +5039,7 @@
         <x:v>Pollen Robotics</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>Reachy Mini Lite</x:v>
+        <x:v>Reachy Mini Wireless</x:v>
       </x:c>
       <x:c r="E11" s="4"/>
       <x:c r="F11" s="10" t="n">
@@ -5048,7 +5050,7 @@
       </x:c>
       <x:c r="H11" s="11"/>
       <x:c r="I11" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-lite.png</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -5556,7 +5558,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35e8a9f14c884c46"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcf6dd3a50754133"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5667,7 +5669,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf529312bef6140b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb078d135983444b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5841,7 +5843,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde40156dd5e1433b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a356ff9ed5c4848"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/templates/NFC_Inventory_Import_Template.xlsx
+++ b/data/templates/NFC_Inventory_Import_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R2ab823917c754294"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R2f811497a6d14128"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="Re52e61fe6f244595"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="R861d94f5bf4b42b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="Rbdfb56e206fd40cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R825b30ce035344b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R50c028b5084544b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="Rd4c794bb905244c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="R8b73a9e01e534673"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R9e247bb6e2274f25"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -155,583 +155,154 @@
     <x:t xml:space="preserve">photo_reference</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">ROB-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Misty Robot</x:t>
+    <x:t xml:space="preserve">component_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">quantity</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">required_on_return</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">notes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">username</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">display_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">active</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">n.salomons</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nicole</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Yes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">e.akinrintoyo23</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Emmanuel</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">s.shahin25</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Shahrooz</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">rht25</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ranul</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">haiwei.luo25</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Haiwei</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ana.nikolova26</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ana</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">asset_code_prefix</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">description</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Robots</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Individual</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Active</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GBP</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/misty-ii.png</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ROB-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ROB-003</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reachy Mini Wireless</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bundle</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Pollen Robotics</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SQ550205 / REACHY-MIN-WLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ROB-004</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reachy Mini Lite</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SQ550205 / PR-RML</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-lite.png</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ROB-005</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ROB-006</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TAB-001</x:t>
+    <x:t xml:space="preserve">ROB</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Robots and embodied robotic platforms</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Tablets</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TAB-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MNT-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tablet Stand</x:t>
+    <x:t xml:space="preserve">TAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tablets and mobile computing devices</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cameras</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">CAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cameras, webcams and depth sensors</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Tripods, stands and mounts</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">MNT-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CAM-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Azure Kinect DK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/azure-kinect-dk.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CAM-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CAM-003</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Anker PowerConf C200</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Anker</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">C200</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2K webcam</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SQ550189 / A3369011</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/anker-powerconf-c200.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CAM-004</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MNT-003</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/victiv-tripod.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MNT-004</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MNT-005</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MNT-006</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Flexible Small Tripod</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MNT-007</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MNT-008</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/lammcou-small-tripod.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MNT-009</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MNT-010</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Overhead Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MNT-011</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LGT-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Overhead Light</x:t>
+    <x:t xml:space="preserve">MNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tripods, stands, arms and mounting equipment</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Lighting</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">NEEWER</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BASICS BP66</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Overhead light supplied as part of a two-pack</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://m.media-amazon.com/images/I/61Gj-qwZzvL._AC_SL1500_.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LGT-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AUD-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boya Lavalier set of 4</x:t>
+    <x:t xml:space="preserve">LGT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lighting equipment</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Audio equipment</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">BOYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BY-V4U</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Four-channel wireless lavalier microphone set</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://m.media-amazon.com/images/I/71YjX9o83LL._AC_SL1500_.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AUD-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DJI Mic Mini Lavalier set of 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/dji-mic-mini.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PWR-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Extension Power Cord (Longer cord)</x:t>
+    <x:t xml:space="preserve">AUD</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Microphones and other audio equipment</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Power and connectivity</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">PWR-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PWR-003</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Extension Power Cord (more sockets)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/belkin-bsv804.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PWR-004</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Smart Wi-Fi Socket Switch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/tapo-p110.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STO-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">File Organiser</x:t>
+    <x:t xml:space="preserve">PWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Power distribution, sockets, cables and connectivity</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Storage and organisation</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">SupaFile</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1622</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">26-part desktop expanding file organiser</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SQ550189 / 1622</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://ik.imagekit.io/pimberly/595e406f0f15f30010780448/tr:w-1000,h-1000,cm-pad_resize/f8d4d464/5d4d73a880150e75f70001de.jpg?product_name=Rapesco-Supafile-Plus-Expanding-File-A4-Assorted-1552.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STO-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CAM-005</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Logitech C920 Webcam</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Logitech</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">C920</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Full HD webcam; product code 960-001055</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SQ550189 / 960-001055</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://resource.logitech.com/w_544%2Ch_466%2Car_7%3A6%2Cc_pad%2Cq_auto%2Cf_auto%2Cdpr_1.0/d_transparent.gif/content/dam/logitech/en/products/webcams/c920s/gallery/c920s-gallery-1.png</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CAM-006</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EMEET NOVA 4K Webcam</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EMEET</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NOVA 4K</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">4K webcam, PDAF autofocus, dual noise-cancelling microphones and 73-degree field of view</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SQ550189 / E3131</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://emeet.com/cdn/shop/files/nova.png?v=1687780101&amp;width=1200</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TAB-003</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Lenovo Idea Tab Pro 12.7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Lenovo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ZAE40036GB</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">12.7-inch LTPS display and 256 GB storage</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SQ550189 / ZAE40036GB</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://p2-ofp.static.pub/ShareResource/we/images/PN-list-image/Lenovo-Idea-Tab-Pro.png?height=584&amp;width=584</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TAB-004</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TAB-005</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Lenovo Idea Tab 11</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ZAFR0384GB</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">11-inch tablet</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SQ550189 / ZAFR0384GB</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://p4-ofp.static.pub/ShareResource/we/Idea_Tab/Lenovo-Idea-Tab--400x300.png</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MNT-012</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tablet Holder</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">G3023</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Holder for 4-inch to 12.9-inch tablets</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SQ550189 / G3023</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STO-003</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STO-004</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Seagate Portable 1 TB External Hard Drive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Seagate</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STGX1000400</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 TB portable external hard drive with USB 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SQ550189 / STGX1000400</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.seagate.com/content/dam/seagate/assets/products/external-hard-drives/portable-drive/1-seagate-portable-drive-2.5-front-hi-res-PhotoRoom.png/_jcr_content/renditions/1-1-large-640x640.png</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STO-005</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STO-006</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STO-007</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ModusTech 500 GB Portable External Hard Drive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ModusTech</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MT500</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">500 GB portable external hard drive with USB 3.0 and USB-C</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SQ550189 / MT500</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://image.review-rating.com/xNzF6eVU4RXRzaEw_WIDTH200.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STO-008</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STO-009</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CMP-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">HP Pro Mini 400 G9</x:t>
+    <x:t xml:space="preserve">STO</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Storage and organisational equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Other accessories</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ACC</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Accessories that do not fit another category</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Computers</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">HP</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">623W7ET#ABU</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Intel Core i5-13500T, 8 GB RAM, 256 GB storage and Windows 11 Pro</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SQ550189 / 623W7ET#ABU</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://media.box.co.uk/product/0/0/00ed038f0c0de034de0918539cc9c6f9.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CMP-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">component_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">quantity</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">required_on_return</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">notes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">username</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">display_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">active</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">n.salomons</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Nicole</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Yes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">e.akinrintoyo23</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Emmanuel</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">s.shahin25</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Shahrooz</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">rht25</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Ranul</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">haiwei.luo25</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Haiwei</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ana.nikolova26</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Ana</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">asset_code_prefix</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">description</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ROB</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Robots and embodied robotic platforms</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tablets and mobile computing devices</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cameras</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cameras, webcams and depth sensors</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tripods, stands, arms and mounting equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LGT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Lighting equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AUD</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Microphones and other audio equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Power distribution, sockets, cables and connectivity</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STO</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Storage and organisational equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Other accessories</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ACC</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Accessories that do not fit another category</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">CMP</x:t>
@@ -1253,7 +824,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="6" t="str">
-        <x:v>78 unique equipment units are included. One asset code is used for each physical unit or complete bundle.</x:v>
+        <x:v>77 unique equipment units are included. One asset code is used for each physical unit or complete bundle.</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="D4" s="4"/>
@@ -1521,17 +1092,17 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="25">
-      <x:c r="A2" s="9" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B2" s="10" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C2" s="10" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D2" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="A2" s="9" t="str">
+        <x:v>ROB-001</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="str">
+        <x:v>Misty Robot</x:v>
+      </x:c>
+      <x:c r="C2" s="10" t="str">
+        <x:v>Robots</x:v>
+      </x:c>
+      <x:c r="D2" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E2" s="4"/>
       <x:c r="F2" s="4"/>
@@ -1539,13 +1110,13 @@
       <x:c r="H2" s="11"/>
       <x:c r="I2" s="11"/>
       <x:c r="J2" s="11"/>
-      <x:c r="K2" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K2" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L2" s="13"/>
       <x:c r="M2" s="14"/>
-      <x:c r="N2" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N2" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O2" s="11"/>
       <x:c r="P2" s="11"/>
@@ -1554,22 +1125,22 @@
       <x:c r="S2" s="11"/>
       <x:c r="T2" s="11"/>
       <x:c r="U2" s="11"/>
-      <x:c r="V2" s="11" t="s">
-        <x:v>53</x:v>
+      <x:c r="V2" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/misty-ii.png</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="25">
-      <x:c r="A3" s="9" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C3" s="10" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D3" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="A3" s="9" t="str">
+        <x:v>ROB-002</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="str">
+        <x:v>Misty Robot</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="str">
+        <x:v>Robots</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E3" s="4"/>
       <x:c r="F3" s="4"/>
@@ -1577,13 +1148,13 @@
       <x:c r="H3" s="11"/>
       <x:c r="I3" s="11"/>
       <x:c r="J3" s="11"/>
-      <x:c r="K3" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K3" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L3" s="13"/>
       <x:c r="M3" s="14"/>
-      <x:c r="N3" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N3" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O3" s="11"/>
       <x:c r="P3" s="11"/>
@@ -1592,42 +1163,42 @@
       <x:c r="S3" s="11"/>
       <x:c r="T3" s="11"/>
       <x:c r="U3" s="11"/>
-      <x:c r="V3" s="11" t="s">
-        <x:v>53</x:v>
+      <x:c r="V3" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/misty-ii.png</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="37.5">
-      <x:c r="A4" s="9" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B4" s="10" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C4" s="10" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D4" s="10" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="s">
-        <x:v>56</x:v>
+      <x:c r="A4" s="9" t="str">
+        <x:v>ROB-003</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>Reachy Mini Wireless</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>Robots</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="str">
+        <x:v>Bundle</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="str">
+        <x:v>Pollen Robotics</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="str">
+        <x:v>Reachy Mini Wireless</x:v>
       </x:c>
       <x:c r="G4" s="4"/>
       <x:c r="H4" s="11"/>
       <x:c r="I4" s="11"/>
       <x:c r="J4" s="11"/>
-      <x:c r="K4" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K4" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L4" s="13"/>
-      <x:c r="M4" s="14">
+      <x:c r="M4" s="14" t="n">
         <x:v>439.93</x:v>
       </x:c>
-      <x:c r="N4" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N4" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O4" s="11"/>
       <x:c r="P4" s="11"/>
@@ -1635,45 +1206,45 @@
       <x:c r="R4" s="11"/>
       <x:c r="S4" s="11"/>
       <x:c r="T4" s="11"/>
-      <x:c r="U4" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="V4" s="11" t="s">
-        <x:v>60</x:v>
+      <x:c r="U4" s="11" t="str">
+        <x:v>SQ550205 / REACHY-MIN-WLS</x:v>
+      </x:c>
+      <x:c r="V4" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="37.5">
-      <x:c r="A5" s="9" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B5" s="10" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F5" s="4" t="s">
-        <x:v>62</x:v>
+      <x:c r="A5" s="9" t="str">
+        <x:v>ROB-004</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>Reachy Mini Lite</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="str">
+        <x:v>Robots</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="str">
+        <x:v>Bundle</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="str">
+        <x:v>Pollen Robotics</x:v>
+      </x:c>
+      <x:c r="F5" s="4" t="str">
+        <x:v>Reachy Mini Lite</x:v>
       </x:c>
       <x:c r="G5" s="4"/>
       <x:c r="H5" s="11"/>
       <x:c r="I5" s="11"/>
       <x:c r="J5" s="11"/>
-      <x:c r="K5" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K5" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L5" s="13"/>
-      <x:c r="M5" s="14">
-        <x:v>302.16000000000003</x:v>
-      </x:c>
-      <x:c r="N5" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="M5" s="14" t="n">
+        <x:v>302.16</x:v>
+      </x:c>
+      <x:c r="N5" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O5" s="11"/>
       <x:c r="P5" s="11"/>
@@ -1681,25 +1252,25 @@
       <x:c r="R5" s="11"/>
       <x:c r="S5" s="11"/>
       <x:c r="T5" s="11"/>
-      <x:c r="U5" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="V5" s="11" t="s">
-        <x:v>64</x:v>
+      <x:c r="U5" s="11" t="str">
+        <x:v>SQ550205 / PR-RML</x:v>
+      </x:c>
+      <x:c r="V5" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-lite.png</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="37.5">
-      <x:c r="A6" s="9" t="s">
-        <x:v>65</x:v>
+      <x:c r="A6" s="9" t="str">
+        <x:v>ROB-005</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
         <x:v>Reachy Mini Wireless</x:v>
       </x:c>
-      <x:c r="C6" s="10" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D6" s="10" t="s">
-        <x:v>57</x:v>
+      <x:c r="C6" s="10" t="str">
+        <x:v>Robots</x:v>
+      </x:c>
+      <x:c r="D6" s="10" t="str">
+        <x:v>Bundle</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
         <x:v>Pollen Robotics</x:v>
@@ -1713,13 +1284,13 @@
       </x:c>
       <x:c r="I6" s="11"/>
       <x:c r="J6" s="11"/>
-      <x:c r="K6" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K6" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L6" s="13"/>
       <x:c r="M6" s="14"/>
-      <x:c r="N6" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N6" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O6" s="11"/>
       <x:c r="P6" s="11"/>
@@ -1733,20 +1304,20 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="37.5">
-      <x:c r="A7" s="9" t="s">
-        <x:v>66</x:v>
+      <x:c r="A7" s="9" t="str">
+        <x:v>ROB-006</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
         <x:v>Reachy Mini Wireless</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D7" s="10" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E7" s="4" t="s">
-        <x:v>58</x:v>
+      <x:c r="C7" s="10" t="str">
+        <x:v>Robots</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="str">
+        <x:v>Bundle</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="str">
+        <x:v>Pollen Robotics</x:v>
       </x:c>
       <x:c r="F7" s="4" t="str">
         <x:v>Reachy Mini Wireless</x:v>
@@ -1757,13 +1328,13 @@
       </x:c>
       <x:c r="I7" s="11"/>
       <x:c r="J7" s="11"/>
-      <x:c r="K7" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K7" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L7" s="13"/>
       <x:c r="M7" s="14"/>
-      <x:c r="N7" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N7" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O7" s="11"/>
       <x:c r="P7" s="11"/>
@@ -1777,17 +1348,17 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="37.5">
-      <x:c r="A8" s="9" t="s">
-        <x:v>67</x:v>
+      <x:c r="A8" s="9" t="str">
+        <x:v>TAB-001</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
         <x:v>Lenovo Tab M10 (3rd Gen)</x:v>
       </x:c>
-      <x:c r="C8" s="10" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D8" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="C8" s="10" t="str">
+        <x:v>Tablets</x:v>
+      </x:c>
+      <x:c r="D8" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
         <x:v>Lenovo</x:v>
@@ -1801,13 +1372,13 @@
       </x:c>
       <x:c r="I8" s="11"/>
       <x:c r="J8" s="11"/>
-      <x:c r="K8" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K8" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L8" s="13"/>
       <x:c r="M8" s="14"/>
-      <x:c r="N8" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N8" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O8" s="11"/>
       <x:c r="P8" s="11"/>
@@ -1816,22 +1387,22 @@
       <x:c r="S8" s="11"/>
       <x:c r="T8" s="11"/>
       <x:c r="U8" s="11"/>
-      <x:c r="V8" s="11" t="s">
-        <x:v>69</x:v>
+      <x:c r="V8" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/lenovo-tab-m10-gen3.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="37.5">
-      <x:c r="A9" s="9" t="s">
-        <x:v>70</x:v>
+      <x:c r="A9" s="9" t="str">
+        <x:v>TAB-002</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
         <x:v>Lenovo Tab M10 (3rd Gen)</x:v>
       </x:c>
-      <x:c r="C9" s="10" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D9" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="C9" s="10" t="str">
+        <x:v>Tablets</x:v>
+      </x:c>
+      <x:c r="D9" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
         <x:v>Lenovo</x:v>
@@ -1845,13 +1416,13 @@
       </x:c>
       <x:c r="I9" s="11"/>
       <x:c r="J9" s="11"/>
-      <x:c r="K9" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K9" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L9" s="13"/>
       <x:c r="M9" s="14"/>
-      <x:c r="N9" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N9" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O9" s="11"/>
       <x:c r="P9" s="11"/>
@@ -1860,22 +1431,22 @@
       <x:c r="S9" s="11"/>
       <x:c r="T9" s="11"/>
       <x:c r="U9" s="11"/>
-      <x:c r="V9" s="11" t="s">
-        <x:v>69</x:v>
+      <x:c r="V9" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/lenovo-tab-m10-gen3.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="37.5">
-      <x:c r="A10" s="9" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B10" s="10" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C10" s="10" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D10" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="A10" s="9" t="str">
+        <x:v>MNT-001</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>Tablet Stand</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D10" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E10" s="4"/>
       <x:c r="F10" s="4"/>
@@ -1883,13 +1454,13 @@
       <x:c r="H10" s="11"/>
       <x:c r="I10" s="11"/>
       <x:c r="J10" s="11"/>
-      <x:c r="K10" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K10" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L10" s="13"/>
       <x:c r="M10" s="14"/>
-      <x:c r="N10" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N10" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O10" s="11"/>
       <x:c r="P10" s="11"/>
@@ -1898,22 +1469,22 @@
       <x:c r="S10" s="11"/>
       <x:c r="T10" s="11"/>
       <x:c r="U10" s="11"/>
-      <x:c r="V10" s="11" t="s">
-        <x:v>69</x:v>
+      <x:c r="V10" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="37.5">
-      <x:c r="A11" s="9" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B11" s="10" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C11" s="10" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D11" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="A11" s="9" t="str">
+        <x:v>MNT-002</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>Tablet Stand</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E11" s="4"/>
       <x:c r="F11" s="4"/>
@@ -1921,13 +1492,13 @@
       <x:c r="H11" s="11"/>
       <x:c r="I11" s="11"/>
       <x:c r="J11" s="11"/>
-      <x:c r="K11" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K11" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L11" s="13"/>
       <x:c r="M11" s="14"/>
-      <x:c r="N11" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N11" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O11" s="11"/>
       <x:c r="P11" s="11"/>
@@ -1936,22 +1507,22 @@
       <x:c r="S11" s="11"/>
       <x:c r="T11" s="11"/>
       <x:c r="U11" s="11"/>
-      <x:c r="V11" s="11" t="s">
-        <x:v>69</x:v>
+      <x:c r="V11" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="37.5">
-      <x:c r="A12" s="9" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B12" s="10" t="s">
-        <x:v>76</x:v>
+      <x:c r="A12" s="9" t="str">
+        <x:v>CAM-001</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>Azure Kinect DK</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
         <x:v>Cameras</x:v>
       </x:c>
-      <x:c r="D12" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="D12" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E12" s="4"/>
       <x:c r="F12" s="4"/>
@@ -1959,13 +1530,13 @@
       <x:c r="H12" s="11"/>
       <x:c r="I12" s="11"/>
       <x:c r="J12" s="11"/>
-      <x:c r="K12" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K12" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L12" s="13"/>
       <x:c r="M12" s="14"/>
-      <x:c r="N12" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N12" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O12" s="11"/>
       <x:c r="P12" s="11"/>
@@ -1974,22 +1545,22 @@
       <x:c r="S12" s="11"/>
       <x:c r="T12" s="11"/>
       <x:c r="U12" s="11"/>
-      <x:c r="V12" s="11" t="s">
-        <x:v>77</x:v>
+      <x:c r="V12" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/azure-kinect-dk.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="37.5">
-      <x:c r="A13" s="9" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B13" s="10" t="s">
-        <x:v>76</x:v>
+      <x:c r="A13" s="9" t="str">
+        <x:v>CAM-002</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>Azure Kinect DK</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
         <x:v>Cameras</x:v>
       </x:c>
-      <x:c r="D13" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="D13" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
@@ -1997,13 +1568,13 @@
       <x:c r="H13" s="11"/>
       <x:c r="I13" s="11"/>
       <x:c r="J13" s="11"/>
-      <x:c r="K13" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K13" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L13" s="13"/>
       <x:c r="M13" s="14"/>
-      <x:c r="N13" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N13" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O13" s="11"/>
       <x:c r="P13" s="11"/>
@@ -2012,44 +1583,44 @@
       <x:c r="S13" s="11"/>
       <x:c r="T13" s="11"/>
       <x:c r="U13" s="11"/>
-      <x:c r="V13" s="11" t="s">
-        <x:v>77</x:v>
+      <x:c r="V13" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/azure-kinect-dk.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="37.5">
-      <x:c r="A14" s="9" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B14" s="10" t="s">
-        <x:v>80</x:v>
+      <x:c r="A14" s="9" t="str">
+        <x:v>CAM-003</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>Anker PowerConf C200</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
         <x:v>Cameras</x:v>
       </x:c>
-      <x:c r="D14" s="10" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E14" s="4" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F14" s="4" t="s">
-        <x:v>82</x:v>
+      <x:c r="D14" s="10" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E14" s="4" t="str">
+        <x:v>Anker</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="str">
+        <x:v>C200</x:v>
       </x:c>
       <x:c r="G14" s="4"/>
-      <x:c r="H14" s="11" t="s">
-        <x:v>83</x:v>
+      <x:c r="H14" s="11" t="str">
+        <x:v>2K webcam</x:v>
       </x:c>
       <x:c r="I14" s="11"/>
       <x:c r="J14" s="11"/>
-      <x:c r="K14" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K14" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L14" s="13"/>
-      <x:c r="M14" s="14">
+      <x:c r="M14" s="14" t="n">
         <x:v>43.81</x:v>
       </x:c>
-      <x:c r="N14" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N14" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O14" s="11"/>
       <x:c r="P14" s="11"/>
@@ -2057,47 +1628,47 @@
       <x:c r="R14" s="11"/>
       <x:c r="S14" s="11"/>
       <x:c r="T14" s="11"/>
-      <x:c r="U14" s="11" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="V14" s="11" t="s">
-        <x:v>85</x:v>
+      <x:c r="U14" s="11" t="str">
+        <x:v>SQ550189 / A3369011</x:v>
+      </x:c>
+      <x:c r="V14" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/anker-powerconf-c200.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="37.5">
-      <x:c r="A15" s="9" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B15" s="10" t="s">
-        <x:v>80</x:v>
+      <x:c r="A15" s="9" t="str">
+        <x:v>CAM-004</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>Anker PowerConf C200</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
         <x:v>Cameras</x:v>
       </x:c>
-      <x:c r="D15" s="10" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E15" s="4" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F15" s="4" t="s">
-        <x:v>82</x:v>
+      <x:c r="D15" s="10" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E15" s="4" t="str">
+        <x:v>Anker</x:v>
+      </x:c>
+      <x:c r="F15" s="4" t="str">
+        <x:v>C200</x:v>
       </x:c>
       <x:c r="G15" s="4"/>
-      <x:c r="H15" s="11" t="s">
-        <x:v>83</x:v>
+      <x:c r="H15" s="11" t="str">
+        <x:v>2K webcam</x:v>
       </x:c>
       <x:c r="I15" s="11"/>
       <x:c r="J15" s="11"/>
-      <x:c r="K15" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K15" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L15" s="13"/>
-      <x:c r="M15" s="14">
+      <x:c r="M15" s="14" t="n">
         <x:v>43.81</x:v>
       </x:c>
-      <x:c r="N15" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N15" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O15" s="11"/>
       <x:c r="P15" s="11"/>
@@ -2105,25 +1676,25 @@
       <x:c r="R15" s="11"/>
       <x:c r="S15" s="11"/>
       <x:c r="T15" s="11"/>
-      <x:c r="U15" s="11" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="V15" s="11" t="s">
-        <x:v>85</x:v>
+      <x:c r="U15" s="11" t="str">
+        <x:v>SQ550189 / A3369011</x:v>
+      </x:c>
+      <x:c r="V15" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/anker-powerconf-c200.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="37.5">
-      <x:c r="A16" s="9" t="s">
-        <x:v>87</x:v>
+      <x:c r="A16" s="9" t="str">
+        <x:v>MNT-003</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
         <x:v>PEMOTech Tripod</x:v>
       </x:c>
-      <x:c r="C16" s="10" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D16" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="C16" s="10" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D16" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
         <x:v>PEMOTech</x:v>
@@ -2133,13 +1704,13 @@
       <x:c r="H16" s="11"/>
       <x:c r="I16" s="11"/>
       <x:c r="J16" s="11"/>
-      <x:c r="K16" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K16" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L16" s="13"/>
       <x:c r="M16" s="14"/>
-      <x:c r="N16" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N16" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O16" s="11"/>
       <x:c r="P16" s="11"/>
@@ -2148,22 +1719,22 @@
       <x:c r="S16" s="11"/>
       <x:c r="T16" s="11"/>
       <x:c r="U16" s="11"/>
-      <x:c r="V16" s="11" t="s">
-        <x:v>88</x:v>
+      <x:c r="V16" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/victiv-tripod.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="37.5">
-      <x:c r="A17" s="9" t="s">
-        <x:v>89</x:v>
+      <x:c r="A17" s="9" t="str">
+        <x:v>MNT-004</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
         <x:v>Victiv Tripod</x:v>
       </x:c>
-      <x:c r="C17" s="10" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D17" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="C17" s="10" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
         <x:v>Victiv</x:v>
@@ -2175,13 +1746,13 @@
       <x:c r="H17" s="11"/>
       <x:c r="I17" s="11"/>
       <x:c r="J17" s="11"/>
-      <x:c r="K17" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K17" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L17" s="13"/>
       <x:c r="M17" s="14"/>
-      <x:c r="N17" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N17" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O17" s="11"/>
       <x:c r="P17" s="11"/>
@@ -2190,22 +1761,22 @@
       <x:c r="S17" s="11"/>
       <x:c r="T17" s="11"/>
       <x:c r="U17" s="11"/>
-      <x:c r="V17" s="11" t="s">
-        <x:v>88</x:v>
+      <x:c r="V17" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/victiv-tripod.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="37.5">
-      <x:c r="A18" s="9" t="s">
-        <x:v>90</x:v>
+      <x:c r="A18" s="9" t="str">
+        <x:v>MNT-005</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
         <x:v>K&amp;F Tripod</x:v>
       </x:c>
-      <x:c r="C18" s="10" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D18" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="C18" s="10" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D18" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
         <x:v>K&amp;F Concept</x:v>
@@ -2217,13 +1788,13 @@
       <x:c r="H18" s="11"/>
       <x:c r="I18" s="11"/>
       <x:c r="J18" s="11"/>
-      <x:c r="K18" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K18" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L18" s="13"/>
       <x:c r="M18" s="14"/>
-      <x:c r="N18" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N18" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O18" s="11"/>
       <x:c r="P18" s="11"/>
@@ -2232,22 +1803,22 @@
       <x:c r="S18" s="11"/>
       <x:c r="T18" s="11"/>
       <x:c r="U18" s="11"/>
-      <x:c r="V18" s="11" t="s">
-        <x:v>88</x:v>
+      <x:c r="V18" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/victiv-tripod.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="37.5">
-      <x:c r="A19" s="9" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B19" s="10" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C19" s="10" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D19" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="A19" s="9" t="str">
+        <x:v>MNT-006</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="str">
+        <x:v>Flexible Small Tripod</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D19" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E19" s="4"/>
       <x:c r="F19" s="4"/>
@@ -2255,13 +1826,13 @@
       <x:c r="H19" s="11"/>
       <x:c r="I19" s="11"/>
       <x:c r="J19" s="11"/>
-      <x:c r="K19" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K19" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L19" s="13"/>
       <x:c r="M19" s="14"/>
-      <x:c r="N19" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N19" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O19" s="11"/>
       <x:c r="P19" s="11"/>
@@ -2270,22 +1841,22 @@
       <x:c r="S19" s="11"/>
       <x:c r="T19" s="11"/>
       <x:c r="U19" s="11"/>
-      <x:c r="V19" s="11" t="s">
-        <x:v>69</x:v>
+      <x:c r="V19" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="37.5">
-      <x:c r="A20" s="9" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B20" s="10" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C20" s="10" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D20" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="A20" s="9" t="str">
+        <x:v>MNT-007</x:v>
+      </x:c>
+      <x:c r="B20" s="10" t="str">
+        <x:v>Flexible Small Tripod</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D20" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E20" s="4"/>
       <x:c r="F20" s="4"/>
@@ -2293,13 +1864,13 @@
       <x:c r="H20" s="11"/>
       <x:c r="I20" s="11"/>
       <x:c r="J20" s="11"/>
-      <x:c r="K20" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K20" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L20" s="13"/>
       <x:c r="M20" s="14"/>
-      <x:c r="N20" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N20" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O20" s="11"/>
       <x:c r="P20" s="11"/>
@@ -2308,22 +1879,22 @@
       <x:c r="S20" s="11"/>
       <x:c r="T20" s="11"/>
       <x:c r="U20" s="11"/>
-      <x:c r="V20" s="11" t="s">
-        <x:v>69</x:v>
+      <x:c r="V20" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="37.5">
-      <x:c r="A21" s="9" t="s">
-        <x:v>94</x:v>
+      <x:c r="A21" s="9" t="str">
+        <x:v>MNT-008</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
         <x:v>Unbranded Three-Stage Tripod</x:v>
       </x:c>
-      <x:c r="C21" s="10" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D21" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="C21" s="10" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D21" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
         <x:v>Unbranded</x:v>
@@ -2333,13 +1904,13 @@
       <x:c r="H21" s="11"/>
       <x:c r="I21" s="11"/>
       <x:c r="J21" s="11"/>
-      <x:c r="K21" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K21" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L21" s="13"/>
       <x:c r="M21" s="14"/>
-      <x:c r="N21" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N21" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O21" s="11"/>
       <x:c r="P21" s="11"/>
@@ -2348,22 +1919,22 @@
       <x:c r="S21" s="11"/>
       <x:c r="T21" s="11"/>
       <x:c r="U21" s="11"/>
-      <x:c r="V21" s="11" t="s">
-        <x:v>95</x:v>
+      <x:c r="V21" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/lammcou-small-tripod.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="37.5">
-      <x:c r="A22" s="9" t="s">
-        <x:v>96</x:v>
+      <x:c r="A22" s="9" t="str">
+        <x:v>MNT-009</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
         <x:v>Unbranded Three-Stage Tripod</x:v>
       </x:c>
-      <x:c r="C22" s="10" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D22" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="C22" s="10" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D22" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
         <x:v>Unbranded</x:v>
@@ -2373,13 +1944,13 @@
       <x:c r="H22" s="11"/>
       <x:c r="I22" s="11"/>
       <x:c r="J22" s="11"/>
-      <x:c r="K22" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K22" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L22" s="13"/>
       <x:c r="M22" s="14"/>
-      <x:c r="N22" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N22" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O22" s="11"/>
       <x:c r="P22" s="11"/>
@@ -2388,22 +1959,22 @@
       <x:c r="S22" s="11"/>
       <x:c r="T22" s="11"/>
       <x:c r="U22" s="11"/>
-      <x:c r="V22" s="11" t="s">
-        <x:v>95</x:v>
+      <x:c r="V22" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/lammcou-small-tripod.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="37.5">
-      <x:c r="A23" s="9" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B23" s="10" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C23" s="10" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D23" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="A23" s="9" t="str">
+        <x:v>MNT-010</x:v>
+      </x:c>
+      <x:c r="B23" s="10" t="str">
+        <x:v>Overhead Mount</x:v>
+      </x:c>
+      <x:c r="C23" s="10" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D23" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E23" s="4"/>
       <x:c r="F23" s="4"/>
@@ -2411,13 +1982,13 @@
       <x:c r="H23" s="11"/>
       <x:c r="I23" s="11"/>
       <x:c r="J23" s="11"/>
-      <x:c r="K23" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K23" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L23" s="13"/>
       <x:c r="M23" s="14"/>
-      <x:c r="N23" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N23" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O23" s="11"/>
       <x:c r="P23" s="11"/>
@@ -2426,22 +1997,22 @@
       <x:c r="S23" s="11"/>
       <x:c r="T23" s="11"/>
       <x:c r="U23" s="11"/>
-      <x:c r="V23" s="11" t="s">
-        <x:v>69</x:v>
+      <x:c r="V23" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="37.5">
-      <x:c r="A24" s="9" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B24" s="10" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C24" s="10" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D24" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="A24" s="9" t="str">
+        <x:v>MNT-011</x:v>
+      </x:c>
+      <x:c r="B24" s="10" t="str">
+        <x:v>Overhead Mount</x:v>
+      </x:c>
+      <x:c r="C24" s="10" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D24" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E24" s="4"/>
       <x:c r="F24" s="4"/>
@@ -2449,13 +2020,13 @@
       <x:c r="H24" s="11"/>
       <x:c r="I24" s="11"/>
       <x:c r="J24" s="11"/>
-      <x:c r="K24" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K24" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L24" s="13"/>
       <x:c r="M24" s="14"/>
-      <x:c r="N24" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N24" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O24" s="11"/>
       <x:c r="P24" s="11"/>
@@ -2464,42 +2035,42 @@
       <x:c r="S24" s="11"/>
       <x:c r="T24" s="11"/>
       <x:c r="U24" s="11"/>
-      <x:c r="V24" s="11" t="s">
-        <x:v>69</x:v>
+      <x:c r="V24" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="37.5">
-      <x:c r="A25" s="9" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B25" s="10" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C25" s="10" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D25" s="10" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E25" s="4" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F25" s="4" t="s">
-        <x:v>104</x:v>
+      <x:c r="A25" s="9" t="str">
+        <x:v>LGT-001</x:v>
+      </x:c>
+      <x:c r="B25" s="10" t="str">
+        <x:v>Overhead Light</x:v>
+      </x:c>
+      <x:c r="C25" s="10" t="str">
+        <x:v>Lighting</x:v>
+      </x:c>
+      <x:c r="D25" s="10" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E25" s="4" t="str">
+        <x:v>NEEWER</x:v>
+      </x:c>
+      <x:c r="F25" s="4" t="str">
+        <x:v>BASICS BP66</x:v>
       </x:c>
       <x:c r="G25" s="4"/>
-      <x:c r="H25" s="11" t="s">
-        <x:v>105</x:v>
+      <x:c r="H25" s="11" t="str">
+        <x:v>Overhead light supplied as part of a two-pack</x:v>
       </x:c>
       <x:c r="I25" s="11"/>
       <x:c r="J25" s="11"/>
-      <x:c r="K25" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K25" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L25" s="13"/>
       <x:c r="M25" s="14"/>
-      <x:c r="N25" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N25" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O25" s="11"/>
       <x:c r="P25" s="11"/>
@@ -2508,42 +2079,42 @@
       <x:c r="S25" s="11"/>
       <x:c r="T25" s="11"/>
       <x:c r="U25" s="11"/>
-      <x:c r="V25" s="11" t="s">
-        <x:v>106</x:v>
+      <x:c r="V25" s="11" t="str">
+        <x:v>https://m.media-amazon.com/images/I/61Gj-qwZzvL._AC_SL1500_.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="37.5">
-      <x:c r="A26" s="9" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="B26" s="10" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C26" s="10" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D26" s="10" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E26" s="4" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F26" s="4" t="s">
-        <x:v>104</x:v>
+      <x:c r="A26" s="9" t="str">
+        <x:v>LGT-002</x:v>
+      </x:c>
+      <x:c r="B26" s="10" t="str">
+        <x:v>Overhead Light</x:v>
+      </x:c>
+      <x:c r="C26" s="10" t="str">
+        <x:v>Lighting</x:v>
+      </x:c>
+      <x:c r="D26" s="10" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E26" s="4" t="str">
+        <x:v>NEEWER</x:v>
+      </x:c>
+      <x:c r="F26" s="4" t="str">
+        <x:v>BASICS BP66</x:v>
       </x:c>
       <x:c r="G26" s="4"/>
-      <x:c r="H26" s="11" t="s">
-        <x:v>105</x:v>
+      <x:c r="H26" s="11" t="str">
+        <x:v>Overhead light supplied as part of a two-pack</x:v>
       </x:c>
       <x:c r="I26" s="11"/>
       <x:c r="J26" s="11"/>
-      <x:c r="K26" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K26" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L26" s="13"/>
       <x:c r="M26" s="14"/>
-      <x:c r="N26" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N26" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O26" s="11"/>
       <x:c r="P26" s="11"/>
@@ -2552,42 +2123,42 @@
       <x:c r="S26" s="11"/>
       <x:c r="T26" s="11"/>
       <x:c r="U26" s="11"/>
-      <x:c r="V26" s="11" t="s">
-        <x:v>106</x:v>
+      <x:c r="V26" s="11" t="str">
+        <x:v>https://m.media-amazon.com/images/I/61Gj-qwZzvL._AC_SL1500_.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="37.5">
-      <x:c r="A27" s="9" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="B27" s="10" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="C27" s="10" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D27" s="10" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E27" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F27" s="4" t="s">
-        <x:v>112</x:v>
+      <x:c r="A27" s="9" t="str">
+        <x:v>AUD-001</x:v>
+      </x:c>
+      <x:c r="B27" s="10" t="str">
+        <x:v>Boya Lavalier set of 4</x:v>
+      </x:c>
+      <x:c r="C27" s="10" t="str">
+        <x:v>Audio equipment</x:v>
+      </x:c>
+      <x:c r="D27" s="10" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E27" s="4" t="str">
+        <x:v>BOYA</x:v>
+      </x:c>
+      <x:c r="F27" s="4" t="str">
+        <x:v>BY-V4U</x:v>
       </x:c>
       <x:c r="G27" s="4"/>
-      <x:c r="H27" s="11" t="s">
-        <x:v>113</x:v>
+      <x:c r="H27" s="11" t="str">
+        <x:v>Four-channel wireless lavalier microphone set</x:v>
       </x:c>
       <x:c r="I27" s="11"/>
       <x:c r="J27" s="11"/>
-      <x:c r="K27" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K27" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L27" s="13"/>
       <x:c r="M27" s="14"/>
-      <x:c r="N27" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N27" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O27" s="11"/>
       <x:c r="P27" s="11"/>
@@ -2596,22 +2167,22 @@
       <x:c r="S27" s="11"/>
       <x:c r="T27" s="11"/>
       <x:c r="U27" s="11"/>
-      <x:c r="V27" s="11" t="s">
-        <x:v>114</x:v>
+      <x:c r="V27" s="11" t="str">
+        <x:v>https://m.media-amazon.com/images/I/71YjX9o83LL._AC_SL1500_.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="37.5">
-      <x:c r="A28" s="9" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="B28" s="10" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="C28" s="10" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D28" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="A28" s="9" t="str">
+        <x:v>AUD-002</x:v>
+      </x:c>
+      <x:c r="B28" s="10" t="str">
+        <x:v>DJI Mic Mini Lavalier set of 2</x:v>
+      </x:c>
+      <x:c r="C28" s="10" t="str">
+        <x:v>Audio equipment</x:v>
+      </x:c>
+      <x:c r="D28" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E28" s="4"/>
       <x:c r="F28" s="4"/>
@@ -2619,13 +2190,13 @@
       <x:c r="H28" s="11"/>
       <x:c r="I28" s="11"/>
       <x:c r="J28" s="11"/>
-      <x:c r="K28" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K28" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L28" s="13"/>
       <x:c r="M28" s="14"/>
-      <x:c r="N28" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N28" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O28" s="11"/>
       <x:c r="P28" s="11"/>
@@ -2634,22 +2205,22 @@
       <x:c r="S28" s="11"/>
       <x:c r="T28" s="11"/>
       <x:c r="U28" s="11"/>
-      <x:c r="V28" s="11" t="s">
-        <x:v>117</x:v>
+      <x:c r="V28" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/dji-mic-mini.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="37.5">
-      <x:c r="A29" s="9" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="B29" s="10" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C29" s="10" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D29" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="A29" s="9" t="str">
+        <x:v>PWR-001</x:v>
+      </x:c>
+      <x:c r="B29" s="10" t="str">
+        <x:v>Extension Power Cord (Longer cord)</x:v>
+      </x:c>
+      <x:c r="C29" s="10" t="str">
+        <x:v>Power and connectivity</x:v>
+      </x:c>
+      <x:c r="D29" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E29" s="4"/>
       <x:c r="F29" s="4"/>
@@ -2657,13 +2228,13 @@
       <x:c r="H29" s="11"/>
       <x:c r="I29" s="11"/>
       <x:c r="J29" s="11"/>
-      <x:c r="K29" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K29" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L29" s="13"/>
       <x:c r="M29" s="14"/>
-      <x:c r="N29" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N29" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O29" s="11"/>
       <x:c r="P29" s="11"/>
@@ -2672,22 +2243,22 @@
       <x:c r="S29" s="11"/>
       <x:c r="T29" s="11"/>
       <x:c r="U29" s="11"/>
-      <x:c r="V29" s="11" t="s">
-        <x:v>69</x:v>
+      <x:c r="V29" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="37.5">
-      <x:c r="A30" s="9" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="B30" s="10" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C30" s="10" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D30" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="A30" s="9" t="str">
+        <x:v>PWR-002</x:v>
+      </x:c>
+      <x:c r="B30" s="10" t="str">
+        <x:v>Extension Power Cord (Longer cord)</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="str">
+        <x:v>Power and connectivity</x:v>
+      </x:c>
+      <x:c r="D30" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E30" s="4"/>
       <x:c r="F30" s="4"/>
@@ -2695,13 +2266,13 @@
       <x:c r="H30" s="11"/>
       <x:c r="I30" s="11"/>
       <x:c r="J30" s="11"/>
-      <x:c r="K30" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K30" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L30" s="13"/>
       <x:c r="M30" s="14"/>
-      <x:c r="N30" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N30" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O30" s="11"/>
       <x:c r="P30" s="11"/>
@@ -2710,22 +2281,22 @@
       <x:c r="S30" s="11"/>
       <x:c r="T30" s="11"/>
       <x:c r="U30" s="11"/>
-      <x:c r="V30" s="11" t="s">
-        <x:v>69</x:v>
+      <x:c r="V30" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="37.5">
-      <x:c r="A31" s="9" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="B31" s="10" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="C31" s="10" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D31" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="A31" s="9" t="str">
+        <x:v>PWR-003</x:v>
+      </x:c>
+      <x:c r="B31" s="10" t="str">
+        <x:v>Extension Power Cord (more sockets)</x:v>
+      </x:c>
+      <x:c r="C31" s="10" t="str">
+        <x:v>Power and connectivity</x:v>
+      </x:c>
+      <x:c r="D31" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E31" s="4"/>
       <x:c r="F31" s="4"/>
@@ -2733,13 +2304,13 @@
       <x:c r="H31" s="11"/>
       <x:c r="I31" s="11"/>
       <x:c r="J31" s="11"/>
-      <x:c r="K31" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K31" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L31" s="13"/>
       <x:c r="M31" s="14"/>
-      <x:c r="N31" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N31" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O31" s="11"/>
       <x:c r="P31" s="11"/>
@@ -2748,22 +2319,22 @@
       <x:c r="S31" s="11"/>
       <x:c r="T31" s="11"/>
       <x:c r="U31" s="11"/>
-      <x:c r="V31" s="11" t="s">
-        <x:v>124</x:v>
+      <x:c r="V31" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/belkin-bsv804.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="37.5">
-      <x:c r="A32" s="9" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="B32" s="10" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="C32" s="10" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D32" s="10" t="s">
-        <x:v>50</x:v>
+      <x:c r="A32" s="9" t="str">
+        <x:v>PWR-004</x:v>
+      </x:c>
+      <x:c r="B32" s="10" t="str">
+        <x:v>Smart Wi-Fi Socket Switch</x:v>
+      </x:c>
+      <x:c r="C32" s="10" t="str">
+        <x:v>Power and connectivity</x:v>
+      </x:c>
+      <x:c r="D32" s="10" t="str">
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E32" s="4"/>
       <x:c r="F32" s="4"/>
@@ -2771,13 +2342,13 @@
       <x:c r="H32" s="11"/>
       <x:c r="I32" s="11"/>
       <x:c r="J32" s="11"/>
-      <x:c r="K32" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K32" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L32" s="13"/>
       <x:c r="M32" s="14"/>
-      <x:c r="N32" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N32" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O32" s="11"/>
       <x:c r="P32" s="11"/>
@@ -2786,44 +2357,44 @@
       <x:c r="S32" s="11"/>
       <x:c r="T32" s="11"/>
       <x:c r="U32" s="11"/>
-      <x:c r="V32" s="11" t="s">
-        <x:v>127</x:v>
+      <x:c r="V32" s="11" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/tapo-p110.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="87.5">
-      <x:c r="A33" s="9" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="B33" s="10" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="C33" s="10" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D33" s="10" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E33" s="4" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F33" s="4" t="s">
-        <x:v>132</x:v>
+      <x:c r="A33" s="9" t="str">
+        <x:v>STO-001</x:v>
+      </x:c>
+      <x:c r="B33" s="10" t="str">
+        <x:v>File Organiser</x:v>
+      </x:c>
+      <x:c r="C33" s="10" t="str">
+        <x:v>Storage and organisation</x:v>
+      </x:c>
+      <x:c r="D33" s="10" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>SupaFile</x:v>
+      </x:c>
+      <x:c r="F33" s="4" t="str">
+        <x:v>1622</x:v>
       </x:c>
       <x:c r="G33" s="4"/>
-      <x:c r="H33" s="11" t="s">
-        <x:v>133</x:v>
+      <x:c r="H33" s="11" t="str">
+        <x:v>26-part desktop expanding file organiser</x:v>
       </x:c>
       <x:c r="I33" s="11"/>
       <x:c r="J33" s="11"/>
-      <x:c r="K33" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K33" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L33" s="13"/>
-      <x:c r="M33" s="14">
+      <x:c r="M33" s="14" t="n">
         <x:v>12.84</x:v>
       </x:c>
-      <x:c r="N33" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N33" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O33" s="11"/>
       <x:c r="P33" s="11"/>
@@ -2831,47 +2402,47 @@
       <x:c r="R33" s="11"/>
       <x:c r="S33" s="11"/>
       <x:c r="T33" s="11"/>
-      <x:c r="U33" s="11" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="V33" s="11" t="s">
-        <x:v>135</x:v>
+      <x:c r="U33" s="11" t="str">
+        <x:v>SQ550189 / 1622</x:v>
+      </x:c>
+      <x:c r="V33" s="11" t="str">
+        <x:v>https://ik.imagekit.io/pimberly/595e406f0f15f30010780448/tr:w-1000,h-1000,cm-pad_resize/f8d4d464/5d4d73a880150e75f70001de.jpg?product_name=Rapesco-Supafile-Plus-Expanding-File-A4-Assorted-1552.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="87.5">
-      <x:c r="A34" s="9" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="B34" s="10" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="C34" s="10" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D34" s="10" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E34" s="4" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F34" s="4" t="s">
-        <x:v>132</x:v>
+      <x:c r="A34" s="9" t="str">
+        <x:v>STO-002</x:v>
+      </x:c>
+      <x:c r="B34" s="10" t="str">
+        <x:v>File Organiser</x:v>
+      </x:c>
+      <x:c r="C34" s="10" t="str">
+        <x:v>Storage and organisation</x:v>
+      </x:c>
+      <x:c r="D34" s="10" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="str">
+        <x:v>SupaFile</x:v>
+      </x:c>
+      <x:c r="F34" s="4" t="str">
+        <x:v>1622</x:v>
       </x:c>
       <x:c r="G34" s="4"/>
-      <x:c r="H34" s="11" t="s">
-        <x:v>133</x:v>
+      <x:c r="H34" s="11" t="str">
+        <x:v>26-part desktop expanding file organiser</x:v>
       </x:c>
       <x:c r="I34" s="11"/>
       <x:c r="J34" s="11"/>
-      <x:c r="K34" s="12" t="s">
-        <x:v>51</x:v>
+      <x:c r="K34" s="12" t="str">
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="L34" s="13"/>
-      <x:c r="M34" s="14">
+      <x:c r="M34" s="14" t="n">
         <x:v>12.84</x:v>
       </x:c>
-      <x:c r="N34" s="11" t="s">
-        <x:v>52</x:v>
+      <x:c r="N34" s="11" t="str">
+        <x:v>GBP</x:v>
       </x:c>
       <x:c r="O34" s="11"/>
       <x:c r="P34" s="11"/>
@@ -2879,602 +2450,749 @@
       <x:c r="R34" s="11"/>
       <x:c r="S34" s="11"/>
       <x:c r="T34" s="11"/>
-      <x:c r="U34" s="11" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="V34" s="11" t="s">
-        <x:v>135</x:v>
+      <x:c r="U34" s="11" t="str">
+        <x:v>SQ550189 / 1622</x:v>
+      </x:c>
+      <x:c r="V34" s="11" t="str">
+        <x:v>https://ik.imagekit.io/pimberly/595e406f0f15f30010780448/tr:w-1000,h-1000,cm-pad_resize/f8d4d464/5d4d73a880150e75f70001de.jpg?product_name=Rapesco-Supafile-Plus-Expanding-File-A4-Assorted-1552.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="B35" t="s">
-        <x:v>138</x:v>
+      <x:c r="A35" t="str">
+        <x:v>CAM-006</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>EMEET NOVA 4K Webcam</x:v>
       </x:c>
       <x:c r="C35" t="str">
         <x:v>Cameras</x:v>
       </x:c>
-      <x:c r="D35" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E35" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F35" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="H35" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="K35" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M35">
-        <x:v>49.77</x:v>
-      </x:c>
-      <x:c r="N35" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U35" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="V35" t="s">
-        <x:v>143</x:v>
+      <x:c r="D35" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>EMEET</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>NOVA 4K</x:v>
+      </x:c>
+      <x:c r="G35"/>
+      <x:c r="H35" t="str">
+        <x:v>4K webcam, PDAF autofocus, dual noise-cancelling microphones and 73-degree field of view</x:v>
+      </x:c>
+      <x:c r="I35"/>
+      <x:c r="J35"/>
+      <x:c r="K35" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L35"/>
+      <x:c r="M35" t="n">
+        <x:v>39.81</x:v>
+      </x:c>
+      <x:c r="N35" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O35"/>
+      <x:c r="P35"/>
+      <x:c r="Q35"/>
+      <x:c r="R35"/>
+      <x:c r="S35"/>
+      <x:c r="T35"/>
+      <x:c r="U35" t="str">
+        <x:v>SQ550189 / E3131</x:v>
+      </x:c>
+      <x:c r="V35" t="str">
+        <x:v>https://emeet.com/cdn/shop/files/nova.png?v=1687780101&amp;width=1200</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="B36" t="s">
-        <x:v>145</x:v>
+      <x:c r="A36" t="str">
+        <x:v>TAB-003</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>Lenovo Idea Tab Pro 12.7</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>Cameras</x:v>
-      </x:c>
-      <x:c r="D36" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E36" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="F36" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="H36" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="K36" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M36">
-        <x:v>39.81</x:v>
-      </x:c>
-      <x:c r="N36" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U36" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="V36" t="s">
-        <x:v>150</x:v>
+        <x:v>Tablets</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>Lenovo</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>ZAE40036GB</x:v>
+      </x:c>
+      <x:c r="G36"/>
+      <x:c r="H36" t="str">
+        <x:v>12.7-inch LTPS display and 256 GB storage</x:v>
+      </x:c>
+      <x:c r="I36"/>
+      <x:c r="J36"/>
+      <x:c r="K36" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L36"/>
+      <x:c r="M36" t="n">
+        <x:v>297.7</x:v>
+      </x:c>
+      <x:c r="N36" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O36"/>
+      <x:c r="P36"/>
+      <x:c r="Q36"/>
+      <x:c r="R36"/>
+      <x:c r="S36"/>
+      <x:c r="T36"/>
+      <x:c r="U36" t="str">
+        <x:v>SQ550189 / ZAE40036GB</x:v>
+      </x:c>
+      <x:c r="V36" t="str">
+        <x:v>https://p2-ofp.static.pub/ShareResource/we/images/PN-list-image/Lenovo-Idea-Tab-Pro.png?height=584&amp;width=584</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="B37" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C37" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D37" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E37" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="F37" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H37" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="K37" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M37">
+      <x:c r="A37" t="str">
+        <x:v>TAB-004</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>Lenovo Idea Tab Pro 12.7</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Tablets</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>Lenovo</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>ZAE40036GB</x:v>
+      </x:c>
+      <x:c r="G37"/>
+      <x:c r="H37" t="str">
+        <x:v>12.7-inch LTPS display and 256 GB storage</x:v>
+      </x:c>
+      <x:c r="I37"/>
+      <x:c r="J37"/>
+      <x:c r="K37" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L37"/>
+      <x:c r="M37" t="n">
         <x:v>297.7</x:v>
       </x:c>
-      <x:c r="N37" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U37" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="V37" t="s">
-        <x:v>157</x:v>
+      <x:c r="N37" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O37"/>
+      <x:c r="P37"/>
+      <x:c r="Q37"/>
+      <x:c r="R37"/>
+      <x:c r="S37"/>
+      <x:c r="T37"/>
+      <x:c r="U37" t="str">
+        <x:v>SQ550189 / ZAE40036GB</x:v>
+      </x:c>
+      <x:c r="V37" t="str">
+        <x:v>https://p2-ofp.static.pub/ShareResource/we/images/PN-list-image/Lenovo-Idea-Tab-Pro.png?height=584&amp;width=584</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="B38" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C38" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D38" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E38" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="F38" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H38" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="K38" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M38">
-        <x:v>297.7</x:v>
-      </x:c>
-      <x:c r="N38" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U38" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="V38" t="s">
-        <x:v>157</x:v>
+      <x:c r="A38" t="str">
+        <x:v>TAB-005</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>Lenovo Idea Tab 11</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Tablets</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>Lenovo</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>ZAFR0384GB</x:v>
+      </x:c>
+      <x:c r="G38"/>
+      <x:c r="H38" t="str">
+        <x:v>11-inch tablet</x:v>
+      </x:c>
+      <x:c r="I38"/>
+      <x:c r="J38"/>
+      <x:c r="K38" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L38"/>
+      <x:c r="M38" t="n">
+        <x:v>146.35</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O38"/>
+      <x:c r="P38"/>
+      <x:c r="Q38"/>
+      <x:c r="R38"/>
+      <x:c r="S38"/>
+      <x:c r="T38"/>
+      <x:c r="U38" t="str">
+        <x:v>SQ550189 / ZAFR0384GB</x:v>
+      </x:c>
+      <x:c r="V38" t="str">
+        <x:v>https://p4-ofp.static.pub/ShareResource/we/Idea_Tab/Lenovo-Idea-Tab--400x300.png</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="B39" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C39" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D39" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E39" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="F39" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="H39" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="K39" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M39">
-        <x:v>146.35</x:v>
-      </x:c>
-      <x:c r="N39" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U39" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="V39" t="s">
-        <x:v>164</x:v>
+      <x:c r="A39" t="str">
+        <x:v>MNT-012</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Tablet Holder</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>Tripods, stands and mounts</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E39"/>
+      <x:c r="F39" t="str">
+        <x:v>G3023</x:v>
+      </x:c>
+      <x:c r="G39"/>
+      <x:c r="H39" t="str">
+        <x:v>Holder for 4-inch to 12.9-inch tablets</x:v>
+      </x:c>
+      <x:c r="I39"/>
+      <x:c r="J39"/>
+      <x:c r="K39" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L39"/>
+      <x:c r="M39" t="n">
+        <x:v>7.95</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O39"/>
+      <x:c r="P39"/>
+      <x:c r="Q39"/>
+      <x:c r="R39"/>
+      <x:c r="S39"/>
+      <x:c r="T39"/>
+      <x:c r="U39" t="str">
+        <x:v>SQ550189 / G3023</x:v>
+      </x:c>
+      <x:c r="V39" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="B40" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="C40" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D40" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F40" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="H40" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="K40" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M40">
-        <x:v>7.95</x:v>
-      </x:c>
-      <x:c r="N40" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U40" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="V40" t="s">
-        <x:v>69</x:v>
+      <x:c r="A40" t="str">
+        <x:v>STO-003</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>File Organiser</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>Storage and organisation</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>SupaFile</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>1622</x:v>
+      </x:c>
+      <x:c r="G40"/>
+      <x:c r="H40" t="str">
+        <x:v>26-part desktop expanding file organiser</x:v>
+      </x:c>
+      <x:c r="I40"/>
+      <x:c r="J40"/>
+      <x:c r="K40" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L40"/>
+      <x:c r="M40" t="n">
+        <x:v>12.84</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O40"/>
+      <x:c r="P40"/>
+      <x:c r="Q40"/>
+      <x:c r="R40"/>
+      <x:c r="S40"/>
+      <x:c r="T40"/>
+      <x:c r="U40" t="str">
+        <x:v>SQ550189 / 1622</x:v>
+      </x:c>
+      <x:c r="V40" t="str">
+        <x:v>https://ik.imagekit.io/pimberly/595e406f0f15f30010780448/tr:w-1000,h-1000,cm-pad_resize/f8d4d464/5d4d73a880150e75f70001de.jpg?product_name=Rapesco-Supafile-Plus-Expanding-File-A4-Assorted-1552.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="B41" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="C41" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D41" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E41" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F41" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="H41" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="K41" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M41">
-        <x:v>12.84</x:v>
-      </x:c>
-      <x:c r="N41" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U41" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="V41" t="s">
-        <x:v>135</x:v>
+      <x:c r="A41" t="str">
+        <x:v>STO-004</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>Seagate Portable 1 TB External Hard Drive</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Storage and organisation</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>Seagate</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>STGX1000400</x:v>
+      </x:c>
+      <x:c r="G41"/>
+      <x:c r="H41" t="str">
+        <x:v>1 TB portable external hard drive with USB 3</x:v>
+      </x:c>
+      <x:c r="I41"/>
+      <x:c r="J41"/>
+      <x:c r="K41" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L41"/>
+      <x:c r="M41" t="n">
+        <x:v>75.65</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O41"/>
+      <x:c r="P41"/>
+      <x:c r="Q41"/>
+      <x:c r="R41"/>
+      <x:c r="S41"/>
+      <x:c r="T41"/>
+      <x:c r="U41" t="str">
+        <x:v>SQ550189 / STGX1000400</x:v>
+      </x:c>
+      <x:c r="V41" t="str">
+        <x:v>https://www.seagate.com/content/dam/seagate/assets/products/external-hard-drives/portable-drive/1-seagate-portable-drive-2.5-front-hi-res-PhotoRoom.png/_jcr_content/renditions/1-1-large-640x640.png</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="B42" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C42" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D42" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E42" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F42" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H42" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="K42" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M42">
-        <x:v>75.650000000000006</x:v>
-      </x:c>
-      <x:c r="N42" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U42" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="V42" t="s">
-        <x:v>177</x:v>
+      <x:c r="A42" t="str">
+        <x:v>STO-005</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>Seagate Portable 1 TB External Hard Drive</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Storage and organisation</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>Seagate</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>STGX1000400</x:v>
+      </x:c>
+      <x:c r="G42"/>
+      <x:c r="H42" t="str">
+        <x:v>1 TB portable external hard drive with USB 3</x:v>
+      </x:c>
+      <x:c r="I42"/>
+      <x:c r="J42"/>
+      <x:c r="K42" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L42"/>
+      <x:c r="M42" t="n">
+        <x:v>75.65</x:v>
+      </x:c>
+      <x:c r="N42" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O42"/>
+      <x:c r="P42"/>
+      <x:c r="Q42"/>
+      <x:c r="R42"/>
+      <x:c r="S42"/>
+      <x:c r="T42"/>
+      <x:c r="U42" t="str">
+        <x:v>SQ550189 / STGX1000400</x:v>
+      </x:c>
+      <x:c r="V42" t="str">
+        <x:v>https://www.seagate.com/content/dam/seagate/assets/products/external-hard-drives/portable-drive/1-seagate-portable-drive-2.5-front-hi-res-PhotoRoom.png/_jcr_content/renditions/1-1-large-640x640.png</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="B43" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C43" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D43" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E43" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F43" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H43" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="K43" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M43">
-        <x:v>75.650000000000006</x:v>
-      </x:c>
-      <x:c r="N43" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U43" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="V43" t="s">
-        <x:v>177</x:v>
+      <x:c r="A43" t="str">
+        <x:v>STO-006</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Seagate Portable 1 TB External Hard Drive</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Storage and organisation</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>Seagate</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>STGX1000400</x:v>
+      </x:c>
+      <x:c r="G43"/>
+      <x:c r="H43" t="str">
+        <x:v>1 TB portable external hard drive with USB 3</x:v>
+      </x:c>
+      <x:c r="I43"/>
+      <x:c r="J43"/>
+      <x:c r="K43" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L43"/>
+      <x:c r="M43" t="n">
+        <x:v>75.65</x:v>
+      </x:c>
+      <x:c r="N43" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O43"/>
+      <x:c r="P43"/>
+      <x:c r="Q43"/>
+      <x:c r="R43"/>
+      <x:c r="S43"/>
+      <x:c r="T43"/>
+      <x:c r="U43" t="str">
+        <x:v>SQ550189 / STGX1000400</x:v>
+      </x:c>
+      <x:c r="V43" t="str">
+        <x:v>https://www.seagate.com/content/dam/seagate/assets/products/external-hard-drives/portable-drive/1-seagate-portable-drive-2.5-front-hi-res-PhotoRoom.png/_jcr_content/renditions/1-1-large-640x640.png</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="B44" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C44" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D44" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E44" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F44" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H44" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="K44" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M44">
-        <x:v>75.650000000000006</x:v>
-      </x:c>
-      <x:c r="N44" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U44" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="V44" t="s">
-        <x:v>177</x:v>
+      <x:c r="A44" t="str">
+        <x:v>STO-007</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>ModusTech 500 GB Portable External Hard Drive</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>Storage and organisation</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>ModusTech</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>MT500</x:v>
+      </x:c>
+      <x:c r="G44"/>
+      <x:c r="H44" t="str">
+        <x:v>500 GB portable external hard drive with USB 3.0 and USB-C</x:v>
+      </x:c>
+      <x:c r="I44"/>
+      <x:c r="J44"/>
+      <x:c r="K44" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L44"/>
+      <x:c r="M44" t="n">
+        <x:v>21.88</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O44"/>
+      <x:c r="P44"/>
+      <x:c r="Q44"/>
+      <x:c r="R44"/>
+      <x:c r="S44"/>
+      <x:c r="T44"/>
+      <x:c r="U44" t="str">
+        <x:v>SQ550189 / MT500</x:v>
+      </x:c>
+      <x:c r="V44" t="str">
+        <x:v>https://image.review-rating.com/xNzF6eVU4RXRzaEw_WIDTH200.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="B45" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="C45" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D45" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E45" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F45" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="H45" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="K45" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M45">
+      <x:c r="A45" t="str">
+        <x:v>STO-008</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>ModusTech 500 GB Portable External Hard Drive</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Storage and organisation</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>ModusTech</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>MT500</x:v>
+      </x:c>
+      <x:c r="G45"/>
+      <x:c r="H45" t="str">
+        <x:v>500 GB portable external hard drive with USB 3.0 and USB-C</x:v>
+      </x:c>
+      <x:c r="I45"/>
+      <x:c r="J45"/>
+      <x:c r="K45" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L45"/>
+      <x:c r="M45" t="n">
         <x:v>21.88</x:v>
       </x:c>
-      <x:c r="N45" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U45" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="V45" t="s">
-        <x:v>186</x:v>
+      <x:c r="N45" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O45"/>
+      <x:c r="P45"/>
+      <x:c r="Q45"/>
+      <x:c r="R45"/>
+      <x:c r="S45"/>
+      <x:c r="T45"/>
+      <x:c r="U45" t="str">
+        <x:v>SQ550189 / MT500</x:v>
+      </x:c>
+      <x:c r="V45" t="str">
+        <x:v>https://image.review-rating.com/xNzF6eVU4RXRzaEw_WIDTH200.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="B46" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="C46" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D46" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E46" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F46" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="H46" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="K46" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M46">
+      <x:c r="A46" t="str">
+        <x:v>STO-009</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>ModusTech 500 GB Portable External Hard Drive</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>Storage and organisation</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>ModusTech</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>MT500</x:v>
+      </x:c>
+      <x:c r="G46"/>
+      <x:c r="H46" t="str">
+        <x:v>500 GB portable external hard drive with USB 3.0 and USB-C</x:v>
+      </x:c>
+      <x:c r="I46"/>
+      <x:c r="J46"/>
+      <x:c r="K46" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L46"/>
+      <x:c r="M46" t="n">
         <x:v>21.88</x:v>
       </x:c>
-      <x:c r="N46" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U46" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="V46" t="s">
-        <x:v>186</x:v>
+      <x:c r="N46" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O46"/>
+      <x:c r="P46"/>
+      <x:c r="Q46"/>
+      <x:c r="R46"/>
+      <x:c r="S46"/>
+      <x:c r="T46"/>
+      <x:c r="U46" t="str">
+        <x:v>SQ550189 / MT500</x:v>
+      </x:c>
+      <x:c r="V46" t="str">
+        <x:v>https://image.review-rating.com/xNzF6eVU4RXRzaEw_WIDTH200.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="B47" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="C47" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D47" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E47" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F47" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="H47" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="K47" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M47">
-        <x:v>21.88</x:v>
-      </x:c>
-      <x:c r="N47" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U47" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="V47" t="s">
-        <x:v>186</x:v>
+      <x:c r="A47" t="str">
+        <x:v>CMP-001</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>HP Pro Mini 400 G9</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Computers</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>623W7ET#ABU</x:v>
+      </x:c>
+      <x:c r="G47"/>
+      <x:c r="H47" t="str">
+        <x:v>Intel Core i5-13500T, 8 GB RAM, 256 GB storage and Windows 11 Pro</x:v>
+      </x:c>
+      <x:c r="I47"/>
+      <x:c r="J47"/>
+      <x:c r="K47" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L47"/>
+      <x:c r="M47" t="n">
+        <x:v>606.93</x:v>
+      </x:c>
+      <x:c r="N47" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O47"/>
+      <x:c r="P47"/>
+      <x:c r="Q47"/>
+      <x:c r="R47"/>
+      <x:c r="S47"/>
+      <x:c r="T47"/>
+      <x:c r="U47" t="str">
+        <x:v>SQ550189 / 623W7ET#ABU</x:v>
+      </x:c>
+      <x:c r="V47" t="str">
+        <x:v>https://media.box.co.uk/product/0/0/00ed038f0c0de034de0918539cc9c6f9.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="B48" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="C48" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="D48" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E48" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F48" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H48" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="K48" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M48">
-        <x:v>606.92999999999995</x:v>
-      </x:c>
-      <x:c r="N48" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U48" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="V48" t="s">
-        <x:v>196</x:v>
+      <x:c r="A48" t="str">
+        <x:v>CMP-002</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>HP Pro Mini 400 G9</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>Computers</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="F48" t="str">
+        <x:v>623W7ET#ABU</x:v>
+      </x:c>
+      <x:c r="G48"/>
+      <x:c r="H48" t="str">
+        <x:v>Intel Core i5-13500T, 8 GB RAM, 256 GB storage and Windows 11 Pro</x:v>
+      </x:c>
+      <x:c r="I48"/>
+      <x:c r="J48"/>
+      <x:c r="K48" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L48"/>
+      <x:c r="M48" t="n">
+        <x:v>606.93</x:v>
+      </x:c>
+      <x:c r="N48" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O48"/>
+      <x:c r="P48"/>
+      <x:c r="Q48"/>
+      <x:c r="R48"/>
+      <x:c r="S48"/>
+      <x:c r="T48"/>
+      <x:c r="U48" t="str">
+        <x:v>SQ550189 / 623W7ET#ABU</x:v>
+      </x:c>
+      <x:c r="V48" t="str">
+        <x:v>https://media.box.co.uk/product/0/0/00ed038f0c0de034de0918539cc9c6f9.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="B49" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="C49" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="D49" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E49" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F49" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H49" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="K49" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M49">
-        <x:v>606.92999999999995</x:v>
-      </x:c>
-      <x:c r="N49" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="U49" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="V49" t="s">
-        <x:v>196</x:v>
+      <x:c r="A49" t="str">
+        <x:v>ROB-007</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>Reachy Mini Wireless</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>Robots</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>Bundle</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>Pollen Robotics</x:v>
+      </x:c>
+      <x:c r="F49" t="str">
+        <x:v>Reachy Mini Wireless</x:v>
+      </x:c>
+      <x:c r="G49"/>
+      <x:c r="H49" t="str">
+        <x:v>Wireless Reachy Mini robot bundle</x:v>
+      </x:c>
+      <x:c r="I49"/>
+      <x:c r="J49"/>
+      <x:c r="K49" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L49"/>
+      <x:c r="M49"/>
+      <x:c r="N49" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O49"/>
+      <x:c r="P49"/>
+      <x:c r="Q49"/>
+      <x:c r="R49"/>
+      <x:c r="S49"/>
+      <x:c r="T49"/>
+      <x:c r="U49"/>
+      <x:c r="V49" t="str">
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
-        <x:v>ROB-007</x:v>
+        <x:v>MON-001</x:v>
       </x:c>
       <x:c r="B50" t="str">
-        <x:v>Reachy Mini Wireless</x:v>
+        <x:v>LG 27-inch Monitor</x:v>
       </x:c>
       <x:c r="C50" t="str">
-        <x:v>Robots</x:v>
+        <x:v>Monitors</x:v>
       </x:c>
       <x:c r="D50" t="str">
-        <x:v>Bundle</x:v>
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E50" t="str">
-        <x:v>Pollen Robotics</x:v>
+        <x:v>LG</x:v>
       </x:c>
       <x:c r="F50" t="str">
-        <x:v>Reachy Mini Wireless</x:v>
+        <x:v>27MR400-B</x:v>
       </x:c>
       <x:c r="G50"/>
       <x:c r="H50" t="str">
-        <x:v>Wireless Reachy Mini robot bundle</x:v>
+        <x:v>27-inch IPS Full HD display, 100 Hz refresh rate and AMD FreeSync</x:v>
       </x:c>
       <x:c r="I50"/>
       <x:c r="J50"/>
@@ -3489,17 +3207,19 @@
       <x:c r="O50"/>
       <x:c r="P50"/>
       <x:c r="Q50"/>
-      <x:c r="R50"/>
+      <x:c r="R50" t="str">
+        <x:v>https://www.lg.com/uk/monitors/fhd-qhd/27mr400-b/</x:v>
+      </x:c>
       <x:c r="S50"/>
       <x:c r="T50"/>
       <x:c r="U50"/>
       <x:c r="V50" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/lg-27mr400-b.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
-        <x:v>MON-001</x:v>
+        <x:v>MON-002</x:v>
       </x:c>
       <x:c r="B51" t="str">
         <x:v>LG 27-inch Monitor</x:v>
@@ -3540,12 +3260,12 @@
       <x:c r="T51"/>
       <x:c r="U51"/>
       <x:c r="V51" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/lg-27mr400-b.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="str">
-        <x:v>MON-002</x:v>
+        <x:v>MON-003</x:v>
       </x:c>
       <x:c r="B52" t="str">
         <x:v>LG 27-inch Monitor</x:v>
@@ -3586,15 +3306,15 @@
       <x:c r="T52"/>
       <x:c r="U52"/>
       <x:c r="V52" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/lg-27mr400-b.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="str">
-        <x:v>MON-003</x:v>
+        <x:v>MON-004</x:v>
       </x:c>
       <x:c r="B53" t="str">
-        <x:v>LG 27-inch Monitor</x:v>
+        <x:v>Amazon Basics Monitor</x:v>
       </x:c>
       <x:c r="C53" t="str">
         <x:v>Monitors</x:v>
@@ -3603,15 +3323,13 @@
         <x:v>Individual</x:v>
       </x:c>
       <x:c r="E53" t="str">
-        <x:v>LG</x:v>
+        <x:v>Amazon Basics</x:v>
       </x:c>
       <x:c r="F53" t="str">
-        <x:v>27MR400-B</x:v>
+        <x:v>C26M2020UK</x:v>
       </x:c>
       <x:c r="G53"/>
-      <x:c r="H53" t="str">
-        <x:v>27-inch IPS Full HD display, 100 Hz refresh rate and AMD FreeSync</x:v>
-      </x:c>
+      <x:c r="H53"/>
       <x:c r="I53"/>
       <x:c r="J53"/>
       <x:c r="K53" t="str">
@@ -3625,9 +3343,7 @@
       <x:c r="O53"/>
       <x:c r="P53"/>
       <x:c r="Q53"/>
-      <x:c r="R53" t="str">
-        <x:v>https://www.lg.com/uk/monitors/fhd-qhd/27mr400-b/</x:v>
-      </x:c>
+      <x:c r="R53"/>
       <x:c r="S53"/>
       <x:c r="T53"/>
       <x:c r="U53"/>
@@ -3637,7 +3353,7 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="str">
-        <x:v>MON-004</x:v>
+        <x:v>MON-005</x:v>
       </x:c>
       <x:c r="B54" t="str">
         <x:v>Amazon Basics Monitor</x:v>
@@ -3679,7 +3395,7 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="str">
-        <x:v>MON-005</x:v>
+        <x:v>MON-006</x:v>
       </x:c>
       <x:c r="B55" t="str">
         <x:v>Amazon Basics Monitor</x:v>
@@ -3721,7 +3437,7 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="str">
-        <x:v>MON-006</x:v>
+        <x:v>MON-007</x:v>
       </x:c>
       <x:c r="B56" t="str">
         <x:v>Amazon Basics Monitor</x:v>
@@ -3763,25 +3479,27 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="str">
-        <x:v>MON-007</x:v>
+        <x:v>NET-001</x:v>
       </x:c>
       <x:c r="B57" t="str">
-        <x:v>Amazon Basics Monitor</x:v>
+        <x:v>TP-Link AX1500 Wi-Fi 6 Router</x:v>
       </x:c>
       <x:c r="C57" t="str">
-        <x:v>Monitors</x:v>
+        <x:v>Networking</x:v>
       </x:c>
       <x:c r="D57" t="str">
         <x:v>Individual</x:v>
       </x:c>
       <x:c r="E57" t="str">
-        <x:v>Amazon Basics</x:v>
+        <x:v>TP-Link</x:v>
       </x:c>
       <x:c r="F57" t="str">
-        <x:v>C26M2020UK</x:v>
+        <x:v>Archer AX1500</x:v>
       </x:c>
       <x:c r="G57"/>
-      <x:c r="H57"/>
+      <x:c r="H57" t="str">
+        <x:v>Dual-band Wi-Fi 6 router with speeds up to 1.5 Gbps</x:v>
+      </x:c>
       <x:c r="I57"/>
       <x:c r="J57"/>
       <x:c r="K57" t="str">
@@ -3795,17 +3513,19 @@
       <x:c r="O57"/>
       <x:c r="P57"/>
       <x:c r="Q57"/>
-      <x:c r="R57"/>
+      <x:c r="R57" t="str">
+        <x:v>https://www.tp-link.com/uk/home-networking/wifi-router/archer-ax1500/v1/</x:v>
+      </x:c>
       <x:c r="S57"/>
       <x:c r="T57"/>
       <x:c r="U57"/>
       <x:c r="V57" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/tp-link-archer-ax1500.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="str">
-        <x:v>NET-001</x:v>
+        <x:v>NET-002</x:v>
       </x:c>
       <x:c r="B58" t="str">
         <x:v>TP-Link AX1500 Wi-Fi 6 Router</x:v>
@@ -3846,12 +3566,12 @@
       <x:c r="T58"/>
       <x:c r="U58"/>
       <x:c r="V58" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/tp-link-archer-ax1500.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="str">
-        <x:v>NET-002</x:v>
+        <x:v>NET-003</x:v>
       </x:c>
       <x:c r="B59" t="str">
         <x:v>TP-Link AX1500 Wi-Fi 6 Router</x:v>
@@ -3892,15 +3612,15 @@
       <x:c r="T59"/>
       <x:c r="U59"/>
       <x:c r="V59" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/tp-link-archer-ax1500.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="str">
-        <x:v>NET-003</x:v>
+        <x:v>NET-004</x:v>
       </x:c>
       <x:c r="B60" t="str">
-        <x:v>TP-Link AX1500 Wi-Fi 6 Router</x:v>
+        <x:v>TP-Link Wireless N Router</x:v>
       </x:c>
       <x:c r="C60" t="str">
         <x:v>Networking</x:v>
@@ -3912,11 +3632,11 @@
         <x:v>TP-Link</x:v>
       </x:c>
       <x:c r="F60" t="str">
-        <x:v>Archer AX1500</x:v>
+        <x:v>TL-WR841N</x:v>
       </x:c>
       <x:c r="G60"/>
       <x:c r="H60" t="str">
-        <x:v>Dual-band Wi-Fi 6 router with speeds up to 1.5 Gbps</x:v>
+        <x:v>300 Mbps 2.4 GHz Wireless N router</x:v>
       </x:c>
       <x:c r="I60"/>
       <x:c r="J60"/>
@@ -3932,18 +3652,18 @@
       <x:c r="P60"/>
       <x:c r="Q60"/>
       <x:c r="R60" t="str">
-        <x:v>https://www.tp-link.com/uk/home-networking/wifi-router/archer-ax1500/v1/</x:v>
+        <x:v>https://www.tp-link.com/uk/home-networking/wifi-router/tl-wr841n/</x:v>
       </x:c>
       <x:c r="S60"/>
       <x:c r="T60"/>
       <x:c r="U60"/>
       <x:c r="V60" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/tp-link-tl-wr841n.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="str">
-        <x:v>NET-004</x:v>
+        <x:v>NET-005</x:v>
       </x:c>
       <x:c r="B61" t="str">
         <x:v>TP-Link Wireless N Router</x:v>
@@ -3984,31 +3704,31 @@
       <x:c r="T61"/>
       <x:c r="U61"/>
       <x:c r="V61" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/tp-link-tl-wr841n.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="str">
-        <x:v>NET-005</x:v>
+        <x:v>LGT-003</x:v>
       </x:c>
       <x:c r="B62" t="str">
-        <x:v>TP-Link Wireless N Router</x:v>
+        <x:v>Overhead Light</x:v>
       </x:c>
       <x:c r="C62" t="str">
-        <x:v>Networking</x:v>
+        <x:v>Lighting</x:v>
       </x:c>
       <x:c r="D62" t="str">
         <x:v>Individual</x:v>
       </x:c>
       <x:c r="E62" t="str">
-        <x:v>TP-Link</x:v>
+        <x:v>NEEWER</x:v>
       </x:c>
       <x:c r="F62" t="str">
-        <x:v>TL-WR841N</x:v>
+        <x:v>BASICS BP66</x:v>
       </x:c>
       <x:c r="G62"/>
       <x:c r="H62" t="str">
-        <x:v>300 Mbps 2.4 GHz Wireless N router</x:v>
+        <x:v>Overhead light supplied as part of a two-pack</x:v>
       </x:c>
       <x:c r="I62"/>
       <x:c r="J62"/>
@@ -4023,19 +3743,17 @@
       <x:c r="O62"/>
       <x:c r="P62"/>
       <x:c r="Q62"/>
-      <x:c r="R62" t="str">
-        <x:v>https://www.tp-link.com/uk/home-networking/wifi-router/tl-wr841n/</x:v>
-      </x:c>
+      <x:c r="R62"/>
       <x:c r="S62"/>
       <x:c r="T62"/>
       <x:c r="U62"/>
       <x:c r="V62" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://m.media-amazon.com/images/I/61Gj-qwZzvL._AC_SL1500_.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="str">
-        <x:v>LGT-003</x:v>
+        <x:v>LGT-004</x:v>
       </x:c>
       <x:c r="B63" t="str">
         <x:v>Overhead Light</x:v>
@@ -4079,26 +3797,26 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="str">
-        <x:v>LGT-004</x:v>
+        <x:v>PER-001</x:v>
       </x:c>
       <x:c r="B64" t="str">
-        <x:v>Overhead Light</x:v>
+        <x:v>Logitech MK270 Wireless Keyboard and Mouse</x:v>
       </x:c>
       <x:c r="C64" t="str">
-        <x:v>Lighting</x:v>
+        <x:v>Computer peripherals</x:v>
       </x:c>
       <x:c r="D64" t="str">
-        <x:v>Individual</x:v>
+        <x:v>Bundle</x:v>
       </x:c>
       <x:c r="E64" t="str">
-        <x:v>NEEWER</x:v>
+        <x:v>Logitech</x:v>
       </x:c>
       <x:c r="F64" t="str">
-        <x:v>BASICS BP66</x:v>
+        <x:v>MK270</x:v>
       </x:c>
       <x:c r="G64"/>
       <x:c r="H64" t="str">
-        <x:v>Overhead light supplied as part of a two-pack</x:v>
+        <x:v>Wireless full-size keyboard and mouse combo</x:v>
       </x:c>
       <x:c r="I64"/>
       <x:c r="J64"/>
@@ -4111,19 +3829,23 @@
         <x:v>GBP</x:v>
       </x:c>
       <x:c r="O64"/>
-      <x:c r="P64"/>
+      <x:c r="P64" t="str">
+        <x:v>Return the keyboard, mouse and USB receiver together.</x:v>
+      </x:c>
       <x:c r="Q64"/>
-      <x:c r="R64"/>
+      <x:c r="R64" t="str">
+        <x:v>https://www.logitech.com/en-gb/shop/p/mk270-wireless-keyboard-mouse</x:v>
+      </x:c>
       <x:c r="S64"/>
       <x:c r="T64"/>
       <x:c r="U64"/>
       <x:c r="V64" t="str">
-        <x:v>https://m.media-amazon.com/images/I/61Gj-qwZzvL._AC_SL1500_.jpg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="str">
-        <x:v>PER-001</x:v>
+        <x:v>PER-002</x:v>
       </x:c>
       <x:c r="B65" t="str">
         <x:v>Logitech MK270 Wireless Keyboard and Mouse</x:v>
@@ -4166,12 +3888,12 @@
       <x:c r="T65"/>
       <x:c r="U65"/>
       <x:c r="V65" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="str">
-        <x:v>PER-002</x:v>
+        <x:v>PER-003</x:v>
       </x:c>
       <x:c r="B66" t="str">
         <x:v>Logitech MK270 Wireless Keyboard and Mouse</x:v>
@@ -4214,12 +3936,12 @@
       <x:c r="T66"/>
       <x:c r="U66"/>
       <x:c r="V66" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="str">
-        <x:v>PER-003</x:v>
+        <x:v>PER-004</x:v>
       </x:c>
       <x:c r="B67" t="str">
         <x:v>Logitech MK270 Wireless Keyboard and Mouse</x:v>
@@ -4262,12 +3984,12 @@
       <x:c r="T67"/>
       <x:c r="U67"/>
       <x:c r="V67" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="str">
-        <x:v>PER-004</x:v>
+        <x:v>PER-005</x:v>
       </x:c>
       <x:c r="B68" t="str">
         <x:v>Logitech MK270 Wireless Keyboard and Mouse</x:v>
@@ -4310,32 +4032,30 @@
       <x:c r="T68"/>
       <x:c r="U68"/>
       <x:c r="V68" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="str">
-        <x:v>PER-005</x:v>
+        <x:v>LGT-005</x:v>
       </x:c>
       <x:c r="B69" t="str">
-        <x:v>Logitech MK270 Wireless Keyboard and Mouse</x:v>
+        <x:v>IKEA TOKABO Ambient Lamp</x:v>
       </x:c>
       <x:c r="C69" t="str">
-        <x:v>Computer peripherals</x:v>
+        <x:v>Lighting</x:v>
       </x:c>
       <x:c r="D69" t="str">
-        <x:v>Bundle</x:v>
+        <x:v>Individual</x:v>
       </x:c>
       <x:c r="E69" t="str">
-        <x:v>Logitech</x:v>
+        <x:v>IKEA</x:v>
       </x:c>
       <x:c r="F69" t="str">
-        <x:v>MK270</x:v>
+        <x:v>B1903 TOKABO</x:v>
       </x:c>
       <x:c r="G69"/>
-      <x:c r="H69" t="str">
-        <x:v>Wireless full-size keyboard and mouse combo</x:v>
-      </x:c>
+      <x:c r="H69"/>
       <x:c r="I69"/>
       <x:c r="J69"/>
       <x:c r="K69" t="str">
@@ -4347,39 +4067,31 @@
         <x:v>GBP</x:v>
       </x:c>
       <x:c r="O69"/>
-      <x:c r="P69" t="str">
-        <x:v>Return the keyboard, mouse and USB receiver together.</x:v>
-      </x:c>
+      <x:c r="P69"/>
       <x:c r="Q69"/>
-      <x:c r="R69" t="str">
-        <x:v>https://www.logitech.com/en-gb/shop/p/mk270-wireless-keyboard-mouse</x:v>
-      </x:c>
+      <x:c r="R69"/>
       <x:c r="S69"/>
       <x:c r="T69"/>
       <x:c r="U69"/>
       <x:c r="V69" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/ikea-tokabo.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="str">
-        <x:v>LGT-005</x:v>
+        <x:v>MNT-013</x:v>
       </x:c>
       <x:c r="B70" t="str">
-        <x:v>IKEA TOKABO Ambient Lamp</x:v>
+        <x:v>Phone Stand</x:v>
       </x:c>
       <x:c r="C70" t="str">
-        <x:v>Lighting</x:v>
+        <x:v>Tripods, stands and mounts</x:v>
       </x:c>
       <x:c r="D70" t="str">
         <x:v>Individual</x:v>
       </x:c>
-      <x:c r="E70" t="str">
-        <x:v>IKEA</x:v>
-      </x:c>
-      <x:c r="F70" t="str">
-        <x:v>B1903 TOKABO</x:v>
-      </x:c>
+      <x:c r="E70"/>
+      <x:c r="F70"/>
       <x:c r="G70"/>
       <x:c r="H70"/>
       <x:c r="I70"/>
@@ -4405,19 +4117,23 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="str">
-        <x:v>MNT-013</x:v>
+        <x:v>PWR-005</x:v>
       </x:c>
       <x:c r="B71" t="str">
-        <x:v>Phone Stand</x:v>
+        <x:v>MSCIEN Power Strip</x:v>
       </x:c>
       <x:c r="C71" t="str">
-        <x:v>Tripods, stands and mounts</x:v>
+        <x:v>Power and connectivity</x:v>
       </x:c>
       <x:c r="D71" t="str">
         <x:v>Individual</x:v>
       </x:c>
-      <x:c r="E71"/>
-      <x:c r="F71"/>
+      <x:c r="E71" t="str">
+        <x:v>MSCIEN</x:v>
+      </x:c>
+      <x:c r="F71" t="str">
+        <x:v>YP11Y2Y203U</x:v>
+      </x:c>
       <x:c r="G71"/>
       <x:c r="H71"/>
       <x:c r="I71"/>
@@ -4443,10 +4159,10 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="str">
-        <x:v>PWR-005</x:v>
+        <x:v>PWR-006</x:v>
       </x:c>
       <x:c r="B72" t="str">
-        <x:v>MSCIEN Power Strip</x:v>
+        <x:v>UGREEN 6-in-1 USB Hub</x:v>
       </x:c>
       <x:c r="C72" t="str">
         <x:v>Power and connectivity</x:v>
@@ -4455,10 +4171,10 @@
         <x:v>Individual</x:v>
       </x:c>
       <x:c r="E72" t="str">
-        <x:v>MSCIEN</x:v>
+        <x:v>UGREEN</x:v>
       </x:c>
       <x:c r="F72" t="str">
-        <x:v>YP11Y2Y203U</x:v>
+        <x:v>6-in-1 USB Hub</x:v>
       </x:c>
       <x:c r="G72"/>
       <x:c r="H72"/>
@@ -4485,23 +4201,19 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" t="str">
-        <x:v>PWR-006</x:v>
+        <x:v>MNT-014</x:v>
       </x:c>
       <x:c r="B73" t="str">
-        <x:v>UGREEN 6-in-1 USB Hub</x:v>
+        <x:v>Phone Mount</x:v>
       </x:c>
       <x:c r="C73" t="str">
-        <x:v>Power and connectivity</x:v>
+        <x:v>Tripods, stands and mounts</x:v>
       </x:c>
       <x:c r="D73" t="str">
         <x:v>Individual</x:v>
       </x:c>
-      <x:c r="E73" t="str">
-        <x:v>UGREEN</x:v>
-      </x:c>
-      <x:c r="F73" t="str">
-        <x:v>6-in-1 USB Hub</x:v>
-      </x:c>
+      <x:c r="E73"/>
+      <x:c r="F73"/>
       <x:c r="G73"/>
       <x:c r="H73"/>
       <x:c r="I73"/>
@@ -4527,7 +4239,7 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="str">
-        <x:v>MNT-014</x:v>
+        <x:v>MNT-015</x:v>
       </x:c>
       <x:c r="B74" t="str">
         <x:v>Phone Mount</x:v>
@@ -4565,7 +4277,7 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" t="str">
-        <x:v>MNT-015</x:v>
+        <x:v>MNT-016</x:v>
       </x:c>
       <x:c r="B75" t="str">
         <x:v>Phone Mount</x:v>
@@ -4603,18 +4315,20 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="str">
-        <x:v>MNT-016</x:v>
+        <x:v>PWR-007</x:v>
       </x:c>
       <x:c r="B76" t="str">
-        <x:v>Phone Mount</x:v>
+        <x:v>RSHTECH USB Hub</x:v>
       </x:c>
       <x:c r="C76" t="str">
-        <x:v>Tripods, stands and mounts</x:v>
+        <x:v>Power and connectivity</x:v>
       </x:c>
       <x:c r="D76" t="str">
         <x:v>Individual</x:v>
       </x:c>
-      <x:c r="E76"/>
+      <x:c r="E76" t="str">
+        <x:v>RSHTECH</x:v>
+      </x:c>
       <x:c r="F76"/>
       <x:c r="G76"/>
       <x:c r="H76"/>
@@ -4641,7 +4355,7 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="str">
-        <x:v>PWR-007</x:v>
+        <x:v>PWR-008</x:v>
       </x:c>
       <x:c r="B77" t="str">
         <x:v>RSHTECH USB Hub</x:v>
@@ -4681,7 +4395,7 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="str">
-        <x:v>PWR-008</x:v>
+        <x:v>PWR-009</x:v>
       </x:c>
       <x:c r="B78" t="str">
         <x:v>RSHTECH USB Hub</x:v>
@@ -4720,34 +4434,20 @@
       </x:c>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" t="str">
-        <x:v>PWR-009</x:v>
-      </x:c>
-      <x:c r="B79" t="str">
-        <x:v>RSHTECH USB Hub</x:v>
-      </x:c>
-      <x:c r="C79" t="str">
-        <x:v>Power and connectivity</x:v>
-      </x:c>
-      <x:c r="D79" t="str">
-        <x:v>Individual</x:v>
-      </x:c>
-      <x:c r="E79" t="str">
-        <x:v>RSHTECH</x:v>
-      </x:c>
+      <x:c r="A79"/>
+      <x:c r="B79"/>
+      <x:c r="C79"/>
+      <x:c r="D79"/>
+      <x:c r="E79"/>
       <x:c r="F79"/>
       <x:c r="G79"/>
       <x:c r="H79"/>
       <x:c r="I79"/>
       <x:c r="J79"/>
-      <x:c r="K79" t="str">
-        <x:v>Active</x:v>
-      </x:c>
+      <x:c r="K79"/>
       <x:c r="L79"/>
       <x:c r="M79"/>
-      <x:c r="N79" t="str">
-        <x:v>GBP</x:v>
-      </x:c>
+      <x:c r="N79"/>
       <x:c r="O79"/>
       <x:c r="P79"/>
       <x:c r="Q79"/>
@@ -4755,9 +4455,7 @@
       <x:c r="S79"/>
       <x:c r="T79"/>
       <x:c r="U79"/>
-      <x:c r="V79" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
-      </x:c>
+      <x:c r="V79"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="5">
@@ -4779,7 +4477,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3b45ed2e1424ab3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b1006f76e924a01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4803,7 +4501,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>198</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
         <x:v>29</x:v>
@@ -4815,13 +4513,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>199</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>200</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H1" s="3" t="s">
-        <x:v>201</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I1" t="s">
         <x:v>46</x:v>
@@ -5184,7 +4882,7 @@
       </x:c>
       <x:c r="H17"/>
       <x:c r="I17" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -5209,7 +4907,7 @@
       </x:c>
       <x:c r="H18"/>
       <x:c r="I18" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -5236,7 +4934,7 @@
         <x:v>Nano receiver for this keyboard and mouse set</x:v>
       </x:c>
       <x:c r="I19" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -5261,7 +4959,7 @@
       </x:c>
       <x:c r="H20"/>
       <x:c r="I20" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -5286,7 +4984,7 @@
       </x:c>
       <x:c r="H21"/>
       <x:c r="I21" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -5313,7 +5011,7 @@
         <x:v>Nano receiver for this keyboard and mouse set</x:v>
       </x:c>
       <x:c r="I22" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -5338,7 +5036,7 @@
       </x:c>
       <x:c r="H23"/>
       <x:c r="I23" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -5363,7 +5061,7 @@
       </x:c>
       <x:c r="H24"/>
       <x:c r="I24" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -5390,7 +5088,7 @@
         <x:v>Nano receiver for this keyboard and mouse set</x:v>
       </x:c>
       <x:c r="I25" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -5415,7 +5113,7 @@
       </x:c>
       <x:c r="H26"/>
       <x:c r="I26" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -5440,7 +5138,7 @@
       </x:c>
       <x:c r="H27"/>
       <x:c r="I27" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -5467,7 +5165,7 @@
         <x:v>Nano receiver for this keyboard and mouse set</x:v>
       </x:c>
       <x:c r="I28" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -5492,7 +5190,7 @@
       </x:c>
       <x:c r="H29"/>
       <x:c r="I29" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -5517,7 +5215,7 @@
       </x:c>
       <x:c r="H30"/>
       <x:c r="I30" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -5544,7 +5242,7 @@
         <x:v>Nano receiver for this keyboard and mouse set</x:v>
       </x:c>
       <x:c r="I31" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5558,7 +5256,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcf6dd3a50754133"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4281346b77d947fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5577,87 +5275,87 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>203</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>204</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D1" s="3" t="s">
-        <x:v>201</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="10" t="s">
-        <x:v>205</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B2" s="10" t="s">
-        <x:v>206</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C2" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D2" s="4"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="s">
-        <x:v>208</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>209</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C3" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D3" s="4"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="s">
-        <x:v>210</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B4" s="10" t="s">
-        <x:v>211</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C4" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D4" s="4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="s">
-        <x:v>212</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B5" s="10" t="s">
-        <x:v>213</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C5" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D5" s="4"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="s">
-        <x:v>214</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B6" s="10" t="s">
-        <x:v>215</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C6" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D6" s="4"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="s">
-        <x:v>216</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B7" s="10" t="s">
-        <x:v>217</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C7" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D7" s="4"/>
     </x:row>
@@ -5669,7 +5367,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb078d135983444b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcb593d5602a4751"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5691,120 +5389,120 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>218</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C1" s="3" t="s">
-        <x:v>219</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="10" t="s">
-        <x:v>49</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B2" s="10" t="s">
-        <x:v>220</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C2" s="11" t="s">
-        <x:v>221</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B3" s="10" t="s">
-        <x:v>222</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>223</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="s">
-        <x:v>224</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B4" s="10" t="s">
-        <x:v>225</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C4" s="11" t="s">
-        <x:v>226</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B5" s="10" t="s">
-        <x:v>227</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C5" s="11" t="s">
-        <x:v>228</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="s">
-        <x:v>102</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B6" s="10" t="s">
-        <x:v>229</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>230</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="s">
-        <x:v>110</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B7" s="10" t="s">
-        <x:v>231</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
-        <x:v>232</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="s">
-        <x:v>120</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B8" s="10" t="s">
-        <x:v>233</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C8" s="11" t="s">
-        <x:v>234</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10" t="s">
-        <x:v>130</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B9" s="10" t="s">
-        <x:v>235</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C9" s="11" t="s">
-        <x:v>236</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="s">
-        <x:v>237</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B10" s="10" t="s">
-        <x:v>238</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C10" s="11" t="s">
-        <x:v>239</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="s">
-        <x:v>191</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>240</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>241</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -5843,7 +5541,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a356ff9ed5c4848"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf5e125fad024d6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/templates/NFC_Inventory_Import_Template.xlsx
+++ b/data/templates/NFC_Inventory_Import_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R825b30ce035344b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R50c028b5084544b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="Rd4c794bb905244c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="R8b73a9e01e534673"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R9e247bb6e2274f25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R1be9b515e85a47a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R5921a656f590438b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="Re5dfcdaa88734f42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="Race9fedfdab5486f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R30e0a418c9a04711"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -508,8 +508,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentTable" displayName="EquipmentTable" ref="A1:V79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:V79"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentTable" displayName="EquipmentTable" ref="A1:V81" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:V81"/>
   <x:tableColumns count="22">
     <x:tableColumn id="1" name="asset_code"/>
     <x:tableColumn id="2" name="equipment_name"/>
@@ -824,7 +824,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="6" t="str">
-        <x:v>77 unique equipment units are included. One asset code is used for each physical unit or complete bundle.</x:v>
+        <x:v>79 unique equipment units are included. One asset code is used for each physical unit or complete bundle.</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="D4" s="4"/>
@@ -4434,20 +4434,38 @@
       </x:c>
     </x:row>
     <x:row r="79">
-      <x:c r="A79"/>
-      <x:c r="B79"/>
-      <x:c r="C79"/>
-      <x:c r="D79"/>
-      <x:c r="E79"/>
-      <x:c r="F79"/>
+      <x:c r="A79" t="str">
+        <x:v>AUD-003</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>DJI Mic 3 Transmitter</x:v>
+      </x:c>
+      <x:c r="C79" t="str">
+        <x:v>Audio equipment</x:v>
+      </x:c>
+      <x:c r="D79" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E79" t="str">
+        <x:v>DJI</x:v>
+      </x:c>
+      <x:c r="F79" t="str">
+        <x:v>DMT03</x:v>
+      </x:c>
       <x:c r="G79"/>
-      <x:c r="H79"/>
+      <x:c r="H79" t="str">
+        <x:v>Wireless microphone transmitter; 32-bit float/24-bit internal recording, 32 GB storage, Bluetooth 5.4 and up to 8-hour operation</x:v>
+      </x:c>
       <x:c r="I79"/>
       <x:c r="J79"/>
-      <x:c r="K79"/>
+      <x:c r="K79" t="str">
+        <x:v>Active</x:v>
+      </x:c>
       <x:c r="L79"/>
       <x:c r="M79"/>
-      <x:c r="N79"/>
+      <x:c r="N79" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
       <x:c r="O79"/>
       <x:c r="P79"/>
       <x:c r="Q79"/>
@@ -4455,7 +4473,77 @@
       <x:c r="S79"/>
       <x:c r="T79"/>
       <x:c r="U79"/>
-      <x:c r="V79"/>
+      <x:c r="V79" t="str">
+        <x:v>https://se-cdn.djiits.com/tpc/uploads/spu/cover/5ac37a6cf8ca7e9e01c18dd9fc096fe8%40small.png?format=webp</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str">
+        <x:v>AUD-004</x:v>
+      </x:c>
+      <x:c r="B80" t="str">
+        <x:v>DJI Mic 3 Transmitter</x:v>
+      </x:c>
+      <x:c r="C80" t="str">
+        <x:v>Audio equipment</x:v>
+      </x:c>
+      <x:c r="D80" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E80" t="str">
+        <x:v>DJI</x:v>
+      </x:c>
+      <x:c r="F80" t="str">
+        <x:v>DMT03</x:v>
+      </x:c>
+      <x:c r="G80"/>
+      <x:c r="H80" t="str">
+        <x:v>Wireless microphone transmitter; 32-bit float/24-bit internal recording, 32 GB storage, Bluetooth 5.4 and up to 8-hour operation</x:v>
+      </x:c>
+      <x:c r="I80"/>
+      <x:c r="J80"/>
+      <x:c r="K80" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L80"/>
+      <x:c r="M80"/>
+      <x:c r="N80" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="O80"/>
+      <x:c r="P80"/>
+      <x:c r="Q80"/>
+      <x:c r="R80"/>
+      <x:c r="S80"/>
+      <x:c r="T80"/>
+      <x:c r="U80"/>
+      <x:c r="V80" t="str">
+        <x:v>https://se-cdn.djiits.com/tpc/uploads/spu/cover/5ac37a6cf8ca7e9e01c18dd9fc096fe8%40small.png?format=webp</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81"/>
+      <x:c r="B81"/>
+      <x:c r="C81"/>
+      <x:c r="D81"/>
+      <x:c r="E81"/>
+      <x:c r="F81"/>
+      <x:c r="G81"/>
+      <x:c r="H81"/>
+      <x:c r="I81"/>
+      <x:c r="J81"/>
+      <x:c r="K81"/>
+      <x:c r="L81"/>
+      <x:c r="M81"/>
+      <x:c r="N81"/>
+      <x:c r="O81"/>
+      <x:c r="P81"/>
+      <x:c r="Q81"/>
+      <x:c r="R81"/>
+      <x:c r="S81"/>
+      <x:c r="T81"/>
+      <x:c r="U81"/>
+      <x:c r="V81"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="5">
@@ -4477,7 +4565,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b1006f76e924a01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3047bf5b53d4886"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5256,7 +5344,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4281346b77d947fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00d18770f38f4c0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5367,7 +5455,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcb593d5602a4751"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75e21adb1ff64988"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5541,7 +5629,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf5e125fad024d6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb49f1abc9e0848f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/templates/NFC_Inventory_Import_Template.xlsx
+++ b/data/templates/NFC_Inventory_Import_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R1be9b515e85a47a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R5921a656f590438b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="Re5dfcdaa88734f42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="Race9fedfdab5486f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R30e0a418c9a04711"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rdf3cfd2e609f40a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb1372ea0635b4219"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="R5d867cb2a2524b48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="Rabf45558dd3942f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R1b0c3d6972834e81"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -557,8 +557,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="MembersTable" displayName="MembersTable" ref="A1:D7" totalsRowShown="0">
-  <x:autoFilter ref="A1:D7"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="MembersTable" displayName="MembersTable" ref="A1:D8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D8"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="username"/>
     <x:tableColumn id="2" name="display_name"/>
@@ -4565,7 +4565,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3047bf5b53d4886"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11450d08c6664261"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5344,7 +5344,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00d18770f38f4c0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fa08336730b48b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5447,6 +5447,18 @@
       </x:c>
       <x:c r="D7" s="4"/>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>naimeh.fakhr-vaezi25</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>Naimeh</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D8"/>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="C2:C7">
@@ -5455,7 +5467,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75e21adb1ff64988"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31aed7fdeb2e4633"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5629,7 +5641,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb49f1abc9e0848f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f89ac8cdb7c4ffb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/templates/NFC_Inventory_Import_Template.xlsx
+++ b/data/templates/NFC_Inventory_Import_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rdf3cfd2e609f40a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb1372ea0635b4219"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="R5d867cb2a2524b48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="Rabf45558dd3942f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R1b0c3d6972834e81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R163bc0692e304949"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb602d8c0fe4f46f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="Rf03e4402a5f246b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="Re32920b2b3184301"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="Rffaf204d6896427b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4522,20 +4522,38 @@
       </x:c>
     </x:row>
     <x:row r="81">
-      <x:c r="A81"/>
-      <x:c r="B81"/>
-      <x:c r="C81"/>
-      <x:c r="D81"/>
-      <x:c r="E81"/>
-      <x:c r="F81"/>
+      <x:c r="A81" t="str">
+        <x:v>AUD-005</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>DJI Mic 3 Set</x:v>
+      </x:c>
+      <x:c r="C81" t="str">
+        <x:v>Audio equipment</x:v>
+      </x:c>
+      <x:c r="D81" t="str">
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E81" t="str">
+        <x:v>DJI</x:v>
+      </x:c>
+      <x:c r="F81" t="str">
+        <x:v>DJI Mic 3 (2 TX + 1 RX)</x:v>
+      </x:c>
       <x:c r="G81"/>
-      <x:c r="H81"/>
+      <x:c r="H81" t="str">
+        <x:v>Wireless microphone set with one receiver, two transmitters and charging case; 32-bit float/24-bit recording, 400 m maximum transmission range and up to 28-hour operation with case</x:v>
+      </x:c>
       <x:c r="I81"/>
       <x:c r="J81"/>
-      <x:c r="K81"/>
+      <x:c r="K81" t="str">
+        <x:v>Active</x:v>
+      </x:c>
       <x:c r="L81"/>
       <x:c r="M81"/>
-      <x:c r="N81"/>
+      <x:c r="N81" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
       <x:c r="O81"/>
       <x:c r="P81"/>
       <x:c r="Q81"/>
@@ -4543,7 +4561,9 @@
       <x:c r="S81"/>
       <x:c r="T81"/>
       <x:c r="U81"/>
-      <x:c r="V81"/>
+      <x:c r="V81" t="str">
+        <x:v>https://se-cdn.djiits.com/tpc/uploads/spu/cover/473691cc5e140d0341a30b31b479c627%40small.png?format=webp</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="5">
@@ -4565,7 +4585,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11450d08c6664261"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d4115b8e82f40f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5344,7 +5364,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fa08336730b48b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39a9becd9f514c35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5467,7 +5487,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31aed7fdeb2e4633"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35ccca0549894800"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5641,7 +5661,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f89ac8cdb7c4ffb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88b6b225f2844c98"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/templates/NFC_Inventory_Import_Template.xlsx
+++ b/data/templates/NFC_Inventory_Import_Template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R163bc0692e304949"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb602d8c0fe4f46f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="Rf03e4402a5f246b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="Re32920b2b3184301"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="Rffaf204d6896427b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rb357be9528194c38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R8d9308c0e0074fc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bundle contents" sheetId="3" r:id="R4ad25641f56a4c2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="4" r:id="R6bcd363f104841ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="5" r:id="R432f5b42b1d9497a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1172,31 +1172,25 @@
         <x:v>ROB-003</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>Reachy Mini Wireless</x:v>
+        <x:v>NAO Robot</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
         <x:v>Robots</x:v>
       </x:c>
       <x:c r="D4" s="10" t="str">
-        <x:v>Bundle</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>Pollen Robotics</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="str">
-        <x:v>Reachy Mini Wireless</x:v>
-      </x:c>
+        <x:v>Individual</x:v>
+      </x:c>
+      <x:c r="E4" s="4"/>
+      <x:c r="F4" s="4"/>
       <x:c r="G4" s="4"/>
       <x:c r="H4" s="11"/>
       <x:c r="I4" s="11"/>
       <x:c r="J4" s="11"/>
       <x:c r="K4" s="12" t="str">
-        <x:v>Active</x:v>
+        <x:v>Retired</x:v>
       </x:c>
       <x:c r="L4" s="13"/>
-      <x:c r="M4" s="14" t="n">
-        <x:v>439.93</x:v>
-      </x:c>
+      <x:c r="M4" s="14"/>
       <x:c r="N4" s="11" t="str">
         <x:v>GBP</x:v>
       </x:c>
@@ -1206,11 +1200,9 @@
       <x:c r="R4" s="11"/>
       <x:c r="S4" s="11"/>
       <x:c r="T4" s="11"/>
-      <x:c r="U4" s="11" t="str">
-        <x:v>SQ550205 / REACHY-MIN-WLS</x:v>
-      </x:c>
+      <x:c r="U4" s="11"/>
       <x:c r="V4" s="11" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="37.5">
@@ -1279,16 +1271,16 @@
         <x:v>Reachy Mini Wireless</x:v>
       </x:c>
       <x:c r="G6" s="4"/>
-      <x:c r="H6" s="11" t="str">
-        <x:v>Wireless Reachy Mini robot bundle</x:v>
-      </x:c>
+      <x:c r="H6" s="11"/>
       <x:c r="I6" s="11"/>
       <x:c r="J6" s="11"/>
       <x:c r="K6" s="12" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L6" s="13"/>
-      <x:c r="M6" s="14"/>
+      <x:c r="M6" s="14" t="n">
+        <x:v>439.93</x:v>
+      </x:c>
       <x:c r="N6" s="11" t="str">
         <x:v>GBP</x:v>
       </x:c>
@@ -1298,7 +1290,9 @@
       <x:c r="R6" s="11"/>
       <x:c r="S6" s="11"/>
       <x:c r="T6" s="11"/>
-      <x:c r="U6" s="11"/>
+      <x:c r="U6" s="11" t="str">
+        <x:v>SQ550205 / REACHY-MIN-WLS</x:v>
+      </x:c>
       <x:c r="V6" s="11" t="str">
         <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
       </x:c>
@@ -4585,7 +4579,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d4115b8e82f40f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d95a47ebcc64f96"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4635,7 +4629,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="10" t="str">
-        <x:v>ROB-003</x:v>
+        <x:v>ROB-004</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>Robot</x:v>
@@ -4644,7 +4638,7 @@
         <x:v>Pollen Robotics</x:v>
       </x:c>
       <x:c r="D2" s="4" t="str">
-        <x:v>Reachy Mini Wireless</x:v>
+        <x:v>Reachy Mini Lite</x:v>
       </x:c>
       <x:c r="E2" s="4"/>
       <x:c r="F2" s="10" t="n">
@@ -4655,12 +4649,12 @@
       </x:c>
       <x:c r="H2" s="11"/>
       <x:c r="I2" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-lite.png</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="10" t="str">
-        <x:v>ROB-003</x:v>
+        <x:v>ROB-004</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
         <x:v>Charger</x:v>
@@ -4681,7 +4675,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="str">
-        <x:v>ROB-003</x:v>
+        <x:v>ROB-004</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
         <x:v>USB Cable</x:v>
@@ -4702,7 +4696,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="str">
-        <x:v>ROB-004</x:v>
+        <x:v>ROB-005</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
         <x:v>Robot</x:v>
@@ -4711,7 +4705,7 @@
         <x:v>Pollen Robotics</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
-        <x:v>Reachy Mini Lite</x:v>
+        <x:v>Reachy Mini Wireless</x:v>
       </x:c>
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="10" t="n">
@@ -4722,12 +4716,12 @@
       </x:c>
       <x:c r="H5" s="11"/>
       <x:c r="I5" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-lite.png</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="str">
-        <x:v>ROB-004</x:v>
+        <x:v>ROB-005</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
         <x:v>Charger</x:v>
@@ -4748,7 +4742,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="str">
-        <x:v>ROB-004</x:v>
+        <x:v>ROB-005</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
         <x:v>USB Cable</x:v>
@@ -4769,7 +4763,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="str">
-        <x:v>ROB-005</x:v>
+        <x:v>ROB-006</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
         <x:v>Robot</x:v>
@@ -4794,7 +4788,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10" t="str">
-        <x:v>ROB-005</x:v>
+        <x:v>ROB-006</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
         <x:v>Charger</x:v>
@@ -4815,7 +4809,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="str">
-        <x:v>ROB-005</x:v>
+        <x:v>ROB-006</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
         <x:v>USB Cable</x:v>
@@ -4836,7 +4830,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="10" t="str">
-        <x:v>ROB-006</x:v>
+        <x:v>ROB-007</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
         <x:v>Robot</x:v>
@@ -4861,7 +4855,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="10" t="str">
-        <x:v>ROB-006</x:v>
+        <x:v>ROB-007</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
         <x:v>Charger</x:v>
@@ -4882,7 +4876,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="10" t="str">
-        <x:v>ROB-006</x:v>
+        <x:v>ROB-007</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
         <x:v>USB Cable</x:v>
@@ -4903,16 +4897,16 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>ROB-007</x:v>
+        <x:v>PER-001</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>Robot</x:v>
+        <x:v>Keyboard</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>Pollen Robotics</x:v>
+        <x:v>Logitech</x:v>
       </x:c>
       <x:c r="D14" t="str">
-        <x:v>Reachy Mini Wireless</x:v>
+        <x:v>MK270</x:v>
       </x:c>
       <x:c r="E14"/>
       <x:c r="F14" t="n">
@@ -4923,18 +4917,22 @@
       </x:c>
       <x:c r="H14"/>
       <x:c r="I14" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/reachy-mini-wireless.png</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>ROB-007</x:v>
+        <x:v>PER-001</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>Charger</x:v>
-      </x:c>
-      <x:c r="C15"/>
-      <x:c r="D15"/>
+        <x:v>Mouse</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
       <x:c r="E15"/>
       <x:c r="F15" t="n">
         <x:v>1</x:v>
@@ -4944,18 +4942,22 @@
       </x:c>
       <x:c r="H15"/>
       <x:c r="I15" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>ROB-007</x:v>
+        <x:v>PER-001</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>USB Cable</x:v>
-      </x:c>
-      <x:c r="C16"/>
-      <x:c r="D16"/>
+        <x:v>USB receiver</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Logitech</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>MK270</x:v>
+      </x:c>
       <x:c r="E16"/>
       <x:c r="F16" t="n">
         <x:v>1</x:v>
@@ -4963,14 +4965,16 @@
       <x:c r="G16" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="H16"/>
+      <x:c r="H16" t="str">
+        <x:v>Nano receiver for this keyboard and mouse set</x:v>
+      </x:c>
       <x:c r="I16" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment-placeholder.svg</x:v>
+        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>PER-001</x:v>
+        <x:v>PER-002</x:v>
       </x:c>
       <x:c r="B17" t="str">
         <x:v>Keyboard</x:v>
@@ -4995,7 +4999,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>PER-001</x:v>
+        <x:v>PER-002</x:v>
       </x:c>
       <x:c r="B18" t="str">
         <x:v>Mouse</x:v>
@@ -5020,7 +5024,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>PER-001</x:v>
+        <x:v>PER-002</x:v>
       </x:c>
       <x:c r="B19" t="str">
         <x:v>USB receiver</x:v>
@@ -5047,7 +5051,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
-        <x:v>PER-002</x:v>
+        <x:v>PER-003</x:v>
       </x:c>
       <x:c r="B20" t="str">
         <x:v>Keyboard</x:v>
@@ -5072,7 +5076,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
-        <x:v>PER-002</x:v>
+        <x:v>PER-003</x:v>
       </x:c>
       <x:c r="B21" t="str">
         <x:v>Mouse</x:v>
@@ -5097,7 +5101,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>PER-002</x:v>
+        <x:v>PER-003</x:v>
       </x:c>
       <x:c r="B22" t="str">
         <x:v>USB receiver</x:v>
@@ -5124,7 +5128,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>PER-003</x:v>
+        <x:v>PER-004</x:v>
       </x:c>
       <x:c r="B23" t="str">
         <x:v>Keyboard</x:v>
@@ -5149,7 +5153,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>PER-003</x:v>
+        <x:v>PER-004</x:v>
       </x:c>
       <x:c r="B24" t="str">
         <x:v>Mouse</x:v>
@@ -5174,7 +5178,7 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>PER-003</x:v>
+        <x:v>PER-004</x:v>
       </x:c>
       <x:c r="B25" t="str">
         <x:v>USB receiver</x:v>
@@ -5201,7 +5205,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>PER-004</x:v>
+        <x:v>PER-005</x:v>
       </x:c>
       <x:c r="B26" t="str">
         <x:v>Keyboard</x:v>
@@ -5226,7 +5230,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>PER-004</x:v>
+        <x:v>PER-005</x:v>
       </x:c>
       <x:c r="B27" t="str">
         <x:v>Mouse</x:v>
@@ -5251,7 +5255,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
-        <x:v>PER-004</x:v>
+        <x:v>PER-005</x:v>
       </x:c>
       <x:c r="B28" t="str">
         <x:v>USB receiver</x:v>
@@ -5277,81 +5281,37 @@
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" t="str">
-        <x:v>PER-005</x:v>
-      </x:c>
-      <x:c r="B29" t="str">
-        <x:v>Keyboard</x:v>
-      </x:c>
-      <x:c r="C29" t="str">
-        <x:v>Logitech</x:v>
-      </x:c>
-      <x:c r="D29" t="str">
-        <x:v>MK270</x:v>
-      </x:c>
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
       <x:c r="E29"/>
-      <x:c r="F29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G29" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
       <x:c r="H29"/>
-      <x:c r="I29" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
-      </x:c>
+      <x:c r="I29"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" t="str">
-        <x:v>PER-005</x:v>
-      </x:c>
-      <x:c r="B30" t="str">
-        <x:v>Mouse</x:v>
-      </x:c>
-      <x:c r="C30" t="str">
-        <x:v>Logitech</x:v>
-      </x:c>
-      <x:c r="D30" t="str">
-        <x:v>MK270</x:v>
-      </x:c>
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
       <x:c r="E30"/>
-      <x:c r="F30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G30" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
       <x:c r="H30"/>
-      <x:c r="I30" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
-      </x:c>
+      <x:c r="I30"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" t="str">
-        <x:v>PER-005</x:v>
-      </x:c>
-      <x:c r="B31" t="str">
-        <x:v>USB receiver</x:v>
-      </x:c>
-      <x:c r="C31" t="str">
-        <x:v>Logitech</x:v>
-      </x:c>
-      <x:c r="D31" t="str">
-        <x:v>MK270</x:v>
-      </x:c>
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
       <x:c r="E31"/>
-      <x:c r="F31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G31" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H31" t="str">
-        <x:v>Nano receiver for this keyboard and mouse set</x:v>
-      </x:c>
-      <x:c r="I31" t="str">
-        <x:v>https://pair-lab-imperial.github.io/nfc-inventory/assets/equipment/logitech-mk270.png</x:v>
-      </x:c>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
+      <x:c r="I31"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="2">
@@ -5364,7 +5324,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39a9becd9f514c35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4d75266a3e1472d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5487,7 +5447,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35ccca0549894800"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfadc1275e962498f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5661,7 +5621,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88b6b225f2844c98"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f76eecd563043ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>